--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="F14" t="n">
-        <v>7.63</v>
+        <v>7.74</v>
       </c>
       <c r="G14" t="n">
-        <v>318</v>
+        <v>308.7</v>
       </c>
       <c r="H14" t="n">
-        <v>47</v>
+        <v>49.4</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>10.38</v>
+        <v>17.89</v>
       </c>
       <c r="K14" t="n">
-        <v>105.18</v>
+        <v>-25.07</v>
       </c>
       <c r="L14" t="n">
-        <v>105.69</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:01:10</t>
+          <t>05:02:03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.57</v>
+        <v>2.02</v>
       </c>
       <c r="F15" t="n">
-        <v>8.25</v>
+        <v>7.41</v>
       </c>
       <c r="G15" t="n">
-        <v>316.9</v>
+        <v>309.3</v>
       </c>
       <c r="H15" t="n">
-        <v>47.2</v>
+        <v>49.4</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>48.73</v>
+        <v>-47.37</v>
       </c>
       <c r="K15" t="n">
-        <v>12.24</v>
+        <v>-22.93</v>
       </c>
       <c r="L15" t="n">
-        <v>50.25</v>
+        <v>52.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:03:21</t>
+          <t>05:03:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="F16" t="n">
-        <v>7.42</v>
+        <v>8.48</v>
       </c>
       <c r="G16" t="n">
-        <v>305.3</v>
+        <v>320.5</v>
       </c>
       <c r="H16" t="n">
-        <v>47.9</v>
+        <v>57.3</v>
       </c>
       <c r="I16" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>56.92</v>
+        <v>50.3</v>
       </c>
       <c r="K16" t="n">
-        <v>93.41</v>
+        <v>-44.8</v>
       </c>
       <c r="L16" t="n">
-        <v>109.39</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:06:38</t>
+          <t>05:06:35</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="F17" t="n">
-        <v>8.25</v>
+        <v>7.88</v>
       </c>
       <c r="G17" t="n">
-        <v>318.2</v>
+        <v>300.8</v>
       </c>
       <c r="H17" t="n">
-        <v>45.4</v>
+        <v>57.2</v>
       </c>
       <c r="I17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>36.1</v>
+        <v>118.08</v>
       </c>
       <c r="K17" t="n">
-        <v>42.59</v>
+        <v>137.16</v>
       </c>
       <c r="L17" t="n">
-        <v>55.83</v>
+        <v>180.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:07:21</t>
+          <t>05:08:17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="F18" t="n">
-        <v>7.29</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>306.1</v>
+        <v>328.7</v>
       </c>
       <c r="H18" t="n">
-        <v>54.7</v>
+        <v>51.1</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-169.68</v>
+        <v>11.32</v>
       </c>
       <c r="K18" t="n">
-        <v>62.4</v>
+        <v>-26.55</v>
       </c>
       <c r="L18" t="n">
-        <v>180.79</v>
+        <v>28.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:08:48</t>
+          <t>05:09:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="F19" t="n">
-        <v>7.49</v>
+        <v>7.56</v>
       </c>
       <c r="G19" t="n">
-        <v>306.5</v>
+        <v>290.6</v>
       </c>
       <c r="H19" t="n">
-        <v>42.9</v>
+        <v>45.6</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-144.72</v>
+        <v>-87.18000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>54.73</v>
+        <v>-304.04</v>
       </c>
       <c r="L19" t="n">
-        <v>154.72</v>
+        <v>316.29</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:13:57</t>
+          <t>05:13:46</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="F20" t="n">
-        <v>7.41</v>
+        <v>8.26</v>
       </c>
       <c r="G20" t="n">
-        <v>288.4</v>
+        <v>313.9</v>
       </c>
       <c r="H20" t="n">
-        <v>50.5</v>
+        <v>48.6</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-89.68000000000001</v>
+        <v>155.97</v>
       </c>
       <c r="K20" t="n">
-        <v>-107.13</v>
+        <v>180.36</v>
       </c>
       <c r="L20" t="n">
-        <v>139.71</v>
+        <v>238.45</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:15:41</t>
+          <t>05:14:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="F21" t="n">
-        <v>7.25</v>
+        <v>7.91</v>
       </c>
       <c r="G21" t="n">
-        <v>310.7</v>
+        <v>304.5</v>
       </c>
       <c r="H21" t="n">
-        <v>50.1</v>
+        <v>49.4</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>58.15</v>
+        <v>-182.9</v>
       </c>
       <c r="K21" t="n">
-        <v>42.96</v>
+        <v>-103.41</v>
       </c>
       <c r="L21" t="n">
-        <v>72.3</v>
+        <v>210.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:16:51</t>
+          <t>05:15:38</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="F22" t="n">
-        <v>7.87</v>
+        <v>7.31</v>
       </c>
       <c r="G22" t="n">
-        <v>324.2</v>
+        <v>303.4</v>
       </c>
       <c r="H22" t="n">
-        <v>50.3</v>
+        <v>55.2</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-77.48999999999999</v>
+        <v>-143.43</v>
       </c>
       <c r="K22" t="n">
-        <v>-79.93000000000001</v>
+        <v>-96.62</v>
       </c>
       <c r="L22" t="n">
-        <v>111.33</v>
+        <v>172.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:21:16</t>
+          <t>05:20:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.43</v>
+        <v>1.84</v>
       </c>
       <c r="F23" t="n">
-        <v>8.039999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="G23" t="n">
-        <v>311.1</v>
+        <v>319</v>
       </c>
       <c r="H23" t="n">
-        <v>54.4</v>
+        <v>47</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>334.22</v>
+        <v>-167.89</v>
       </c>
       <c r="K23" t="n">
-        <v>269.48</v>
+        <v>-161.79</v>
       </c>
       <c r="L23" t="n">
-        <v>429.33</v>
+        <v>233.15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:22:43</t>
+          <t>05:21:41</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="F24" t="n">
-        <v>8</v>
+        <v>7.51</v>
       </c>
       <c r="G24" t="n">
-        <v>308.5</v>
+        <v>299.4</v>
       </c>
       <c r="H24" t="n">
-        <v>58.2</v>
+        <v>58.5</v>
       </c>
       <c r="I24" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>68.06</v>
+        <v>-276.36</v>
       </c>
       <c r="K24" t="n">
-        <v>140.71</v>
+        <v>28</v>
       </c>
       <c r="L24" t="n">
-        <v>156.31</v>
+        <v>277.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:24:12</t>
+          <t>05:22:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>7.39</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>313.9</v>
+        <v>310.9</v>
       </c>
       <c r="H25" t="n">
-        <v>55.7</v>
+        <v>46.3</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>108.83</v>
+        <v>26.57</v>
       </c>
       <c r="K25" t="n">
-        <v>12</v>
+        <v>-110.91</v>
       </c>
       <c r="L25" t="n">
-        <v>109.49</v>
+        <v>114.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:28:18</t>
+          <t>05:28:41</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="F26" t="n">
-        <v>7.78</v>
+        <v>7.79</v>
       </c>
       <c r="G26" t="n">
-        <v>321.8</v>
+        <v>310</v>
       </c>
       <c r="H26" t="n">
-        <v>56.8</v>
+        <v>53</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>280.69</v>
+        <v>-261.18</v>
       </c>
       <c r="K26" t="n">
-        <v>244.95</v>
+        <v>248.19</v>
       </c>
       <c r="L26" t="n">
-        <v>372.54</v>
+        <v>360.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:30:08</t>
+          <t>05:29:43</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.76</v>
+        <v>2.52</v>
       </c>
       <c r="F27" t="n">
-        <v>7.61</v>
+        <v>7.21</v>
       </c>
       <c r="G27" t="n">
-        <v>307.2</v>
+        <v>308.9</v>
       </c>
       <c r="H27" t="n">
-        <v>53.8</v>
+        <v>53.1</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>43.94</v>
+        <v>210.72</v>
       </c>
       <c r="K27" t="n">
-        <v>377.29</v>
+        <v>586.79</v>
       </c>
       <c r="L27" t="n">
-        <v>379.84</v>
+        <v>623.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:32:21</t>
+          <t>05:32:02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>8.07</v>
       </c>
       <c r="G28" t="n">
-        <v>322.8</v>
+        <v>287.9</v>
       </c>
       <c r="H28" t="n">
-        <v>51.4</v>
+        <v>46</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>299.21</v>
+        <v>-13.27</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.04</v>
+        <v>-439.38</v>
       </c>
       <c r="L28" t="n">
-        <v>299.24</v>
+        <v>439.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:42:25</t>
+          <t>05:42:56</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="F29" t="n">
-        <v>8.49</v>
+        <v>7.65</v>
       </c>
       <c r="G29" t="n">
-        <v>314.2</v>
+        <v>316.1</v>
       </c>
       <c r="H29" t="n">
-        <v>53.3</v>
+        <v>52.2</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-105.2</v>
+        <v>53.03</v>
       </c>
       <c r="K29" t="n">
-        <v>-38.62</v>
+        <v>-100.49</v>
       </c>
       <c r="L29" t="n">
-        <v>112.07</v>
+        <v>113.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:44:53</t>
+          <t>05:44:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.42</v>
+        <v>2.69</v>
       </c>
       <c r="F30" t="n">
-        <v>7.11</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>304.8</v>
+        <v>313</v>
       </c>
       <c r="H30" t="n">
-        <v>45.3</v>
+        <v>53</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>92.06999999999999</v>
+        <v>129.73</v>
       </c>
       <c r="K30" t="n">
-        <v>76.09</v>
+        <v>-48.93</v>
       </c>
       <c r="L30" t="n">
-        <v>119.44</v>
+        <v>138.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:46:32</t>
+          <t>05:45:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.19</v>
+        <v>2.62</v>
       </c>
       <c r="F31" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="G31" t="n">
-        <v>323.1</v>
+        <v>319</v>
       </c>
       <c r="H31" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>35.92</v>
+        <v>-62.66</v>
       </c>
       <c r="K31" t="n">
-        <v>-71.81</v>
+        <v>64.22</v>
       </c>
       <c r="L31" t="n">
-        <v>80.29000000000001</v>
+        <v>89.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:50:27</t>
+          <t>05:50:17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.16</v>
+        <v>2.79</v>
       </c>
       <c r="F32" t="n">
-        <v>7.28</v>
+        <v>7.93</v>
       </c>
       <c r="G32" t="n">
-        <v>328.4</v>
+        <v>312.4</v>
       </c>
       <c r="H32" t="n">
-        <v>58.1</v>
+        <v>62.3</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-185.63</v>
+        <v>-5.33</v>
       </c>
       <c r="K32" t="n">
-        <v>12.83</v>
+        <v>39.79</v>
       </c>
       <c r="L32" t="n">
-        <v>186.07</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:51:56</t>
+          <t>05:51:48</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="F33" t="n">
-        <v>8.1</v>
+        <v>7.55</v>
       </c>
       <c r="G33" t="n">
-        <v>311.3</v>
+        <v>314.3</v>
       </c>
       <c r="H33" t="n">
-        <v>48.8</v>
+        <v>44.9</v>
       </c>
       <c r="I33" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-73.02</v>
+        <v>211</v>
       </c>
       <c r="K33" t="n">
-        <v>-20.06</v>
+        <v>-101.14</v>
       </c>
       <c r="L33" t="n">
-        <v>75.72</v>
+        <v>233.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:52:33</t>
+          <t>05:53:38</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.54</v>
+        <v>2.09</v>
       </c>
       <c r="F34" t="n">
-        <v>7.83</v>
+        <v>7.76</v>
       </c>
       <c r="G34" t="n">
-        <v>303.4</v>
+        <v>310.9</v>
       </c>
       <c r="H34" t="n">
-        <v>50.5</v>
+        <v>48</v>
       </c>
       <c r="I34" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-72.69</v>
+        <v>-17.75</v>
       </c>
       <c r="K34" t="n">
-        <v>86.5</v>
+        <v>-84.86</v>
       </c>
       <c r="L34" t="n">
-        <v>112.99</v>
+        <v>86.7</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:56:39</t>
+          <t>05:58:21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="F35" t="n">
-        <v>8.050000000000001</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>305.9</v>
+        <v>309.8</v>
       </c>
       <c r="H35" t="n">
-        <v>59.3</v>
+        <v>57</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>186.3</v>
+        <v>204.7</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.05</v>
+        <v>120.74</v>
       </c>
       <c r="L35" t="n">
-        <v>201.61</v>
+        <v>237.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:58:30</t>
+          <t>05:58:51</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="F36" t="n">
-        <v>7.1</v>
+        <v>7.99</v>
       </c>
       <c r="G36" t="n">
-        <v>305.4</v>
+        <v>293.5</v>
       </c>
       <c r="H36" t="n">
-        <v>51.2</v>
+        <v>50.1</v>
       </c>
       <c r="I36" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>62.98</v>
+        <v>129.28</v>
       </c>
       <c r="K36" t="n">
-        <v>42.23</v>
+        <v>-15.69</v>
       </c>
       <c r="L36" t="n">
-        <v>75.81999999999999</v>
+        <v>130.23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:00:33</t>
+          <t>06:00:48</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="F37" t="n">
-        <v>7.61</v>
+        <v>7.39</v>
       </c>
       <c r="G37" t="n">
-        <v>308.7</v>
+        <v>309.7</v>
       </c>
       <c r="H37" t="n">
-        <v>52</v>
+        <v>41.2</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-6.63</v>
+        <v>62</v>
       </c>
       <c r="K37" t="n">
-        <v>-220.6</v>
+        <v>-83.45</v>
       </c>
       <c r="L37" t="n">
-        <v>220.7</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:04:18</t>
+          <t>06:04:42</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.49</v>
+        <v>2.04</v>
       </c>
       <c r="F38" t="n">
-        <v>8.23</v>
+        <v>7.43</v>
       </c>
       <c r="G38" t="n">
-        <v>325.7</v>
+        <v>302.1</v>
       </c>
       <c r="H38" t="n">
-        <v>48.9</v>
+        <v>51</v>
       </c>
       <c r="I38" t="n">
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>295.98</v>
+        <v>-50.13</v>
       </c>
       <c r="K38" t="n">
-        <v>394.56</v>
+        <v>281.49</v>
       </c>
       <c r="L38" t="n">
-        <v>493.24</v>
+        <v>285.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:05:03</t>
+          <t>06:06:10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="F39" t="n">
-        <v>7.67</v>
+        <v>8.18</v>
       </c>
       <c r="G39" t="n">
-        <v>317.5</v>
+        <v>319</v>
       </c>
       <c r="H39" t="n">
-        <v>53.4</v>
+        <v>52.8</v>
       </c>
       <c r="I39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-229.44</v>
+        <v>-100.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-366.05</v>
+        <v>18.55</v>
       </c>
       <c r="L39" t="n">
-        <v>432.01</v>
+        <v>102.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:07:15</t>
+          <t>06:07:50</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="F40" t="n">
-        <v>7.9</v>
+        <v>7.67</v>
       </c>
       <c r="G40" t="n">
-        <v>310.2</v>
+        <v>318</v>
       </c>
       <c r="H40" t="n">
-        <v>56.2</v>
+        <v>55.5</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>372.44</v>
+        <v>-76.84999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>132.37</v>
+        <v>-119.7</v>
       </c>
       <c r="L40" t="n">
-        <v>395.27</v>
+        <v>142.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:12:02</t>
+          <t>06:12:42</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="F41" t="n">
-        <v>7.56</v>
+        <v>7.53</v>
       </c>
       <c r="G41" t="n">
-        <v>313.3</v>
+        <v>315.7</v>
       </c>
       <c r="H41" t="n">
-        <v>51.5</v>
+        <v>52.3</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>184.27</v>
+        <v>-699.1900000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>-134.18</v>
+        <v>141.62</v>
       </c>
       <c r="L41" t="n">
-        <v>227.95</v>
+        <v>713.39</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:13:34</t>
+          <t>06:14:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="F42" t="n">
-        <v>8.06</v>
+        <v>8.41</v>
       </c>
       <c r="G42" t="n">
-        <v>316.5</v>
+        <v>308.7</v>
       </c>
       <c r="H42" t="n">
-        <v>49.8</v>
+        <v>50.7</v>
       </c>
       <c r="I42" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>122.55</v>
+        <v>80.36</v>
       </c>
       <c r="K42" t="n">
-        <v>333.92</v>
+        <v>-343.4</v>
       </c>
       <c r="L42" t="n">
-        <v>355.7</v>
+        <v>352.68</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:15:19</t>
+          <t>06:16:38</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.54</v>
+        <v>2.97</v>
       </c>
       <c r="F43" t="n">
-        <v>7.38</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>312.7</v>
+        <v>306.9</v>
       </c>
       <c r="H43" t="n">
-        <v>47.6</v>
+        <v>52.4</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>593.95</v>
+        <v>-89.14</v>
       </c>
       <c r="K43" t="n">
-        <v>-575.3099999999999</v>
+        <v>186.65</v>
       </c>
       <c r="L43" t="n">
-        <v>826.9</v>
+        <v>206.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:26:29</t>
+          <t>06:28:02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="F44" t="n">
-        <v>7.71</v>
+        <v>7.57</v>
       </c>
       <c r="G44" t="n">
-        <v>312.6</v>
+        <v>314.6</v>
       </c>
       <c r="H44" t="n">
-        <v>55.1</v>
+        <v>52.4</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-16.63</v>
+        <v>-127.94</v>
       </c>
       <c r="K44" t="n">
-        <v>-59.75</v>
+        <v>-147.2</v>
       </c>
       <c r="L44" t="n">
-        <v>62.02</v>
+        <v>195.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:28:39</t>
+          <t>06:29:06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="F45" t="n">
-        <v>7.94</v>
+        <v>6.82</v>
       </c>
       <c r="G45" t="n">
-        <v>312.7</v>
+        <v>320.3</v>
       </c>
       <c r="H45" t="n">
-        <v>52.2</v>
+        <v>47.8</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-101.29</v>
+        <v>160.57</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.96</v>
+        <v>81.33</v>
       </c>
       <c r="L45" t="n">
-        <v>101.53</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:30:18</t>
+          <t>06:30:33</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.41</v>
+        <v>2.37</v>
       </c>
       <c r="F46" t="n">
-        <v>7.91</v>
+        <v>7.56</v>
       </c>
       <c r="G46" t="n">
-        <v>315.9</v>
+        <v>321.9</v>
       </c>
       <c r="H46" t="n">
-        <v>53.1</v>
+        <v>45.8</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>61.11</v>
+        <v>-160.69</v>
       </c>
       <c r="K46" t="n">
-        <v>29.9</v>
+        <v>25.43</v>
       </c>
       <c r="L46" t="n">
-        <v>68.03</v>
+        <v>162.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:35:32</t>
+          <t>06:34:58</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="F47" t="n">
-        <v>7.83</v>
+        <v>7.07</v>
       </c>
       <c r="G47" t="n">
-        <v>314.9</v>
+        <v>306.2</v>
       </c>
       <c r="H47" t="n">
-        <v>55.8</v>
+        <v>52.3</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>-68.41</v>
+        <v>63.91</v>
       </c>
       <c r="K47" t="n">
-        <v>121.43</v>
+        <v>42.26</v>
       </c>
       <c r="L47" t="n">
-        <v>139.38</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:36:34</t>
+          <t>06:36:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="F48" t="n">
-        <v>7.39</v>
+        <v>7.51</v>
       </c>
       <c r="G48" t="n">
-        <v>318.5</v>
+        <v>311.3</v>
       </c>
       <c r="H48" t="n">
-        <v>51.2</v>
+        <v>50.3</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>12.97</v>
+        <v>36.01</v>
       </c>
       <c r="K48" t="n">
-        <v>45.16</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>46.99</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:38:10</t>
+          <t>06:38:39</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="F49" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="G49" t="n">
-        <v>298.3</v>
+        <v>329.6</v>
       </c>
       <c r="H49" t="n">
-        <v>48.4</v>
+        <v>51.4</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.36</v>
+        <v>-54.88</v>
       </c>
       <c r="K49" t="n">
-        <v>58.77</v>
+        <v>108.86</v>
       </c>
       <c r="L49" t="n">
-        <v>64.01000000000001</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:43:21</t>
+          <t>06:42:40</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="F50" t="n">
-        <v>7.53</v>
+        <v>7.71</v>
       </c>
       <c r="G50" t="n">
-        <v>327.5</v>
+        <v>308.6</v>
       </c>
       <c r="H50" t="n">
-        <v>56.3</v>
+        <v>59.2</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>44.34</v>
+        <v>145.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-53.24</v>
+        <v>-90.56999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>69.28</v>
+        <v>171.59</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:44:28</t>
+          <t>06:43:45</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.6</v>
+        <v>2.73</v>
       </c>
       <c r="F51" t="n">
-        <v>7.39</v>
+        <v>7.69</v>
       </c>
       <c r="G51" t="n">
-        <v>309</v>
+        <v>316.6</v>
       </c>
       <c r="H51" t="n">
-        <v>50.1</v>
+        <v>48.5</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>19.02</v>
+        <v>-87.2</v>
       </c>
       <c r="K51" t="n">
-        <v>-8.82</v>
+        <v>-161.52</v>
       </c>
       <c r="L51" t="n">
-        <v>20.97</v>
+        <v>183.56</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:46:48</t>
+          <t>06:45:55</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="F52" t="n">
-        <v>7.44</v>
+        <v>8.35</v>
       </c>
       <c r="G52" t="n">
-        <v>316.6</v>
+        <v>313.6</v>
       </c>
       <c r="H52" t="n">
-        <v>47.9</v>
+        <v>50</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-24.13</v>
+        <v>-63.32</v>
       </c>
       <c r="K52" t="n">
-        <v>-39.93</v>
+        <v>69.61</v>
       </c>
       <c r="L52" t="n">
-        <v>46.65</v>
+        <v>94.09999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:51:43</t>
+          <t>06:50:30</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.24</v>
+        <v>1.98</v>
       </c>
       <c r="F53" t="n">
-        <v>8.1</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>298.4</v>
+        <v>298</v>
       </c>
       <c r="H53" t="n">
-        <v>43.5</v>
+        <v>48.2</v>
       </c>
       <c r="I53" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>397.5</v>
+        <v>14.45</v>
       </c>
       <c r="K53" t="n">
-        <v>-213.26</v>
+        <v>-125.89</v>
       </c>
       <c r="L53" t="n">
-        <v>451.09</v>
+        <v>126.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:54:03</t>
+          <t>06:52:25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.89</v>
+        <v>2.52</v>
       </c>
       <c r="F54" t="n">
-        <v>8.1</v>
+        <v>7.38</v>
       </c>
       <c r="G54" t="n">
-        <v>305</v>
+        <v>314.4</v>
       </c>
       <c r="H54" t="n">
-        <v>52.4</v>
+        <v>50</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>22.28</v>
+        <v>228.95</v>
       </c>
       <c r="K54" t="n">
-        <v>949.16</v>
+        <v>276</v>
       </c>
       <c r="L54" t="n">
-        <v>949.42</v>
+        <v>358.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:55:12</t>
+          <t>06:54:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="F55" t="n">
-        <v>7.33</v>
+        <v>7.16</v>
       </c>
       <c r="G55" t="n">
-        <v>299.2</v>
+        <v>296.3</v>
       </c>
       <c r="H55" t="n">
-        <v>45</v>
+        <v>49.3</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-28.57</v>
+        <v>-45.01</v>
       </c>
       <c r="K55" t="n">
-        <v>-71.56</v>
+        <v>325.03</v>
       </c>
       <c r="L55" t="n">
-        <v>77.05</v>
+        <v>328.13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>06:59:56</t>
+          <t>07:00:25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="F56" t="n">
-        <v>7.36</v>
+        <v>7.97</v>
       </c>
       <c r="G56" t="n">
-        <v>313.2</v>
+        <v>307</v>
       </c>
       <c r="H56" t="n">
-        <v>52.5</v>
+        <v>54.4</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>302.3</v>
+        <v>394.54</v>
       </c>
       <c r="K56" t="n">
-        <v>2.5</v>
+        <v>-142.57</v>
       </c>
       <c r="L56" t="n">
-        <v>302.31</v>
+        <v>419.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:01:20</t>
+          <t>07:02:57</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.62</v>
+        <v>2.77</v>
       </c>
       <c r="F57" t="n">
-        <v>7.84</v>
+        <v>6.89</v>
       </c>
       <c r="G57" t="n">
-        <v>300.7</v>
+        <v>310.8</v>
       </c>
       <c r="H57" t="n">
-        <v>59.8</v>
+        <v>51</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>136.53</v>
+        <v>416.36</v>
       </c>
       <c r="K57" t="n">
-        <v>-384.08</v>
+        <v>-112.25</v>
       </c>
       <c r="L57" t="n">
-        <v>407.62</v>
+        <v>431.22</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:02:20</t>
+          <t>07:03:42</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="F58" t="n">
-        <v>7.7</v>
+        <v>7.33</v>
       </c>
       <c r="G58" t="n">
-        <v>300.2</v>
+        <v>312.3</v>
       </c>
       <c r="H58" t="n">
-        <v>45.7</v>
+        <v>55.4</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>335.75</v>
+        <v>445.03</v>
       </c>
       <c r="K58" t="n">
-        <v>-316.25</v>
+        <v>173.85</v>
       </c>
       <c r="L58" t="n">
-        <v>461.24</v>
+        <v>477.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:14:13</t>
+          <t>07:13:06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>3.44</v>
+        <v>2.51</v>
       </c>
       <c r="F59" t="n">
-        <v>7.02</v>
+        <v>7.99</v>
       </c>
       <c r="G59" t="n">
-        <v>305.5</v>
+        <v>313.3</v>
       </c>
       <c r="H59" t="n">
-        <v>49.3</v>
+        <v>54.4</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-92.84</v>
+        <v>-198.4</v>
       </c>
       <c r="K59" t="n">
-        <v>-74.06999999999999</v>
+        <v>36.82</v>
       </c>
       <c r="L59" t="n">
-        <v>118.77</v>
+        <v>201.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:15:17</t>
+          <t>07:14:41</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="F60" t="n">
-        <v>7.86</v>
+        <v>6.98</v>
       </c>
       <c r="G60" t="n">
-        <v>307.3</v>
+        <v>298.4</v>
       </c>
       <c r="H60" t="n">
-        <v>46.1</v>
+        <v>50.3</v>
       </c>
       <c r="I60" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>79.61</v>
+        <v>40.03</v>
       </c>
       <c r="K60" t="n">
-        <v>88.53</v>
+        <v>-215.84</v>
       </c>
       <c r="L60" t="n">
-        <v>119.05</v>
+        <v>219.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:16:11</t>
+          <t>07:17:20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="F61" t="n">
-        <v>7.19</v>
+        <v>7.16</v>
       </c>
       <c r="G61" t="n">
-        <v>308.4</v>
+        <v>319.2</v>
       </c>
       <c r="H61" t="n">
-        <v>47.1</v>
+        <v>56.1</v>
       </c>
       <c r="I61" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-36.04</v>
+        <v>-41.56</v>
       </c>
       <c r="K61" t="n">
-        <v>65.09999999999999</v>
+        <v>-124.37</v>
       </c>
       <c r="L61" t="n">
-        <v>74.41</v>
+        <v>131.13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:20:28</t>
+          <t>07:21:11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.86</v>
+        <v>3.03</v>
       </c>
       <c r="F62" t="n">
-        <v>7.39</v>
+        <v>7.91</v>
       </c>
       <c r="G62" t="n">
-        <v>310.3</v>
+        <v>319.2</v>
       </c>
       <c r="H62" t="n">
-        <v>50.5</v>
+        <v>52.2</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-13.26</v>
+        <v>-44.09</v>
       </c>
       <c r="K62" t="n">
-        <v>-144.85</v>
+        <v>95.64</v>
       </c>
       <c r="L62" t="n">
-        <v>145.46</v>
+        <v>105.31</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:21:53</t>
+          <t>07:22:54</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.05</v>
+        <v>2.53</v>
       </c>
       <c r="F63" t="n">
-        <v>8.550000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="G63" t="n">
-        <v>304.9</v>
+        <v>295.8</v>
       </c>
       <c r="H63" t="n">
-        <v>52.3</v>
+        <v>41.8</v>
       </c>
       <c r="I63" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>91.75</v>
+        <v>-168.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-53.12</v>
+        <v>-119.71</v>
       </c>
       <c r="L63" t="n">
-        <v>106.02</v>
+        <v>206.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:22:50</t>
+          <t>07:24:30</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="F64" t="n">
-        <v>7.61</v>
+        <v>7.06</v>
       </c>
       <c r="G64" t="n">
-        <v>314.3</v>
+        <v>323.9</v>
       </c>
       <c r="H64" t="n">
-        <v>51.2</v>
+        <v>55.9</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.84</v>
+        <v>-165.31</v>
       </c>
       <c r="K64" t="n">
-        <v>-23.84</v>
+        <v>149.33</v>
       </c>
       <c r="L64" t="n">
-        <v>36.65</v>
+        <v>222.77</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:27:11</t>
+          <t>07:29:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="F65" t="n">
-        <v>7.58</v>
+        <v>7.91</v>
       </c>
       <c r="G65" t="n">
-        <v>304.9</v>
+        <v>301.8</v>
       </c>
       <c r="H65" t="n">
-        <v>54.8</v>
+        <v>50.9</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>89.11</v>
+        <v>-217.33</v>
       </c>
       <c r="K65" t="n">
-        <v>-283.3</v>
+        <v>105.35</v>
       </c>
       <c r="L65" t="n">
-        <v>296.99</v>
+        <v>241.52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:28:25</t>
+          <t>07:32:26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="F66" t="n">
-        <v>7.6</v>
+        <v>7.79</v>
       </c>
       <c r="G66" t="n">
-        <v>283.8</v>
+        <v>317.9</v>
       </c>
       <c r="H66" t="n">
-        <v>53.2</v>
+        <v>50.6</v>
       </c>
       <c r="I66" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>85.45</v>
+        <v>61.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-222.63</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>238.47</v>
+        <v>106.11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:29:40</t>
+          <t>07:34:06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.94</v>
+        <v>2.71</v>
       </c>
       <c r="F67" t="n">
-        <v>7.52</v>
+        <v>7.65</v>
       </c>
       <c r="G67" t="n">
-        <v>314.9</v>
+        <v>297</v>
       </c>
       <c r="H67" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>37.69</v>
+        <v>254.56</v>
       </c>
       <c r="K67" t="n">
-        <v>5.01</v>
+        <v>-23.11</v>
       </c>
       <c r="L67" t="n">
-        <v>38.02</v>
+        <v>255.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:34:07</t>
+          <t>07:39:49</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="F68" t="n">
-        <v>6.96</v>
+        <v>8.69</v>
       </c>
       <c r="G68" t="n">
-        <v>311.9</v>
+        <v>304</v>
       </c>
       <c r="H68" t="n">
-        <v>55.2</v>
+        <v>49.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-53.41</v>
+        <v>-4.72</v>
       </c>
       <c r="K68" t="n">
-        <v>-397.79</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>401.35</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:36:04</t>
+          <t>07:41:13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.68</v>
+        <v>2.21</v>
       </c>
       <c r="F69" t="n">
-        <v>8.050000000000001</v>
+        <v>7.47</v>
       </c>
       <c r="G69" t="n">
-        <v>329.6</v>
+        <v>292.4</v>
       </c>
       <c r="H69" t="n">
-        <v>54.2</v>
+        <v>51.4</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>380.82</v>
+        <v>95.66</v>
       </c>
       <c r="K69" t="n">
-        <v>327.18</v>
+        <v>233.03</v>
       </c>
       <c r="L69" t="n">
-        <v>502.07</v>
+        <v>251.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:38:02</t>
+          <t>07:42:25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.91</v>
+        <v>2.36</v>
       </c>
       <c r="F70" t="n">
-        <v>6.22</v>
+        <v>7.7</v>
       </c>
       <c r="G70" t="n">
-        <v>302.7</v>
+        <v>323.5</v>
       </c>
       <c r="H70" t="n">
-        <v>50.8</v>
+        <v>50.9</v>
       </c>
       <c r="I70" t="n">
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-194.47</v>
+        <v>187.2</v>
       </c>
       <c r="K70" t="n">
-        <v>3.27</v>
+        <v>-87.67</v>
       </c>
       <c r="L70" t="n">
-        <v>194.5</v>
+        <v>206.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:43:10</t>
+          <t>07:46:44</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.69</v>
+        <v>2.52</v>
       </c>
       <c r="F71" t="n">
-        <v>7.25</v>
+        <v>7.53</v>
       </c>
       <c r="G71" t="n">
-        <v>303.8</v>
+        <v>323.4</v>
       </c>
       <c r="H71" t="n">
-        <v>51.3</v>
+        <v>49</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>209.9</v>
+        <v>390.16</v>
       </c>
       <c r="K71" t="n">
-        <v>17.87</v>
+        <v>8.23</v>
       </c>
       <c r="L71" t="n">
-        <v>210.66</v>
+        <v>390.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:44:51</t>
+          <t>07:47:47</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="F72" t="n">
-        <v>8.01</v>
+        <v>7.18</v>
       </c>
       <c r="G72" t="n">
-        <v>316.7</v>
+        <v>314.2</v>
       </c>
       <c r="H72" t="n">
-        <v>48.3</v>
+        <v>49.3</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>1.03</v>
+        <v>-199.13</v>
       </c>
       <c r="K72" t="n">
-        <v>-526.17</v>
+        <v>60.52</v>
       </c>
       <c r="L72" t="n">
-        <v>526.1799999999999</v>
+        <v>208.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:46:24</t>
+          <t>07:48:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="F73" t="n">
-        <v>8.18</v>
+        <v>7.62</v>
       </c>
       <c r="G73" t="n">
-        <v>321.1</v>
+        <v>307.3</v>
       </c>
       <c r="H73" t="n">
-        <v>49.7</v>
+        <v>62.1</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>34.41</v>
+        <v>-162.95</v>
       </c>
       <c r="K73" t="n">
-        <v>-335.66</v>
+        <v>69.02</v>
       </c>
       <c r="L73" t="n">
-        <v>337.42</v>
+        <v>176.96</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:57:40</t>
+          <t>07:58:03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.41</v>
+        <v>2.86</v>
       </c>
       <c r="F74" t="n">
-        <v>7.27</v>
+        <v>7.78</v>
       </c>
       <c r="G74" t="n">
-        <v>319.4</v>
+        <v>319.2</v>
       </c>
       <c r="H74" t="n">
-        <v>56.7</v>
+        <v>55.4</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-37.47</v>
+        <v>114.41</v>
       </c>
       <c r="K74" t="n">
-        <v>94.05</v>
+        <v>-114.44</v>
       </c>
       <c r="L74" t="n">
-        <v>101.24</v>
+        <v>161.82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>07:59:58</t>
+          <t>08:00:05</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="F75" t="n">
-        <v>8.119999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="G75" t="n">
-        <v>311.7</v>
+        <v>301.3</v>
       </c>
       <c r="H75" t="n">
-        <v>47</v>
+        <v>46.3</v>
       </c>
       <c r="I75" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>0.27</v>
+        <v>-83.5</v>
       </c>
       <c r="K75" t="n">
-        <v>84.69</v>
+        <v>51.12</v>
       </c>
       <c r="L75" t="n">
-        <v>84.69</v>
+        <v>97.91</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:01:20</t>
+          <t>08:00:58</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="F76" t="n">
-        <v>7.16</v>
+        <v>7.6</v>
       </c>
       <c r="G76" t="n">
-        <v>316.2</v>
+        <v>323</v>
       </c>
       <c r="H76" t="n">
-        <v>54.3</v>
+        <v>60</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-198.52</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>115.77</v>
+        <v>-0.47</v>
       </c>
       <c r="L76" t="n">
-        <v>229.81</v>
+        <v>68.26000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:05:49</t>
+          <t>08:04:02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.03</v>
+        <v>2.37</v>
       </c>
       <c r="F77" t="n">
-        <v>7.89</v>
+        <v>7.8</v>
       </c>
       <c r="G77" t="n">
-        <v>325.7</v>
+        <v>309.1</v>
       </c>
       <c r="H77" t="n">
-        <v>52.6</v>
+        <v>56.1</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-10.64</v>
+        <v>-175.67</v>
       </c>
       <c r="K77" t="n">
-        <v>-216.62</v>
+        <v>-43.53</v>
       </c>
       <c r="L77" t="n">
-        <v>216.88</v>
+        <v>180.98</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:07:36</t>
+          <t>08:06:16</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="F78" t="n">
-        <v>7.08</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>307.1</v>
+        <v>311.7</v>
       </c>
       <c r="H78" t="n">
-        <v>54.6</v>
+        <v>46.6</v>
       </c>
       <c r="I78" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>42.01</v>
+        <v>23.43</v>
       </c>
       <c r="K78" t="n">
-        <v>10.18</v>
+        <v>-55.1</v>
       </c>
       <c r="L78" t="n">
-        <v>43.22</v>
+        <v>59.87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:08:41</t>
+          <t>08:08:34</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="F79" t="n">
-        <v>7.69</v>
+        <v>7.29</v>
       </c>
       <c r="G79" t="n">
-        <v>315.4</v>
+        <v>308</v>
       </c>
       <c r="H79" t="n">
-        <v>54.3</v>
+        <v>51</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-131.42</v>
+        <v>-83.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-13.24</v>
+        <v>102.19</v>
       </c>
       <c r="L79" t="n">
-        <v>132.09</v>
+        <v>131.71</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:12:59</t>
+          <t>08:12:33</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.59</v>
+        <v>2.71</v>
       </c>
       <c r="F80" t="n">
-        <v>7.9</v>
+        <v>7.99</v>
       </c>
       <c r="G80" t="n">
-        <v>311</v>
+        <v>307.8</v>
       </c>
       <c r="H80" t="n">
-        <v>53.7</v>
+        <v>46.9</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-84.29000000000001</v>
+        <v>-82.79000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>31.1</v>
+        <v>-401.58</v>
       </c>
       <c r="L80" t="n">
-        <v>89.84</v>
+        <v>410.03</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:14:32</t>
+          <t>08:14:36</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.01</v>
+        <v>2.49</v>
       </c>
       <c r="F81" t="n">
-        <v>7.96</v>
+        <v>7.69</v>
       </c>
       <c r="G81" t="n">
-        <v>313.2</v>
+        <v>317.3</v>
       </c>
       <c r="H81" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.38</v>
+        <v>-250.17</v>
       </c>
       <c r="K81" t="n">
-        <v>-346.73</v>
+        <v>-41.97</v>
       </c>
       <c r="L81" t="n">
-        <v>348.74</v>
+        <v>253.67</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:16:02</t>
+          <t>08:16:11</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="F82" t="n">
-        <v>8.09</v>
+        <v>7.86</v>
       </c>
       <c r="G82" t="n">
-        <v>305.3</v>
+        <v>321.1</v>
       </c>
       <c r="H82" t="n">
-        <v>51.7</v>
+        <v>46.9</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>77.83</v>
+        <v>-76.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-200.85</v>
+        <v>-162.49</v>
       </c>
       <c r="L82" t="n">
-        <v>215.41</v>
+        <v>179.8</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:21:19</t>
+          <t>08:19:22</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.81</v>
+        <v>2.41</v>
       </c>
       <c r="F83" t="n">
-        <v>8.050000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="G83" t="n">
-        <v>302.8</v>
+        <v>307.8</v>
       </c>
       <c r="H83" t="n">
-        <v>54.6</v>
+        <v>52.7</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>55.35</v>
+        <v>367.11</v>
       </c>
       <c r="K83" t="n">
-        <v>114.21</v>
+        <v>241.72</v>
       </c>
       <c r="L83" t="n">
-        <v>126.92</v>
+        <v>439.55</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:22:09</t>
+          <t>08:20:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.92</v>
+        <v>2.73</v>
       </c>
       <c r="F84" t="n">
-        <v>7.85</v>
+        <v>7.53</v>
       </c>
       <c r="G84" t="n">
-        <v>315.7</v>
+        <v>314.8</v>
       </c>
       <c r="H84" t="n">
-        <v>51.9</v>
+        <v>52.3</v>
       </c>
       <c r="I84" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>378.71</v>
+        <v>251.29</v>
       </c>
       <c r="K84" t="n">
-        <v>174</v>
+        <v>24.33</v>
       </c>
       <c r="L84" t="n">
-        <v>416.77</v>
+        <v>252.46</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:23:20</t>
+          <t>08:21:24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.41</v>
+        <v>2.91</v>
       </c>
       <c r="F85" t="n">
-        <v>7.32</v>
+        <v>7.78</v>
       </c>
       <c r="G85" t="n">
-        <v>318.9</v>
+        <v>336.4</v>
       </c>
       <c r="H85" t="n">
-        <v>42.7</v>
+        <v>52.5</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>135.18</v>
+        <v>-75.48</v>
       </c>
       <c r="K85" t="n">
-        <v>633.88</v>
+        <v>384.16</v>
       </c>
       <c r="L85" t="n">
-        <v>648.14</v>
+        <v>391.5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:28:44</t>
+          <t>08:27:17</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.93</v>
+        <v>2.36</v>
       </c>
       <c r="F86" t="n">
-        <v>7.93</v>
+        <v>7.66</v>
       </c>
       <c r="G86" t="n">
-        <v>311.7</v>
+        <v>308.6</v>
       </c>
       <c r="H86" t="n">
-        <v>62.7</v>
+        <v>55.5</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-16.88</v>
+        <v>-242.33</v>
       </c>
       <c r="K86" t="n">
-        <v>111.93</v>
+        <v>-418.91</v>
       </c>
       <c r="L86" t="n">
-        <v>113.19</v>
+        <v>483.96</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:31:04</t>
+          <t>08:28:34</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3694,31 +3694,31 @@
         <v>2.34</v>
       </c>
       <c r="F87" t="n">
-        <v>7.54</v>
+        <v>7.59</v>
       </c>
       <c r="G87" t="n">
-        <v>318.3</v>
+        <v>301.5</v>
       </c>
       <c r="H87" t="n">
-        <v>53.5</v>
+        <v>48.3</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>72.06</v>
+        <v>-283.77</v>
       </c>
       <c r="K87" t="n">
-        <v>480.28</v>
+        <v>-183.04</v>
       </c>
       <c r="L87" t="n">
-        <v>485.65</v>
+        <v>337.68</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:32:38</t>
+          <t>08:30:22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="F88" t="n">
-        <v>8.01</v>
+        <v>7.79</v>
       </c>
       <c r="G88" t="n">
-        <v>309.9</v>
+        <v>327.7</v>
       </c>
       <c r="H88" t="n">
-        <v>47.1</v>
+        <v>52.5</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>-76.39</v>
+        <v>245.35</v>
       </c>
       <c r="K88" t="n">
-        <v>-254.92</v>
+        <v>244</v>
       </c>
       <c r="L88" t="n">
-        <v>266.12</v>
+        <v>346.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>17.89</v>
+        <v>22.45</v>
       </c>
       <c r="K14" t="n">
-        <v>-25.07</v>
+        <v>-31.47</v>
       </c>
       <c r="L14" t="n">
-        <v>30.8</v>
+        <v>38.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.37</v>
+        <v>-41.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.93</v>
+        <v>-20.29</v>
       </c>
       <c r="L15" t="n">
-        <v>52.63</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>50.3</v>
+        <v>46.19</v>
       </c>
       <c r="K16" t="n">
-        <v>-44.8</v>
+        <v>-41.14</v>
       </c>
       <c r="L16" t="n">
-        <v>67.36</v>
+        <v>61.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>118.08</v>
+        <v>92.98</v>
       </c>
       <c r="K17" t="n">
-        <v>137.16</v>
+        <v>107.99</v>
       </c>
       <c r="L17" t="n">
-        <v>180.99</v>
+        <v>142.5</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>11.32</v>
+        <v>21.12</v>
       </c>
       <c r="K18" t="n">
-        <v>-26.55</v>
+        <v>-49.54</v>
       </c>
       <c r="L18" t="n">
-        <v>28.86</v>
+        <v>53.86</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-87.18000000000001</v>
+        <v>-57.93</v>
       </c>
       <c r="K19" t="n">
-        <v>-304.04</v>
+        <v>-202.04</v>
       </c>
       <c r="L19" t="n">
-        <v>316.29</v>
+        <v>210.18</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>155.97</v>
+        <v>140.02</v>
       </c>
       <c r="K20" t="n">
-        <v>180.36</v>
+        <v>161.92</v>
       </c>
       <c r="L20" t="n">
-        <v>238.45</v>
+        <v>214.06</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-182.9</v>
+        <v>-176.59</v>
       </c>
       <c r="K21" t="n">
-        <v>-103.41</v>
+        <v>-99.84999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>210.11</v>
+        <v>202.86</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-143.43</v>
+        <v>-143.87</v>
       </c>
       <c r="K22" t="n">
-        <v>-96.62</v>
+        <v>-96.92</v>
       </c>
       <c r="L22" t="n">
-        <v>172.94</v>
+        <v>173.47</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-167.89</v>
+        <v>-171.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-161.79</v>
+        <v>-164.91</v>
       </c>
       <c r="L23" t="n">
-        <v>233.15</v>
+        <v>237.65</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-276.36</v>
+        <v>-271.71</v>
       </c>
       <c r="K24" t="n">
-        <v>28</v>
+        <v>27.53</v>
       </c>
       <c r="L24" t="n">
-        <v>277.77</v>
+        <v>273.1</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>26.57</v>
+        <v>35.25</v>
       </c>
       <c r="K25" t="n">
-        <v>-110.91</v>
+        <v>-147.18</v>
       </c>
       <c r="L25" t="n">
-        <v>114.05</v>
+        <v>151.35</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-261.18</v>
+        <v>-303.48</v>
       </c>
       <c r="K26" t="n">
-        <v>248.19</v>
+        <v>288.38</v>
       </c>
       <c r="L26" t="n">
-        <v>360.3</v>
+        <v>418.65</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>210.72</v>
+        <v>214.37</v>
       </c>
       <c r="K27" t="n">
-        <v>586.79</v>
+        <v>596.95</v>
       </c>
       <c r="L27" t="n">
-        <v>623.48</v>
+        <v>634.28</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-13.27</v>
+        <v>-17.06</v>
       </c>
       <c r="K28" t="n">
-        <v>-439.38</v>
+        <v>-564.8</v>
       </c>
       <c r="L28" t="n">
-        <v>439.58</v>
+        <v>565.0599999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>53.03</v>
+        <v>39.31</v>
       </c>
       <c r="K29" t="n">
-        <v>-100.49</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>113.62</v>
+        <v>84.23</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>129.73</v>
+        <v>116.68</v>
       </c>
       <c r="K30" t="n">
-        <v>-48.93</v>
+        <v>-44.01</v>
       </c>
       <c r="L30" t="n">
-        <v>138.65</v>
+        <v>124.7</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-62.66</v>
+        <v>-55.81</v>
       </c>
       <c r="K31" t="n">
-        <v>64.22</v>
+        <v>57.2</v>
       </c>
       <c r="L31" t="n">
-        <v>89.72</v>
+        <v>79.92</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.33</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>39.79</v>
+        <v>68.09</v>
       </c>
       <c r="L32" t="n">
-        <v>40.15</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>211</v>
+        <v>163.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-101.14</v>
+        <v>-78.27</v>
       </c>
       <c r="L33" t="n">
-        <v>233.99</v>
+        <v>181.06</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-17.75</v>
+        <v>-19.53</v>
       </c>
       <c r="K34" t="n">
-        <v>-84.86</v>
+        <v>-93.38</v>
       </c>
       <c r="L34" t="n">
-        <v>86.7</v>
+        <v>95.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>204.7</v>
+        <v>185.18</v>
       </c>
       <c r="K35" t="n">
-        <v>120.74</v>
+        <v>109.23</v>
       </c>
       <c r="L35" t="n">
-        <v>237.65</v>
+        <v>214.99</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>129.28</v>
+        <v>134.37</v>
       </c>
       <c r="K36" t="n">
-        <v>-15.69</v>
+        <v>-16.3</v>
       </c>
       <c r="L36" t="n">
-        <v>130.23</v>
+        <v>135.35</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>62</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-83.45</v>
+        <v>-120.94</v>
       </c>
       <c r="L37" t="n">
-        <v>103.96</v>
+        <v>150.66</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-50.13</v>
+        <v>-52.35</v>
       </c>
       <c r="K38" t="n">
-        <v>281.49</v>
+        <v>293.95</v>
       </c>
       <c r="L38" t="n">
-        <v>285.92</v>
+        <v>298.58</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-100.51</v>
+        <v>-179.68</v>
       </c>
       <c r="K39" t="n">
-        <v>18.55</v>
+        <v>33.16</v>
       </c>
       <c r="L39" t="n">
-        <v>102.2</v>
+        <v>182.71</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-76.84999999999999</v>
+        <v>-88.63</v>
       </c>
       <c r="K40" t="n">
-        <v>-119.7</v>
+        <v>-138.05</v>
       </c>
       <c r="L40" t="n">
-        <v>142.24</v>
+        <v>164.05</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-699.1900000000001</v>
+        <v>-697.9400000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>141.62</v>
+        <v>141.37</v>
       </c>
       <c r="L41" t="n">
-        <v>713.39</v>
+        <v>712.12</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>80.36</v>
+        <v>99.88</v>
       </c>
       <c r="K42" t="n">
-        <v>-343.4</v>
+        <v>-426.83</v>
       </c>
       <c r="L42" t="n">
-        <v>352.68</v>
+        <v>438.36</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-89.14</v>
+        <v>-148.27</v>
       </c>
       <c r="K43" t="n">
-        <v>186.65</v>
+        <v>310.45</v>
       </c>
       <c r="L43" t="n">
-        <v>206.84</v>
+        <v>344.04</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-127.94</v>
+        <v>-93.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-147.2</v>
+        <v>-107.72</v>
       </c>
       <c r="L44" t="n">
-        <v>195.03</v>
+        <v>142.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>160.57</v>
+        <v>149.37</v>
       </c>
       <c r="K45" t="n">
-        <v>81.33</v>
+        <v>75.66</v>
       </c>
       <c r="L45" t="n">
-        <v>179.99</v>
+        <v>167.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-160.69</v>
+        <v>-116.74</v>
       </c>
       <c r="K46" t="n">
-        <v>25.43</v>
+        <v>18.48</v>
       </c>
       <c r="L46" t="n">
-        <v>162.69</v>
+        <v>118.19</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>63.91</v>
+        <v>59.6</v>
       </c>
       <c r="K47" t="n">
-        <v>42.26</v>
+        <v>39.41</v>
       </c>
       <c r="L47" t="n">
-        <v>76.62</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>36.01</v>
+        <v>44.74</v>
       </c>
       <c r="K48" t="n">
-        <v>-71.95999999999999</v>
+        <v>-89.41</v>
       </c>
       <c r="L48" t="n">
-        <v>80.47</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-54.88</v>
+        <v>-45.55</v>
       </c>
       <c r="K49" t="n">
-        <v>108.86</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>121.91</v>
+        <v>101.18</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>145.73</v>
+        <v>156.14</v>
       </c>
       <c r="K50" t="n">
-        <v>-90.56999999999999</v>
+        <v>-97.04000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>171.59</v>
+        <v>183.84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-87.2</v>
+        <v>-107.79</v>
       </c>
       <c r="K51" t="n">
-        <v>-161.52</v>
+        <v>-199.67</v>
       </c>
       <c r="L51" t="n">
-        <v>183.56</v>
+        <v>226.91</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-63.32</v>
+        <v>-96.75</v>
       </c>
       <c r="K52" t="n">
-        <v>69.61</v>
+        <v>106.36</v>
       </c>
       <c r="L52" t="n">
-        <v>94.09999999999999</v>
+        <v>143.78</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>14.45</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-125.89</v>
+        <v>-148.08</v>
       </c>
       <c r="L53" t="n">
-        <v>126.72</v>
+        <v>149.06</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>228.95</v>
+        <v>226.64</v>
       </c>
       <c r="K54" t="n">
-        <v>276</v>
+        <v>273.21</v>
       </c>
       <c r="L54" t="n">
-        <v>358.6</v>
+        <v>354.98</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-45.01</v>
+        <v>-46.21</v>
       </c>
       <c r="K55" t="n">
-        <v>325.03</v>
+        <v>333.68</v>
       </c>
       <c r="L55" t="n">
-        <v>328.13</v>
+        <v>336.87</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>394.54</v>
+        <v>496.27</v>
       </c>
       <c r="K56" t="n">
-        <v>-142.57</v>
+        <v>-179.34</v>
       </c>
       <c r="L56" t="n">
-        <v>419.51</v>
+        <v>527.6799999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>416.36</v>
+        <v>495.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-112.25</v>
+        <v>-133.51</v>
       </c>
       <c r="L57" t="n">
-        <v>431.22</v>
+        <v>512.92</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>445.03</v>
+        <v>452.76</v>
       </c>
       <c r="K58" t="n">
-        <v>173.85</v>
+        <v>176.87</v>
       </c>
       <c r="L58" t="n">
-        <v>477.78</v>
+        <v>486.08</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-198.4</v>
+        <v>-144.64</v>
       </c>
       <c r="K59" t="n">
-        <v>36.82</v>
+        <v>26.85</v>
       </c>
       <c r="L59" t="n">
-        <v>201.79</v>
+        <v>147.11</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>40.03</v>
+        <v>28.61</v>
       </c>
       <c r="K60" t="n">
-        <v>-215.84</v>
+        <v>-154.25</v>
       </c>
       <c r="L60" t="n">
-        <v>219.52</v>
+        <v>156.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-41.56</v>
+        <v>-32.82</v>
       </c>
       <c r="K61" t="n">
-        <v>-124.37</v>
+        <v>-98.22</v>
       </c>
       <c r="L61" t="n">
-        <v>131.13</v>
+        <v>103.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.09</v>
+        <v>-56.62</v>
       </c>
       <c r="K62" t="n">
-        <v>95.64</v>
+        <v>122.83</v>
       </c>
       <c r="L62" t="n">
-        <v>105.31</v>
+        <v>135.25</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-168.45</v>
+        <v>-143.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-119.71</v>
+        <v>-102</v>
       </c>
       <c r="L63" t="n">
-        <v>206.66</v>
+        <v>176.09</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-165.31</v>
+        <v>-138.5</v>
       </c>
       <c r="K64" t="n">
-        <v>149.33</v>
+        <v>125.11</v>
       </c>
       <c r="L64" t="n">
-        <v>222.77</v>
+        <v>186.64</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-217.33</v>
+        <v>-210.52</v>
       </c>
       <c r="K65" t="n">
-        <v>105.35</v>
+        <v>102.05</v>
       </c>
       <c r="L65" t="n">
-        <v>241.52</v>
+        <v>233.96</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>61.01</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>86.81999999999999</v>
+        <v>129.08</v>
       </c>
       <c r="L66" t="n">
-        <v>106.11</v>
+        <v>157.77</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>254.56</v>
+        <v>260.79</v>
       </c>
       <c r="K67" t="n">
-        <v>-23.11</v>
+        <v>-23.68</v>
       </c>
       <c r="L67" t="n">
-        <v>255.6</v>
+        <v>261.86</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.72</v>
+        <v>-11.67</v>
       </c>
       <c r="K68" t="n">
-        <v>79.45999999999999</v>
+        <v>196.28</v>
       </c>
       <c r="L68" t="n">
-        <v>79.59999999999999</v>
+        <v>196.63</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>95.66</v>
+        <v>86.47</v>
       </c>
       <c r="K69" t="n">
-        <v>233.03</v>
+        <v>210.64</v>
       </c>
       <c r="L69" t="n">
-        <v>251.9</v>
+        <v>227.7</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>187.2</v>
+        <v>229.66</v>
       </c>
       <c r="K70" t="n">
-        <v>-87.67</v>
+        <v>-107.56</v>
       </c>
       <c r="L70" t="n">
-        <v>206.71</v>
+        <v>253.6</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>390.16</v>
+        <v>442.22</v>
       </c>
       <c r="K71" t="n">
-        <v>8.23</v>
+        <v>9.32</v>
       </c>
       <c r="L71" t="n">
-        <v>390.25</v>
+        <v>442.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-199.13</v>
+        <v>-325.09</v>
       </c>
       <c r="K72" t="n">
-        <v>60.52</v>
+        <v>98.81</v>
       </c>
       <c r="L72" t="n">
-        <v>208.12</v>
+        <v>339.78</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-162.95</v>
+        <v>-281.62</v>
       </c>
       <c r="K73" t="n">
-        <v>69.02</v>
+        <v>119.28</v>
       </c>
       <c r="L73" t="n">
-        <v>176.96</v>
+        <v>305.84</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>114.41</v>
+        <v>100.02</v>
       </c>
       <c r="K74" t="n">
-        <v>-114.44</v>
+        <v>-100.04</v>
       </c>
       <c r="L74" t="n">
-        <v>161.82</v>
+        <v>141.47</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.5</v>
+        <v>-109.92</v>
       </c>
       <c r="K75" t="n">
-        <v>51.12</v>
+        <v>67.28</v>
       </c>
       <c r="L75" t="n">
-        <v>97.91</v>
+        <v>128.87</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>68.26000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.47</v>
+        <v>-0.52</v>
       </c>
       <c r="L76" t="n">
-        <v>68.26000000000001</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-175.67</v>
+        <v>-134.52</v>
       </c>
       <c r="K77" t="n">
-        <v>-43.53</v>
+        <v>-33.34</v>
       </c>
       <c r="L77" t="n">
-        <v>180.98</v>
+        <v>138.59</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>23.43</v>
+        <v>34.17</v>
       </c>
       <c r="K78" t="n">
-        <v>-55.1</v>
+        <v>-80.34999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>59.87</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-83.09</v>
+        <v>-79.69</v>
       </c>
       <c r="K79" t="n">
-        <v>102.19</v>
+        <v>98.01000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>131.71</v>
+        <v>126.31</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-82.79000000000001</v>
+        <v>-65.06</v>
       </c>
       <c r="K80" t="n">
-        <v>-401.58</v>
+        <v>-315.58</v>
       </c>
       <c r="L80" t="n">
-        <v>410.03</v>
+        <v>322.22</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-250.17</v>
+        <v>-225.81</v>
       </c>
       <c r="K81" t="n">
-        <v>-41.97</v>
+        <v>-37.88</v>
       </c>
       <c r="L81" t="n">
-        <v>253.67</v>
+        <v>228.96</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-76.98</v>
+        <v>-77.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-162.49</v>
+        <v>-164.31</v>
       </c>
       <c r="L82" t="n">
-        <v>179.8</v>
+        <v>181.81</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>367.11</v>
+        <v>301.01</v>
       </c>
       <c r="K83" t="n">
-        <v>241.72</v>
+        <v>198.2</v>
       </c>
       <c r="L83" t="n">
-        <v>439.55</v>
+        <v>360.4</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>251.29</v>
+        <v>327.06</v>
       </c>
       <c r="K84" t="n">
-        <v>24.33</v>
+        <v>31.66</v>
       </c>
       <c r="L84" t="n">
-        <v>252.46</v>
+        <v>328.59</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-75.48</v>
+        <v>-77.59</v>
       </c>
       <c r="K85" t="n">
-        <v>384.16</v>
+        <v>394.89</v>
       </c>
       <c r="L85" t="n">
-        <v>391.5</v>
+        <v>402.44</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-242.33</v>
+        <v>-255.79</v>
       </c>
       <c r="K86" t="n">
-        <v>-418.91</v>
+        <v>-442.18</v>
       </c>
       <c r="L86" t="n">
-        <v>483.96</v>
+        <v>510.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-283.77</v>
+        <v>-325.43</v>
       </c>
       <c r="K87" t="n">
-        <v>-183.04</v>
+        <v>-209.91</v>
       </c>
       <c r="L87" t="n">
-        <v>337.68</v>
+        <v>387.26</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>245.35</v>
+        <v>282.06</v>
       </c>
       <c r="K88" t="n">
-        <v>244</v>
+        <v>280.51</v>
       </c>
       <c r="L88" t="n">
-        <v>346.02</v>
+        <v>397.8</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>22.45</v>
+        <v>21.1</v>
       </c>
       <c r="K14" t="n">
-        <v>-31.47</v>
+        <v>-29.57</v>
       </c>
       <c r="L14" t="n">
-        <v>38.66</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-41.91</v>
+        <v>-42.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.29</v>
+        <v>-20.66</v>
       </c>
       <c r="L15" t="n">
-        <v>46.57</v>
+        <v>47.41</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>46.19</v>
+        <v>46.28</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.14</v>
+        <v>-41.22</v>
       </c>
       <c r="L16" t="n">
-        <v>61.86</v>
+        <v>61.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>92.98</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>107.99</v>
+        <v>95.2</v>
       </c>
       <c r="L17" t="n">
-        <v>142.5</v>
+        <v>125.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>21.12</v>
+        <v>19.55</v>
       </c>
       <c r="K18" t="n">
-        <v>-49.54</v>
+        <v>-45.86</v>
       </c>
       <c r="L18" t="n">
-        <v>53.86</v>
+        <v>49.85</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-57.93</v>
+        <v>-50.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-202.04</v>
+        <v>-176.93</v>
       </c>
       <c r="L19" t="n">
-        <v>210.18</v>
+        <v>184.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>140.02</v>
+        <v>96.59</v>
       </c>
       <c r="K20" t="n">
-        <v>161.92</v>
+        <v>111.7</v>
       </c>
       <c r="L20" t="n">
-        <v>214.06</v>
+        <v>147.67</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-176.59</v>
+        <v>-116.87</v>
       </c>
       <c r="K21" t="n">
-        <v>-99.84999999999999</v>
+        <v>-66.08</v>
       </c>
       <c r="L21" t="n">
-        <v>202.86</v>
+        <v>134.25</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-143.87</v>
+        <v>-106.98</v>
       </c>
       <c r="K22" t="n">
-        <v>-96.92</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>173.47</v>
+        <v>128.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-171.12</v>
+        <v>-104.54</v>
       </c>
       <c r="K23" t="n">
-        <v>-164.91</v>
+        <v>-100.75</v>
       </c>
       <c r="L23" t="n">
-        <v>237.65</v>
+        <v>145.19</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-271.71</v>
+        <v>-175.34</v>
       </c>
       <c r="K24" t="n">
-        <v>27.53</v>
+        <v>17.76</v>
       </c>
       <c r="L24" t="n">
-        <v>273.1</v>
+        <v>176.24</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>35.25</v>
+        <v>25.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-147.18</v>
+        <v>-105.57</v>
       </c>
       <c r="L25" t="n">
-        <v>151.35</v>
+        <v>108.55</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-303.48</v>
+        <v>-172.11</v>
       </c>
       <c r="K26" t="n">
-        <v>288.38</v>
+        <v>163.54</v>
       </c>
       <c r="L26" t="n">
-        <v>418.65</v>
+        <v>237.42</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>214.37</v>
+        <v>119.71</v>
       </c>
       <c r="K27" t="n">
-        <v>596.95</v>
+        <v>333.36</v>
       </c>
       <c r="L27" t="n">
-        <v>634.28</v>
+        <v>354.2</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-17.06</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>-564.8</v>
+        <v>-288.61</v>
       </c>
       <c r="L28" t="n">
-        <v>565.0599999999999</v>
+        <v>288.74</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>39.31</v>
+        <v>38.49</v>
       </c>
       <c r="K29" t="n">
-        <v>-74.48999999999999</v>
+        <v>-72.94</v>
       </c>
       <c r="L29" t="n">
-        <v>84.23</v>
+        <v>82.47</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>116.68</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-44.01</v>
+        <v>-36.2</v>
       </c>
       <c r="L30" t="n">
-        <v>124.7</v>
+        <v>102.59</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-55.81</v>
+        <v>-53.92</v>
       </c>
       <c r="K31" t="n">
-        <v>57.2</v>
+        <v>55.26</v>
       </c>
       <c r="L31" t="n">
-        <v>79.92</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-9.119999999999999</v>
+        <v>-8.1</v>
       </c>
       <c r="K32" t="n">
-        <v>68.09</v>
+        <v>60.51</v>
       </c>
       <c r="L32" t="n">
-        <v>68.69</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>163.27</v>
+        <v>126.69</v>
       </c>
       <c r="K33" t="n">
-        <v>-78.27</v>
+        <v>-60.73</v>
       </c>
       <c r="L33" t="n">
-        <v>181.06</v>
+        <v>140.49</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-19.53</v>
+        <v>-15.09</v>
       </c>
       <c r="K34" t="n">
-        <v>-93.38</v>
+        <v>-72.15000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>95.41</v>
+        <v>73.70999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>185.18</v>
+        <v>140.46</v>
       </c>
       <c r="K35" t="n">
-        <v>109.23</v>
+        <v>82.84999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>214.99</v>
+        <v>163.07</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>134.37</v>
+        <v>108.42</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.3</v>
+        <v>-13.15</v>
       </c>
       <c r="L36" t="n">
-        <v>135.35</v>
+        <v>109.21</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>89.84999999999999</v>
+        <v>61.06</v>
       </c>
       <c r="K37" t="n">
-        <v>-120.94</v>
+        <v>-82.18000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>150.66</v>
+        <v>102.38</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-52.35</v>
+        <v>-30.22</v>
       </c>
       <c r="K38" t="n">
-        <v>293.95</v>
+        <v>169.69</v>
       </c>
       <c r="L38" t="n">
-        <v>298.58</v>
+        <v>172.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-179.68</v>
+        <v>-106.33</v>
       </c>
       <c r="K39" t="n">
-        <v>33.16</v>
+        <v>19.62</v>
       </c>
       <c r="L39" t="n">
-        <v>182.71</v>
+        <v>108.12</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-88.63</v>
+        <v>-58.69</v>
       </c>
       <c r="K40" t="n">
-        <v>-138.05</v>
+        <v>-91.42</v>
       </c>
       <c r="L40" t="n">
-        <v>164.05</v>
+        <v>108.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-697.9400000000001</v>
+        <v>-371.59</v>
       </c>
       <c r="K41" t="n">
-        <v>141.37</v>
+        <v>75.27</v>
       </c>
       <c r="L41" t="n">
-        <v>712.12</v>
+        <v>379.13</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>99.88</v>
+        <v>54.26</v>
       </c>
       <c r="K42" t="n">
-        <v>-426.83</v>
+        <v>-231.86</v>
       </c>
       <c r="L42" t="n">
-        <v>438.36</v>
+        <v>238.13</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-148.27</v>
+        <v>-83.28</v>
       </c>
       <c r="K43" t="n">
-        <v>310.45</v>
+        <v>174.37</v>
       </c>
       <c r="L43" t="n">
-        <v>344.04</v>
+        <v>193.24</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-93.62</v>
+        <v>-82.11</v>
       </c>
       <c r="K44" t="n">
-        <v>-107.72</v>
+        <v>-94.47</v>
       </c>
       <c r="L44" t="n">
-        <v>142.72</v>
+        <v>125.17</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>149.37</v>
+        <v>112.71</v>
       </c>
       <c r="K45" t="n">
-        <v>75.66</v>
+        <v>57.08</v>
       </c>
       <c r="L45" t="n">
-        <v>167.44</v>
+        <v>126.34</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-116.74</v>
+        <v>-104.93</v>
       </c>
       <c r="K46" t="n">
-        <v>18.48</v>
+        <v>16.61</v>
       </c>
       <c r="L46" t="n">
-        <v>118.19</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>59.6</v>
+        <v>57.15</v>
       </c>
       <c r="K47" t="n">
-        <v>39.41</v>
+        <v>37.79</v>
       </c>
       <c r="L47" t="n">
-        <v>71.45</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>44.74</v>
+        <v>34.23</v>
       </c>
       <c r="K48" t="n">
-        <v>-89.41</v>
+        <v>-68.40000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>99.98</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-45.55</v>
+        <v>-40.24</v>
       </c>
       <c r="K49" t="n">
-        <v>90.34999999999999</v>
+        <v>79.81999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>101.18</v>
+        <v>89.39</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>156.14</v>
+        <v>110.55</v>
       </c>
       <c r="K50" t="n">
-        <v>-97.04000000000001</v>
+        <v>-68.7</v>
       </c>
       <c r="L50" t="n">
-        <v>183.84</v>
+        <v>130.16</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.79</v>
+        <v>-67.52</v>
       </c>
       <c r="K51" t="n">
-        <v>-199.67</v>
+        <v>-125.07</v>
       </c>
       <c r="L51" t="n">
-        <v>226.91</v>
+        <v>142.13</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-96.75</v>
+        <v>-66.97</v>
       </c>
       <c r="K52" t="n">
-        <v>106.36</v>
+        <v>73.62</v>
       </c>
       <c r="L52" t="n">
-        <v>143.78</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>17</v>
+        <v>11.85</v>
       </c>
       <c r="K53" t="n">
-        <v>-148.08</v>
+        <v>-103.28</v>
       </c>
       <c r="L53" t="n">
-        <v>149.06</v>
+        <v>103.96</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>226.64</v>
+        <v>140.94</v>
       </c>
       <c r="K54" t="n">
-        <v>273.21</v>
+        <v>169.9</v>
       </c>
       <c r="L54" t="n">
-        <v>354.98</v>
+        <v>220.75</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-46.21</v>
+        <v>-30.05</v>
       </c>
       <c r="K55" t="n">
-        <v>333.68</v>
+        <v>217.03</v>
       </c>
       <c r="L55" t="n">
-        <v>336.87</v>
+        <v>219.1</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>496.27</v>
+        <v>261.97</v>
       </c>
       <c r="K56" t="n">
-        <v>-179.34</v>
+        <v>-94.67</v>
       </c>
       <c r="L56" t="n">
-        <v>527.6799999999999</v>
+        <v>278.55</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>495.24</v>
+        <v>271.68</v>
       </c>
       <c r="K57" t="n">
-        <v>-133.51</v>
+        <v>-73.23999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>512.92</v>
+        <v>281.38</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>452.76</v>
+        <v>280.38</v>
       </c>
       <c r="K58" t="n">
-        <v>176.87</v>
+        <v>109.53</v>
       </c>
       <c r="L58" t="n">
-        <v>486.08</v>
+        <v>301.01</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-144.64</v>
+        <v>-126.63</v>
       </c>
       <c r="K59" t="n">
-        <v>26.85</v>
+        <v>23.5</v>
       </c>
       <c r="L59" t="n">
-        <v>147.11</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>28.61</v>
+        <v>25.04</v>
       </c>
       <c r="K60" t="n">
-        <v>-154.25</v>
+        <v>-135.05</v>
       </c>
       <c r="L60" t="n">
-        <v>156.88</v>
+        <v>137.35</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-32.82</v>
+        <v>-29.27</v>
       </c>
       <c r="K61" t="n">
-        <v>-98.22</v>
+        <v>-87.59</v>
       </c>
       <c r="L61" t="n">
-        <v>103.56</v>
+        <v>92.34999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-56.62</v>
+        <v>-41.12</v>
       </c>
       <c r="K62" t="n">
-        <v>122.83</v>
+        <v>89.2</v>
       </c>
       <c r="L62" t="n">
-        <v>135.25</v>
+        <v>98.22</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-143.54</v>
+        <v>-112.61</v>
       </c>
       <c r="K63" t="n">
-        <v>-102</v>
+        <v>-80.02</v>
       </c>
       <c r="L63" t="n">
-        <v>176.09</v>
+        <v>138.15</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-138.5</v>
+        <v>-104.45</v>
       </c>
       <c r="K64" t="n">
-        <v>125.11</v>
+        <v>94.34999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>186.64</v>
+        <v>140.75</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-210.52</v>
+        <v>-151.24</v>
       </c>
       <c r="K65" t="n">
-        <v>102.05</v>
+        <v>73.31999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>233.96</v>
+        <v>168.08</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>90.70999999999999</v>
+        <v>58.43</v>
       </c>
       <c r="K66" t="n">
-        <v>129.08</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>157.77</v>
+        <v>101.63</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>260.79</v>
+        <v>174.13</v>
       </c>
       <c r="K67" t="n">
-        <v>-23.68</v>
+        <v>-15.81</v>
       </c>
       <c r="L67" t="n">
-        <v>261.86</v>
+        <v>174.85</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-11.67</v>
+        <v>-6.44</v>
       </c>
       <c r="K68" t="n">
-        <v>196.28</v>
+        <v>108.4</v>
       </c>
       <c r="L68" t="n">
-        <v>196.63</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>86.47</v>
+        <v>62.78</v>
       </c>
       <c r="K69" t="n">
-        <v>210.64</v>
+        <v>152.94</v>
       </c>
       <c r="L69" t="n">
-        <v>227.7</v>
+        <v>165.33</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>229.66</v>
+        <v>136.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-107.56</v>
+        <v>-63.81</v>
       </c>
       <c r="L70" t="n">
-        <v>253.6</v>
+        <v>150.44</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>442.22</v>
+        <v>256.05</v>
       </c>
       <c r="K71" t="n">
-        <v>9.32</v>
+        <v>5.4</v>
       </c>
       <c r="L71" t="n">
-        <v>442.32</v>
+        <v>256.11</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-325.09</v>
+        <v>-174.45</v>
       </c>
       <c r="K72" t="n">
-        <v>98.81</v>
+        <v>53.02</v>
       </c>
       <c r="L72" t="n">
-        <v>339.78</v>
+        <v>182.33</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-281.62</v>
+        <v>-164.33</v>
       </c>
       <c r="K73" t="n">
-        <v>119.28</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>305.84</v>
+        <v>178.46</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>100.02</v>
+        <v>83.25</v>
       </c>
       <c r="K74" t="n">
-        <v>-100.04</v>
+        <v>-83.27</v>
       </c>
       <c r="L74" t="n">
-        <v>141.47</v>
+        <v>117.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-109.92</v>
+        <v>-79.90000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>67.28</v>
+        <v>48.91</v>
       </c>
       <c r="L75" t="n">
-        <v>128.87</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>76.48999999999999</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.52</v>
+        <v>-0.46</v>
       </c>
       <c r="L76" t="n">
-        <v>76.48999999999999</v>
+        <v>67.48999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-134.52</v>
+        <v>-119.87</v>
       </c>
       <c r="K77" t="n">
-        <v>-33.34</v>
+        <v>-29.71</v>
       </c>
       <c r="L77" t="n">
-        <v>138.59</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>34.17</v>
+        <v>29.53</v>
       </c>
       <c r="K78" t="n">
-        <v>-80.34999999999999</v>
+        <v>-69.44</v>
       </c>
       <c r="L78" t="n">
-        <v>87.31</v>
+        <v>75.45999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-79.69</v>
+        <v>-60.9</v>
       </c>
       <c r="K79" t="n">
-        <v>98.01000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L79" t="n">
-        <v>126.31</v>
+        <v>96.54000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-65.06</v>
+        <v>-50.49</v>
       </c>
       <c r="K80" t="n">
-        <v>-315.58</v>
+        <v>-244.91</v>
       </c>
       <c r="L80" t="n">
-        <v>322.22</v>
+        <v>250.06</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-225.81</v>
+        <v>-165.76</v>
       </c>
       <c r="K81" t="n">
-        <v>-37.88</v>
+        <v>-27.81</v>
       </c>
       <c r="L81" t="n">
-        <v>228.96</v>
+        <v>168.08</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-77.84</v>
+        <v>-53.84</v>
       </c>
       <c r="K82" t="n">
-        <v>-164.31</v>
+        <v>-113.65</v>
       </c>
       <c r="L82" t="n">
-        <v>181.81</v>
+        <v>125.76</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>301.01</v>
+        <v>212.96</v>
       </c>
       <c r="K83" t="n">
-        <v>198.2</v>
+        <v>140.22</v>
       </c>
       <c r="L83" t="n">
-        <v>360.4</v>
+        <v>254.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>327.06</v>
+        <v>180.97</v>
       </c>
       <c r="K84" t="n">
-        <v>31.66</v>
+        <v>17.52</v>
       </c>
       <c r="L84" t="n">
-        <v>328.59</v>
+        <v>181.81</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-77.59</v>
+        <v>-48.23</v>
       </c>
       <c r="K85" t="n">
-        <v>394.89</v>
+        <v>245.43</v>
       </c>
       <c r="L85" t="n">
-        <v>402.44</v>
+        <v>250.13</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-255.79</v>
+        <v>-144.69</v>
       </c>
       <c r="K86" t="n">
-        <v>-442.18</v>
+        <v>-250.13</v>
       </c>
       <c r="L86" t="n">
-        <v>510.84</v>
+        <v>288.96</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-325.43</v>
+        <v>-191.19</v>
       </c>
       <c r="K87" t="n">
-        <v>-209.91</v>
+        <v>-123.32</v>
       </c>
       <c r="L87" t="n">
-        <v>387.26</v>
+        <v>227.51</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>282.06</v>
+        <v>165.01</v>
       </c>
       <c r="K88" t="n">
-        <v>280.51</v>
+        <v>164.11</v>
       </c>
       <c r="L88" t="n">
-        <v>397.8</v>
+        <v>232.73</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>21.1</v>
+        <v>20.55</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.57</v>
+        <v>-28.81</v>
       </c>
       <c r="L14" t="n">
-        <v>36.33</v>
+        <v>35.39</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-42.67</v>
+        <v>-41.34</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.66</v>
+        <v>-20.02</v>
       </c>
       <c r="L15" t="n">
-        <v>47.41</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>46.28</v>
+        <v>45.33</v>
       </c>
       <c r="K16" t="n">
-        <v>-41.22</v>
+        <v>-40.38</v>
       </c>
       <c r="L16" t="n">
-        <v>61.97</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>81.95999999999999</v>
+        <v>83.48</v>
       </c>
       <c r="K17" t="n">
-        <v>95.2</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>125.63</v>
+        <v>127.95</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>19.55</v>
+        <v>19.62</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.86</v>
+        <v>-46.01</v>
       </c>
       <c r="L18" t="n">
-        <v>49.85</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-50.73</v>
+        <v>-50.86</v>
       </c>
       <c r="K19" t="n">
-        <v>-176.93</v>
+        <v>-177.38</v>
       </c>
       <c r="L19" t="n">
-        <v>184.06</v>
+        <v>184.52</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>96.59</v>
+        <v>103.22</v>
       </c>
       <c r="K20" t="n">
-        <v>111.7</v>
+        <v>119.37</v>
       </c>
       <c r="L20" t="n">
-        <v>147.67</v>
+        <v>157.81</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-116.87</v>
+        <v>-125.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-66.08</v>
+        <v>-71.02</v>
       </c>
       <c r="L21" t="n">
-        <v>134.25</v>
+        <v>144.29</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-106.98</v>
+        <v>-113.69</v>
       </c>
       <c r="K22" t="n">
-        <v>-72.06999999999999</v>
+        <v>-76.59</v>
       </c>
       <c r="L22" t="n">
-        <v>128.99</v>
+        <v>137.08</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-104.54</v>
+        <v>-113.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-100.75</v>
+        <v>-109.8</v>
       </c>
       <c r="L23" t="n">
-        <v>145.19</v>
+        <v>158.24</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-175.34</v>
+        <v>-193.91</v>
       </c>
       <c r="K24" t="n">
-        <v>17.76</v>
+        <v>19.64</v>
       </c>
       <c r="L24" t="n">
-        <v>176.24</v>
+        <v>194.9</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>25.28</v>
+        <v>27.03</v>
       </c>
       <c r="K25" t="n">
-        <v>-105.57</v>
+        <v>-112.85</v>
       </c>
       <c r="L25" t="n">
-        <v>108.55</v>
+        <v>116.05</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-172.11</v>
+        <v>-190.7</v>
       </c>
       <c r="K26" t="n">
-        <v>163.54</v>
+        <v>181.21</v>
       </c>
       <c r="L26" t="n">
-        <v>237.42</v>
+        <v>263.06</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>119.71</v>
+        <v>132.4</v>
       </c>
       <c r="K27" t="n">
-        <v>333.36</v>
+        <v>368.69</v>
       </c>
       <c r="L27" t="n">
-        <v>354.2</v>
+        <v>391.74</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-8.720000000000001</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>-288.61</v>
+        <v>-318.17</v>
       </c>
       <c r="L28" t="n">
-        <v>288.74</v>
+        <v>318.31</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>38.49</v>
+        <v>37.64</v>
       </c>
       <c r="K29" t="n">
-        <v>-72.94</v>
+        <v>-71.33</v>
       </c>
       <c r="L29" t="n">
-        <v>82.47</v>
+        <v>80.65000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>95.98999999999999</v>
+        <v>95.43000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-36.2</v>
+        <v>-35.99</v>
       </c>
       <c r="L30" t="n">
-        <v>102.59</v>
+        <v>101.99</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-53.92</v>
+        <v>-52.22</v>
       </c>
       <c r="K31" t="n">
-        <v>55.26</v>
+        <v>53.52</v>
       </c>
       <c r="L31" t="n">
-        <v>77.20999999999999</v>
+        <v>74.78</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-8.1</v>
+        <v>-8.31</v>
       </c>
       <c r="K32" t="n">
-        <v>60.51</v>
+        <v>62.05</v>
       </c>
       <c r="L32" t="n">
-        <v>61.05</v>
+        <v>62.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>126.69</v>
+        <v>129.07</v>
       </c>
       <c r="K33" t="n">
-        <v>-60.73</v>
+        <v>-61.87</v>
       </c>
       <c r="L33" t="n">
-        <v>140.49</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-15.09</v>
+        <v>-15.43</v>
       </c>
       <c r="K34" t="n">
-        <v>-72.15000000000001</v>
+        <v>-73.78</v>
       </c>
       <c r="L34" t="n">
-        <v>73.70999999999999</v>
+        <v>75.38</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>140.46</v>
+        <v>148.85</v>
       </c>
       <c r="K35" t="n">
-        <v>82.84999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="L35" t="n">
-        <v>163.07</v>
+        <v>172.82</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>108.42</v>
+        <v>113.18</v>
       </c>
       <c r="K36" t="n">
-        <v>-13.15</v>
+        <v>-13.73</v>
       </c>
       <c r="L36" t="n">
-        <v>109.21</v>
+        <v>114.01</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>61.06</v>
+        <v>64.27</v>
       </c>
       <c r="K37" t="n">
-        <v>-82.18000000000001</v>
+        <v>-86.5</v>
       </c>
       <c r="L37" t="n">
-        <v>102.38</v>
+        <v>107.77</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-30.22</v>
+        <v>-33.65</v>
       </c>
       <c r="K38" t="n">
-        <v>169.69</v>
+        <v>188.93</v>
       </c>
       <c r="L38" t="n">
-        <v>172.36</v>
+        <v>191.91</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-106.33</v>
+        <v>-117.53</v>
       </c>
       <c r="K39" t="n">
-        <v>19.62</v>
+        <v>21.69</v>
       </c>
       <c r="L39" t="n">
-        <v>108.12</v>
+        <v>119.52</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-58.69</v>
+        <v>-64.04000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-91.42</v>
+        <v>-99.73999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>108.64</v>
+        <v>118.53</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-371.59</v>
+        <v>-415.46</v>
       </c>
       <c r="K41" t="n">
-        <v>75.27</v>
+        <v>84.15000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>379.13</v>
+        <v>423.89</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>54.26</v>
+        <v>60.15</v>
       </c>
       <c r="K42" t="n">
-        <v>-231.86</v>
+        <v>-257.05</v>
       </c>
       <c r="L42" t="n">
-        <v>238.13</v>
+        <v>264</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-83.28</v>
+        <v>-91.18000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>174.37</v>
+        <v>190.92</v>
       </c>
       <c r="L43" t="n">
-        <v>193.24</v>
+        <v>211.58</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-82.11</v>
+        <v>-81.16</v>
       </c>
       <c r="K44" t="n">
-        <v>-94.47</v>
+        <v>-93.38</v>
       </c>
       <c r="L44" t="n">
-        <v>125.17</v>
+        <v>123.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>112.71</v>
+        <v>112.28</v>
       </c>
       <c r="K45" t="n">
-        <v>57.08</v>
+        <v>56.87</v>
       </c>
       <c r="L45" t="n">
-        <v>126.34</v>
+        <v>125.86</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-104.93</v>
+        <v>-102.77</v>
       </c>
       <c r="K46" t="n">
-        <v>16.61</v>
+        <v>16.27</v>
       </c>
       <c r="L46" t="n">
-        <v>106.24</v>
+        <v>104.05</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>57.15</v>
+        <v>57.12</v>
       </c>
       <c r="K47" t="n">
-        <v>37.79</v>
+        <v>37.77</v>
       </c>
       <c r="L47" t="n">
-        <v>68.51000000000001</v>
+        <v>68.48</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>34.23</v>
+        <v>35.24</v>
       </c>
       <c r="K48" t="n">
-        <v>-68.40000000000001</v>
+        <v>-70.41</v>
       </c>
       <c r="L48" t="n">
-        <v>76.48999999999999</v>
+        <v>78.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.24</v>
+        <v>-40.57</v>
       </c>
       <c r="K49" t="n">
-        <v>79.81999999999999</v>
+        <v>80.45999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>89.39</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>110.55</v>
+        <v>118.74</v>
       </c>
       <c r="K50" t="n">
-        <v>-68.7</v>
+        <v>-73.79000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>130.16</v>
+        <v>139.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-67.52</v>
+        <v>-72.48</v>
       </c>
       <c r="K51" t="n">
-        <v>-125.07</v>
+        <v>-134.26</v>
       </c>
       <c r="L51" t="n">
-        <v>142.13</v>
+        <v>152.57</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-66.97</v>
+        <v>-71.02</v>
       </c>
       <c r="K52" t="n">
-        <v>73.62</v>
+        <v>78.06999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>99.52</v>
+        <v>105.54</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>11.85</v>
+        <v>12.77</v>
       </c>
       <c r="K53" t="n">
-        <v>-103.28</v>
+        <v>-111.27</v>
       </c>
       <c r="L53" t="n">
-        <v>103.96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>140.94</v>
+        <v>153.43</v>
       </c>
       <c r="K54" t="n">
-        <v>169.9</v>
+        <v>184.95</v>
       </c>
       <c r="L54" t="n">
-        <v>220.75</v>
+        <v>240.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-30.05</v>
+        <v>-32.24</v>
       </c>
       <c r="K55" t="n">
-        <v>217.03</v>
+        <v>232.8</v>
       </c>
       <c r="L55" t="n">
-        <v>219.1</v>
+        <v>235.02</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>261.97</v>
+        <v>290.83</v>
       </c>
       <c r="K56" t="n">
-        <v>-94.67</v>
+        <v>-105.1</v>
       </c>
       <c r="L56" t="n">
-        <v>278.55</v>
+        <v>309.24</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>271.68</v>
+        <v>298.9</v>
       </c>
       <c r="K57" t="n">
-        <v>-73.23999999999999</v>
+        <v>-80.58</v>
       </c>
       <c r="L57" t="n">
-        <v>281.38</v>
+        <v>309.57</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>280.38</v>
+        <v>305.67</v>
       </c>
       <c r="K58" t="n">
-        <v>109.53</v>
+        <v>119.41</v>
       </c>
       <c r="L58" t="n">
-        <v>301.01</v>
+        <v>328.17</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-126.63</v>
+        <v>-125.51</v>
       </c>
       <c r="K59" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="L59" t="n">
-        <v>128.79</v>
+        <v>127.65</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>25.04</v>
+        <v>24.68</v>
       </c>
       <c r="K60" t="n">
-        <v>-135.05</v>
+        <v>-133.1</v>
       </c>
       <c r="L60" t="n">
-        <v>137.35</v>
+        <v>135.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.27</v>
+        <v>-29.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-87.59</v>
+        <v>-87.02</v>
       </c>
       <c r="L61" t="n">
-        <v>92.34999999999999</v>
+        <v>91.75</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.12</v>
+        <v>-42.8</v>
       </c>
       <c r="K62" t="n">
-        <v>89.2</v>
+        <v>92.84</v>
       </c>
       <c r="L62" t="n">
-        <v>98.22</v>
+        <v>102.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-112.61</v>
+        <v>-114.13</v>
       </c>
       <c r="K63" t="n">
-        <v>-80.02</v>
+        <v>-81.09999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>138.15</v>
+        <v>140.01</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-104.45</v>
+        <v>-108.59</v>
       </c>
       <c r="K64" t="n">
-        <v>94.34999999999999</v>
+        <v>98.09</v>
       </c>
       <c r="L64" t="n">
-        <v>140.75</v>
+        <v>146.33</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-151.24</v>
+        <v>-159.78</v>
       </c>
       <c r="K65" t="n">
-        <v>73.31999999999999</v>
+        <v>77.45</v>
       </c>
       <c r="L65" t="n">
-        <v>168.08</v>
+        <v>177.56</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>58.43</v>
+        <v>62.91</v>
       </c>
       <c r="K66" t="n">
-        <v>83.15000000000001</v>
+        <v>89.52</v>
       </c>
       <c r="L66" t="n">
-        <v>101.63</v>
+        <v>109.41</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>174.13</v>
+        <v>186.55</v>
       </c>
       <c r="K67" t="n">
-        <v>-15.81</v>
+        <v>-16.94</v>
       </c>
       <c r="L67" t="n">
-        <v>174.85</v>
+        <v>187.32</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-6.44</v>
+        <v>-7.09</v>
       </c>
       <c r="K68" t="n">
-        <v>108.4</v>
+        <v>119.34</v>
       </c>
       <c r="L68" t="n">
-        <v>108.59</v>
+        <v>119.55</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>62.78</v>
+        <v>67.68000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>152.94</v>
+        <v>164.88</v>
       </c>
       <c r="L69" t="n">
-        <v>165.33</v>
+        <v>178.23</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>136.24</v>
+        <v>150.24</v>
       </c>
       <c r="K70" t="n">
-        <v>-63.81</v>
+        <v>-70.36</v>
       </c>
       <c r="L70" t="n">
-        <v>150.44</v>
+        <v>165.9</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>256.05</v>
+        <v>280.15</v>
       </c>
       <c r="K71" t="n">
-        <v>5.4</v>
+        <v>5.91</v>
       </c>
       <c r="L71" t="n">
-        <v>256.11</v>
+        <v>280.21</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-174.45</v>
+        <v>-192.71</v>
       </c>
       <c r="K72" t="n">
-        <v>53.02</v>
+        <v>58.57</v>
       </c>
       <c r="L72" t="n">
-        <v>182.33</v>
+        <v>201.42</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-164.33</v>
+        <v>-181.37</v>
       </c>
       <c r="K73" t="n">
-        <v>69.59999999999999</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>178.46</v>
+        <v>196.96</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>83.25</v>
+        <v>82.63</v>
       </c>
       <c r="K74" t="n">
-        <v>-83.27</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>117.75</v>
+        <v>116.87</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-79.90000000000001</v>
+        <v>-79.44</v>
       </c>
       <c r="K75" t="n">
-        <v>48.91</v>
+        <v>48.63</v>
       </c>
       <c r="L75" t="n">
-        <v>93.69</v>
+        <v>93.14</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>67.48999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K76" t="n">
         <v>-0.46</v>
       </c>
       <c r="L76" t="n">
-        <v>67.48999999999999</v>
+        <v>67.08</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-119.87</v>
+        <v>-121.69</v>
       </c>
       <c r="K77" t="n">
-        <v>-29.71</v>
+        <v>-30.16</v>
       </c>
       <c r="L77" t="n">
-        <v>123.5</v>
+        <v>125.38</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>29.53</v>
+        <v>29.77</v>
       </c>
       <c r="K78" t="n">
-        <v>-69.44</v>
+        <v>-70.01000000000001</v>
       </c>
       <c r="L78" t="n">
-        <v>75.45999999999999</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-60.9</v>
+        <v>-62.76</v>
       </c>
       <c r="K79" t="n">
-        <v>74.90000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="L79" t="n">
-        <v>96.54000000000001</v>
+        <v>99.48</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.49</v>
+        <v>-52.47</v>
       </c>
       <c r="K80" t="n">
-        <v>-244.91</v>
+        <v>-254.54</v>
       </c>
       <c r="L80" t="n">
-        <v>250.06</v>
+        <v>259.89</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-165.76</v>
+        <v>-174.75</v>
       </c>
       <c r="K81" t="n">
-        <v>-27.81</v>
+        <v>-29.32</v>
       </c>
       <c r="L81" t="n">
-        <v>168.08</v>
+        <v>177.19</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-53.84</v>
+        <v>-57.4</v>
       </c>
       <c r="K82" t="n">
-        <v>-113.65</v>
+        <v>-121.17</v>
       </c>
       <c r="L82" t="n">
-        <v>125.76</v>
+        <v>134.07</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>212.96</v>
+        <v>229.36</v>
       </c>
       <c r="K83" t="n">
-        <v>140.22</v>
+        <v>151.02</v>
       </c>
       <c r="L83" t="n">
-        <v>254.98</v>
+        <v>274.61</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>180.97</v>
+        <v>199.99</v>
       </c>
       <c r="K84" t="n">
-        <v>17.52</v>
+        <v>19.36</v>
       </c>
       <c r="L84" t="n">
-        <v>181.81</v>
+        <v>200.92</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-48.23</v>
+        <v>-52.19</v>
       </c>
       <c r="K85" t="n">
-        <v>245.43</v>
+        <v>265.63</v>
       </c>
       <c r="L85" t="n">
-        <v>250.13</v>
+        <v>270.71</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-144.69</v>
+        <v>-160.82</v>
       </c>
       <c r="K86" t="n">
-        <v>-250.13</v>
+        <v>-278.01</v>
       </c>
       <c r="L86" t="n">
-        <v>288.96</v>
+        <v>321.18</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-191.19</v>
+        <v>-209.37</v>
       </c>
       <c r="K87" t="n">
-        <v>-123.32</v>
+        <v>-135.05</v>
       </c>
       <c r="L87" t="n">
-        <v>227.51</v>
+        <v>249.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>165.01</v>
+        <v>181.67</v>
       </c>
       <c r="K88" t="n">
-        <v>164.11</v>
+        <v>180.67</v>
       </c>
       <c r="L88" t="n">
-        <v>232.73</v>
+        <v>256.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>20.55</v>
+        <v>14.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.81</v>
+        <v>-20.82</v>
       </c>
       <c r="L14" t="n">
-        <v>35.39</v>
+        <v>25.58</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-41.34</v>
+        <v>-29.18</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.02</v>
+        <v>-14.13</v>
       </c>
       <c r="L15" t="n">
-        <v>45.93</v>
+        <v>32.42</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>45.33</v>
+        <v>28.7</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.38</v>
+        <v>-25.56</v>
       </c>
       <c r="L16" t="n">
-        <v>60.7</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>83.48</v>
+        <v>52.74</v>
       </c>
       <c r="K17" t="n">
-        <v>96.95999999999999</v>
+        <v>61.26</v>
       </c>
       <c r="L17" t="n">
-        <v>127.95</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>19.62</v>
+        <v>5.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.01</v>
+        <v>-13.58</v>
       </c>
       <c r="L18" t="n">
-        <v>50.01</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-50.86</v>
+        <v>-34.24</v>
       </c>
       <c r="K19" t="n">
-        <v>-177.38</v>
+        <v>-119.4</v>
       </c>
       <c r="L19" t="n">
-        <v>184.52</v>
+        <v>124.22</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>103.22</v>
+        <v>71.64</v>
       </c>
       <c r="K20" t="n">
-        <v>119.37</v>
+        <v>82.84</v>
       </c>
       <c r="L20" t="n">
-        <v>157.81</v>
+        <v>109.52</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-125.61</v>
+        <v>-88.34999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-71.02</v>
+        <v>-49.95</v>
       </c>
       <c r="L21" t="n">
-        <v>144.29</v>
+        <v>101.49</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-113.69</v>
+        <v>-71.56999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-76.59</v>
+        <v>-48.21</v>
       </c>
       <c r="L22" t="n">
-        <v>137.08</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-113.94</v>
+        <v>-85.45</v>
       </c>
       <c r="K23" t="n">
-        <v>-109.8</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>158.24</v>
+        <v>118.68</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-193.91</v>
+        <v>-133.34</v>
       </c>
       <c r="K24" t="n">
-        <v>19.64</v>
+        <v>13.51</v>
       </c>
       <c r="L24" t="n">
-        <v>194.9</v>
+        <v>134.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>27.03</v>
+        <v>18.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-112.85</v>
+        <v>-76.33</v>
       </c>
       <c r="L25" t="n">
-        <v>116.05</v>
+        <v>78.48999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-190.7</v>
+        <v>-128.22</v>
       </c>
       <c r="K26" t="n">
-        <v>181.21</v>
+        <v>121.84</v>
       </c>
       <c r="L26" t="n">
-        <v>263.06</v>
+        <v>176.87</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>132.4</v>
+        <v>85.62</v>
       </c>
       <c r="K27" t="n">
-        <v>368.69</v>
+        <v>238.43</v>
       </c>
       <c r="L27" t="n">
-        <v>391.74</v>
+        <v>253.34</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-9.609999999999999</v>
+        <v>-5.84</v>
       </c>
       <c r="K28" t="n">
-        <v>-318.17</v>
+        <v>-193.26</v>
       </c>
       <c r="L28" t="n">
-        <v>318.31</v>
+        <v>193.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>37.64</v>
+        <v>24.36</v>
       </c>
       <c r="K29" t="n">
-        <v>-71.33</v>
+        <v>-46.16</v>
       </c>
       <c r="L29" t="n">
-        <v>80.65000000000001</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>95.43000000000001</v>
+        <v>56.93</v>
       </c>
       <c r="K30" t="n">
-        <v>-35.99</v>
+        <v>-21.47</v>
       </c>
       <c r="L30" t="n">
-        <v>101.99</v>
+        <v>60.85</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-52.22</v>
+        <v>-31.58</v>
       </c>
       <c r="K31" t="n">
-        <v>53.52</v>
+        <v>32.37</v>
       </c>
       <c r="L31" t="n">
-        <v>74.78</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-8.31</v>
+        <v>-4.07</v>
       </c>
       <c r="K32" t="n">
-        <v>62.05</v>
+        <v>30.43</v>
       </c>
       <c r="L32" t="n">
-        <v>62.61</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>129.07</v>
+        <v>89.33</v>
       </c>
       <c r="K33" t="n">
-        <v>-61.87</v>
+        <v>-42.82</v>
       </c>
       <c r="L33" t="n">
-        <v>143.13</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-15.43</v>
+        <v>-10.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-73.78</v>
+        <v>-51.37</v>
       </c>
       <c r="L34" t="n">
-        <v>75.38</v>
+        <v>52.48</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>148.85</v>
+        <v>89.98</v>
       </c>
       <c r="K35" t="n">
-        <v>87.8</v>
+        <v>53.08</v>
       </c>
       <c r="L35" t="n">
-        <v>172.82</v>
+        <v>104.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>113.18</v>
+        <v>71.45</v>
       </c>
       <c r="K36" t="n">
-        <v>-13.73</v>
+        <v>-8.67</v>
       </c>
       <c r="L36" t="n">
-        <v>114.01</v>
+        <v>71.98</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>64.27</v>
+        <v>38.75</v>
       </c>
       <c r="K37" t="n">
-        <v>-86.5</v>
+        <v>-52.16</v>
       </c>
       <c r="L37" t="n">
-        <v>107.77</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-33.65</v>
+        <v>-24.08</v>
       </c>
       <c r="K38" t="n">
-        <v>188.93</v>
+        <v>135.23</v>
       </c>
       <c r="L38" t="n">
-        <v>191.91</v>
+        <v>137.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-117.53</v>
+        <v>-78.23</v>
       </c>
       <c r="K39" t="n">
-        <v>21.69</v>
+        <v>14.44</v>
       </c>
       <c r="L39" t="n">
-        <v>119.52</v>
+        <v>79.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-64.04000000000001</v>
+        <v>-48.03</v>
       </c>
       <c r="K40" t="n">
-        <v>-99.73999999999999</v>
+        <v>-74.81</v>
       </c>
       <c r="L40" t="n">
-        <v>118.53</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-415.46</v>
+        <v>-281.11</v>
       </c>
       <c r="K41" t="n">
-        <v>84.15000000000001</v>
+        <v>56.94</v>
       </c>
       <c r="L41" t="n">
-        <v>423.89</v>
+        <v>286.82</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>60.15</v>
+        <v>39.53</v>
       </c>
       <c r="K42" t="n">
-        <v>-257.05</v>
+        <v>-168.93</v>
       </c>
       <c r="L42" t="n">
-        <v>264</v>
+        <v>173.5</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-91.18000000000001</v>
+        <v>-54.21</v>
       </c>
       <c r="K43" t="n">
-        <v>190.92</v>
+        <v>113.51</v>
       </c>
       <c r="L43" t="n">
-        <v>211.58</v>
+        <v>125.8</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-81.16</v>
+        <v>-50.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-93.38</v>
+        <v>-57.92</v>
       </c>
       <c r="L44" t="n">
-        <v>123.72</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>112.28</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>56.87</v>
+        <v>32.79</v>
       </c>
       <c r="L45" t="n">
-        <v>125.86</v>
+        <v>72.56999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-102.77</v>
+        <v>-65.69</v>
       </c>
       <c r="K46" t="n">
-        <v>16.27</v>
+        <v>10.4</v>
       </c>
       <c r="L46" t="n">
-        <v>104.05</v>
+        <v>66.51000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>57.12</v>
+        <v>39.2</v>
       </c>
       <c r="K47" t="n">
-        <v>37.77</v>
+        <v>25.92</v>
       </c>
       <c r="L47" t="n">
-        <v>68.48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>35.24</v>
+        <v>22.21</v>
       </c>
       <c r="K48" t="n">
-        <v>-70.41</v>
+        <v>-44.38</v>
       </c>
       <c r="L48" t="n">
-        <v>78.73</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.57</v>
+        <v>-28.16</v>
       </c>
       <c r="K49" t="n">
-        <v>80.45999999999999</v>
+        <v>55.85</v>
       </c>
       <c r="L49" t="n">
-        <v>90.11</v>
+        <v>62.55</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>118.74</v>
+        <v>72.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-73.79000000000001</v>
+        <v>-45.2</v>
       </c>
       <c r="L50" t="n">
-        <v>139.8</v>
+        <v>85.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-72.48</v>
+        <v>-41.78</v>
       </c>
       <c r="K51" t="n">
-        <v>-134.26</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>152.57</v>
+        <v>87.95999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-71.02</v>
+        <v>-41.34</v>
       </c>
       <c r="K52" t="n">
-        <v>78.06999999999999</v>
+        <v>45.44</v>
       </c>
       <c r="L52" t="n">
-        <v>105.54</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>12.77</v>
+        <v>9.27</v>
       </c>
       <c r="K53" t="n">
-        <v>-111.27</v>
+        <v>-80.78</v>
       </c>
       <c r="L53" t="n">
-        <v>112</v>
+        <v>81.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>153.43</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>184.95</v>
+        <v>119.9</v>
       </c>
       <c r="L54" t="n">
-        <v>240.3</v>
+        <v>155.78</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-32.24</v>
+        <v>-19.82</v>
       </c>
       <c r="K55" t="n">
-        <v>232.8</v>
+        <v>143.16</v>
       </c>
       <c r="L55" t="n">
-        <v>235.02</v>
+        <v>144.53</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>290.83</v>
+        <v>176.97</v>
       </c>
       <c r="K56" t="n">
-        <v>-105.1</v>
+        <v>-63.95</v>
       </c>
       <c r="L56" t="n">
-        <v>309.24</v>
+        <v>188.18</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>298.9</v>
+        <v>184.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-80.58</v>
+        <v>-49.67</v>
       </c>
       <c r="L57" t="n">
-        <v>309.57</v>
+        <v>190.81</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>305.67</v>
+        <v>190.9</v>
       </c>
       <c r="K58" t="n">
-        <v>119.41</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>328.17</v>
+        <v>204.94</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-125.51</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>23.3</v>
+        <v>14.42</v>
       </c>
       <c r="L59" t="n">
-        <v>127.65</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>24.68</v>
+        <v>15.28</v>
       </c>
       <c r="K60" t="n">
-        <v>-133.1</v>
+        <v>-82.38</v>
       </c>
       <c r="L60" t="n">
-        <v>135.37</v>
+        <v>83.78</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.08</v>
+        <v>-18.41</v>
       </c>
       <c r="K61" t="n">
-        <v>-87.02</v>
+        <v>-55.09</v>
       </c>
       <c r="L61" t="n">
-        <v>91.75</v>
+        <v>58.09</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-42.8</v>
+        <v>-24.01</v>
       </c>
       <c r="K62" t="n">
-        <v>92.84</v>
+        <v>52.09</v>
       </c>
       <c r="L62" t="n">
-        <v>102.23</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-114.13</v>
+        <v>-70.94</v>
       </c>
       <c r="K63" t="n">
-        <v>-81.09999999999999</v>
+        <v>-50.41</v>
       </c>
       <c r="L63" t="n">
-        <v>140.01</v>
+        <v>87.03</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-108.59</v>
+        <v>-70.66</v>
       </c>
       <c r="K64" t="n">
-        <v>98.09</v>
+        <v>63.82</v>
       </c>
       <c r="L64" t="n">
-        <v>146.33</v>
+        <v>95.20999999999999</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-159.78</v>
+        <v>-93.23</v>
       </c>
       <c r="K65" t="n">
-        <v>77.45</v>
+        <v>45.2</v>
       </c>
       <c r="L65" t="n">
-        <v>177.56</v>
+        <v>103.61</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>62.91</v>
+        <v>38.64</v>
       </c>
       <c r="K66" t="n">
-        <v>89.52</v>
+        <v>54.98</v>
       </c>
       <c r="L66" t="n">
-        <v>109.41</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>186.55</v>
+        <v>108.07</v>
       </c>
       <c r="K67" t="n">
-        <v>-16.94</v>
+        <v>-9.81</v>
       </c>
       <c r="L67" t="n">
-        <v>187.32</v>
+        <v>108.51</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-7.09</v>
+        <v>-2.96</v>
       </c>
       <c r="K68" t="n">
-        <v>119.34</v>
+        <v>49.74</v>
       </c>
       <c r="L68" t="n">
-        <v>119.55</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>67.68000000000001</v>
+        <v>46.64</v>
       </c>
       <c r="K69" t="n">
-        <v>164.88</v>
+        <v>113.62</v>
       </c>
       <c r="L69" t="n">
-        <v>178.23</v>
+        <v>122.82</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>150.24</v>
+        <v>100.4</v>
       </c>
       <c r="K70" t="n">
-        <v>-70.36</v>
+        <v>-47.02</v>
       </c>
       <c r="L70" t="n">
-        <v>165.9</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>280.15</v>
+        <v>181.17</v>
       </c>
       <c r="K71" t="n">
-        <v>5.91</v>
+        <v>3.82</v>
       </c>
       <c r="L71" t="n">
-        <v>280.21</v>
+        <v>181.21</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-192.71</v>
+        <v>-122.68</v>
       </c>
       <c r="K72" t="n">
-        <v>58.57</v>
+        <v>37.29</v>
       </c>
       <c r="L72" t="n">
-        <v>201.42</v>
+        <v>128.22</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-181.37</v>
+        <v>-107.64</v>
       </c>
       <c r="K73" t="n">
-        <v>76.81999999999999</v>
+        <v>45.59</v>
       </c>
       <c r="L73" t="n">
-        <v>196.96</v>
+        <v>116.9</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>82.63</v>
+        <v>47.81</v>
       </c>
       <c r="K74" t="n">
-        <v>-82.65000000000001</v>
+        <v>-47.82</v>
       </c>
       <c r="L74" t="n">
-        <v>116.87</v>
+        <v>67.62</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-79.44</v>
+        <v>-43.33</v>
       </c>
       <c r="K75" t="n">
-        <v>48.63</v>
+        <v>26.52</v>
       </c>
       <c r="L75" t="n">
-        <v>93.14</v>
+        <v>50.8</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>67.06999999999999</v>
+        <v>40.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.46</v>
+        <v>-0.27</v>
       </c>
       <c r="L76" t="n">
-        <v>67.08</v>
+        <v>40.02</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-121.69</v>
+        <v>-78.59</v>
       </c>
       <c r="K77" t="n">
-        <v>-30.16</v>
+        <v>-19.48</v>
       </c>
       <c r="L77" t="n">
-        <v>125.38</v>
+        <v>80.97</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>29.77</v>
+        <v>16.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-70.01000000000001</v>
+        <v>-38.52</v>
       </c>
       <c r="L78" t="n">
-        <v>76.06999999999999</v>
+        <v>41.86</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-62.76</v>
+        <v>-41.91</v>
       </c>
       <c r="K79" t="n">
-        <v>77.19</v>
+        <v>51.54</v>
       </c>
       <c r="L79" t="n">
-        <v>99.48</v>
+        <v>66.43000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-52.47</v>
+        <v>-30.4</v>
       </c>
       <c r="K80" t="n">
-        <v>-254.54</v>
+        <v>-147.45</v>
       </c>
       <c r="L80" t="n">
-        <v>259.89</v>
+        <v>150.55</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-174.75</v>
+        <v>-107.04</v>
       </c>
       <c r="K81" t="n">
-        <v>-29.32</v>
+        <v>-17.96</v>
       </c>
       <c r="L81" t="n">
-        <v>177.19</v>
+        <v>108.54</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-57.4</v>
+        <v>-38.33</v>
       </c>
       <c r="K82" t="n">
-        <v>-121.17</v>
+        <v>-80.91</v>
       </c>
       <c r="L82" t="n">
-        <v>134.07</v>
+        <v>89.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>229.36</v>
+        <v>151.78</v>
       </c>
       <c r="K83" t="n">
-        <v>151.02</v>
+        <v>99.94</v>
       </c>
       <c r="L83" t="n">
-        <v>274.61</v>
+        <v>181.73</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>199.99</v>
+        <v>124.99</v>
       </c>
       <c r="K84" t="n">
-        <v>19.36</v>
+        <v>12.1</v>
       </c>
       <c r="L84" t="n">
-        <v>200.92</v>
+        <v>125.58</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-52.19</v>
+        <v>-31.7</v>
       </c>
       <c r="K85" t="n">
-        <v>265.63</v>
+        <v>161.33</v>
       </c>
       <c r="L85" t="n">
-        <v>270.71</v>
+        <v>164.41</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-160.82</v>
+        <v>-107.45</v>
       </c>
       <c r="K86" t="n">
-        <v>-278.01</v>
+        <v>-185.75</v>
       </c>
       <c r="L86" t="n">
-        <v>321.18</v>
+        <v>214.59</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-209.37</v>
+        <v>-140.47</v>
       </c>
       <c r="K87" t="n">
-        <v>-135.05</v>
+        <v>-90.61</v>
       </c>
       <c r="L87" t="n">
-        <v>249.15</v>
+        <v>167.16</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>181.67</v>
+        <v>120.62</v>
       </c>
       <c r="K88" t="n">
-        <v>180.67</v>
+        <v>119.96</v>
       </c>
       <c r="L88" t="n">
-        <v>256.21</v>
+        <v>170.12</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>14.85</v>
+        <v>16.24</v>
       </c>
       <c r="K14" t="n">
-        <v>-20.82</v>
+        <v>-22.76</v>
       </c>
       <c r="L14" t="n">
-        <v>25.58</v>
+        <v>27.96</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-29.18</v>
+        <v>-30.57</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.13</v>
+        <v>-14.8</v>
       </c>
       <c r="L15" t="n">
-        <v>32.42</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>28.7</v>
+        <v>29.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.56</v>
+        <v>-26.59</v>
       </c>
       <c r="L16" t="n">
-        <v>38.43</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>52.74</v>
+        <v>51.68</v>
       </c>
       <c r="K17" t="n">
-        <v>61.26</v>
+        <v>60.02</v>
       </c>
       <c r="L17" t="n">
-        <v>80.84</v>
+        <v>79.20999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.58</v>
+        <v>-13.3</v>
       </c>
       <c r="L18" t="n">
-        <v>14.76</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.24</v>
+        <v>-32.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-119.4</v>
+        <v>-112.48</v>
       </c>
       <c r="L19" t="n">
-        <v>124.22</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>71.64</v>
+        <v>70.70999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>82.84</v>
+        <v>81.77</v>
       </c>
       <c r="L20" t="n">
-        <v>109.52</v>
+        <v>108.1</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-88.34999999999999</v>
+        <v>-88.13</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.95</v>
+        <v>-49.83</v>
       </c>
       <c r="L21" t="n">
-        <v>101.49</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-71.56999999999999</v>
+        <v>-72.59999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-48.21</v>
+        <v>-48.91</v>
       </c>
       <c r="L22" t="n">
-        <v>86.3</v>
+        <v>87.54000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-85.45</v>
+        <v>-85.22</v>
       </c>
       <c r="K23" t="n">
-        <v>-82.34999999999999</v>
+        <v>-82.12</v>
       </c>
       <c r="L23" t="n">
-        <v>118.68</v>
+        <v>118.35</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-133.34</v>
+        <v>-132.68</v>
       </c>
       <c r="K24" t="n">
-        <v>13.51</v>
+        <v>13.44</v>
       </c>
       <c r="L24" t="n">
-        <v>134.02</v>
+        <v>133.36</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>18.28</v>
+        <v>19.48</v>
       </c>
       <c r="K25" t="n">
-        <v>-76.33</v>
+        <v>-81.34999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>78.48999999999999</v>
+        <v>83.65000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-128.22</v>
+        <v>-129.12</v>
       </c>
       <c r="K26" t="n">
-        <v>121.84</v>
+        <v>122.69</v>
       </c>
       <c r="L26" t="n">
-        <v>176.87</v>
+        <v>178.11</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>85.62</v>
+        <v>82.97</v>
       </c>
       <c r="K27" t="n">
-        <v>238.43</v>
+        <v>231.05</v>
       </c>
       <c r="L27" t="n">
-        <v>253.34</v>
+        <v>245.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.84</v>
+        <v>-5.86</v>
       </c>
       <c r="K28" t="n">
-        <v>-193.26</v>
+        <v>-194.04</v>
       </c>
       <c r="L28" t="n">
-        <v>193.35</v>
+        <v>194.13</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.36</v>
+        <v>24.26</v>
       </c>
       <c r="K29" t="n">
-        <v>-46.16</v>
+        <v>-45.98</v>
       </c>
       <c r="L29" t="n">
-        <v>52.2</v>
+        <v>51.99</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>56.93</v>
+        <v>56.75</v>
       </c>
       <c r="K30" t="n">
-        <v>-21.47</v>
+        <v>-21.41</v>
       </c>
       <c r="L30" t="n">
-        <v>60.85</v>
+        <v>60.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.58</v>
+        <v>-32.28</v>
       </c>
       <c r="K31" t="n">
-        <v>32.37</v>
+        <v>33.09</v>
       </c>
       <c r="L31" t="n">
-        <v>45.23</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.07</v>
+        <v>-3.98</v>
       </c>
       <c r="K32" t="n">
-        <v>30.43</v>
+        <v>29.71</v>
       </c>
       <c r="L32" t="n">
-        <v>30.7</v>
+        <v>29.97</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>89.33</v>
+        <v>86.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-42.82</v>
+        <v>-41.28</v>
       </c>
       <c r="L33" t="n">
-        <v>99.06999999999999</v>
+        <v>95.5</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-10.74</v>
+        <v>-11.19</v>
       </c>
       <c r="K34" t="n">
-        <v>-51.37</v>
+        <v>-53.49</v>
       </c>
       <c r="L34" t="n">
-        <v>52.48</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>89.98</v>
+        <v>89.12</v>
       </c>
       <c r="K35" t="n">
-        <v>53.08</v>
+        <v>52.57</v>
       </c>
       <c r="L35" t="n">
-        <v>104.47</v>
+        <v>103.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>71.45</v>
+        <v>73.88</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.67</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>71.98</v>
+        <v>74.42</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>38.75</v>
+        <v>41.33</v>
       </c>
       <c r="K37" t="n">
-        <v>-52.16</v>
+        <v>-55.63</v>
       </c>
       <c r="L37" t="n">
-        <v>64.98</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-24.08</v>
+        <v>-23.94</v>
       </c>
       <c r="K38" t="n">
-        <v>135.23</v>
+        <v>134.44</v>
       </c>
       <c r="L38" t="n">
-        <v>137.36</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-78.23</v>
+        <v>-85.12</v>
       </c>
       <c r="K39" t="n">
-        <v>14.44</v>
+        <v>15.71</v>
       </c>
       <c r="L39" t="n">
-        <v>79.55</v>
+        <v>86.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-48.03</v>
+        <v>-49.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-74.81</v>
+        <v>-77.23999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>88.90000000000001</v>
+        <v>91.79000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-281.11</v>
+        <v>-269.95</v>
       </c>
       <c r="K41" t="n">
-        <v>56.94</v>
+        <v>54.68</v>
       </c>
       <c r="L41" t="n">
-        <v>286.82</v>
+        <v>275.43</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>39.53</v>
+        <v>40.05</v>
       </c>
       <c r="K42" t="n">
-        <v>-168.93</v>
+        <v>-171.13</v>
       </c>
       <c r="L42" t="n">
-        <v>173.5</v>
+        <v>175.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-54.21</v>
+        <v>-57.7</v>
       </c>
       <c r="K43" t="n">
-        <v>113.51</v>
+        <v>120.81</v>
       </c>
       <c r="L43" t="n">
-        <v>125.8</v>
+        <v>133.88</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-50.34</v>
+        <v>-48.49</v>
       </c>
       <c r="K44" t="n">
-        <v>-57.92</v>
+        <v>-55.79</v>
       </c>
       <c r="L44" t="n">
-        <v>76.73999999999999</v>
+        <v>73.92</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>64.73999999999999</v>
+        <v>63.62</v>
       </c>
       <c r="K45" t="n">
-        <v>32.79</v>
+        <v>32.22</v>
       </c>
       <c r="L45" t="n">
-        <v>72.56999999999999</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-65.69</v>
+        <v>-63.85</v>
       </c>
       <c r="K46" t="n">
-        <v>10.4</v>
+        <v>10.11</v>
       </c>
       <c r="L46" t="n">
-        <v>66.51000000000001</v>
+        <v>64.65000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>39.2</v>
+        <v>40.66</v>
       </c>
       <c r="K47" t="n">
-        <v>25.92</v>
+        <v>26.88</v>
       </c>
       <c r="L47" t="n">
-        <v>47</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>22.21</v>
+        <v>23.36</v>
       </c>
       <c r="K48" t="n">
-        <v>-44.38</v>
+        <v>-46.68</v>
       </c>
       <c r="L48" t="n">
-        <v>49.63</v>
+        <v>52.2</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.16</v>
+        <v>-28.21</v>
       </c>
       <c r="K49" t="n">
-        <v>55.85</v>
+        <v>55.95</v>
       </c>
       <c r="L49" t="n">
-        <v>62.55</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>72.73</v>
+        <v>73.95</v>
       </c>
       <c r="K50" t="n">
-        <v>-45.2</v>
+        <v>-45.96</v>
       </c>
       <c r="L50" t="n">
-        <v>85.63</v>
+        <v>87.06</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-41.78</v>
+        <v>-42.73</v>
       </c>
       <c r="K51" t="n">
-        <v>-77.40000000000001</v>
+        <v>-79.15000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>87.95999999999999</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-41.34</v>
+        <v>-44.37</v>
       </c>
       <c r="K52" t="n">
-        <v>45.44</v>
+        <v>48.77</v>
       </c>
       <c r="L52" t="n">
-        <v>61.43</v>
+        <v>65.93000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>9.27</v>
+        <v>9.69</v>
       </c>
       <c r="K53" t="n">
-        <v>-80.78</v>
+        <v>-84.41</v>
       </c>
       <c r="L53" t="n">
-        <v>81.31</v>
+        <v>84.97</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>99.45999999999999</v>
+        <v>97.45</v>
       </c>
       <c r="K54" t="n">
-        <v>119.9</v>
+        <v>117.48</v>
       </c>
       <c r="L54" t="n">
-        <v>155.78</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.82</v>
+        <v>-19.6</v>
       </c>
       <c r="K55" t="n">
-        <v>143.16</v>
+        <v>141.57</v>
       </c>
       <c r="L55" t="n">
-        <v>144.53</v>
+        <v>142.92</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>176.97</v>
+        <v>177.49</v>
       </c>
       <c r="K56" t="n">
-        <v>-63.95</v>
+        <v>-64.14</v>
       </c>
       <c r="L56" t="n">
-        <v>188.18</v>
+        <v>188.73</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>184.24</v>
+        <v>183.8</v>
       </c>
       <c r="K57" t="n">
-        <v>-49.67</v>
+        <v>-49.55</v>
       </c>
       <c r="L57" t="n">
-        <v>190.81</v>
+        <v>190.36</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>190.9</v>
+        <v>187.6</v>
       </c>
       <c r="K58" t="n">
-        <v>74.56999999999999</v>
+        <v>73.28</v>
       </c>
       <c r="L58" t="n">
-        <v>204.94</v>
+        <v>201.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-77.68000000000001</v>
+        <v>-74.73999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>14.42</v>
+        <v>13.87</v>
       </c>
       <c r="L59" t="n">
-        <v>79.01000000000001</v>
+        <v>76.02</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>15.28</v>
+        <v>14.62</v>
       </c>
       <c r="K60" t="n">
-        <v>-82.38</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>83.78</v>
+        <v>80.17</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.41</v>
+        <v>-18.22</v>
       </c>
       <c r="K61" t="n">
-        <v>-55.09</v>
+        <v>-54.54</v>
       </c>
       <c r="L61" t="n">
-        <v>58.09</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-24.01</v>
+        <v>-25.02</v>
       </c>
       <c r="K62" t="n">
-        <v>52.09</v>
+        <v>54.27</v>
       </c>
       <c r="L62" t="n">
-        <v>57.36</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-70.94</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-50.41</v>
+        <v>-49.18</v>
       </c>
       <c r="L63" t="n">
-        <v>87.03</v>
+        <v>84.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-70.66</v>
+        <v>-68.55</v>
       </c>
       <c r="K64" t="n">
-        <v>63.82</v>
+        <v>61.92</v>
       </c>
       <c r="L64" t="n">
-        <v>95.20999999999999</v>
+        <v>92.38</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-93.23</v>
+        <v>-92.53</v>
       </c>
       <c r="K65" t="n">
-        <v>45.2</v>
+        <v>44.86</v>
       </c>
       <c r="L65" t="n">
-        <v>103.61</v>
+        <v>102.83</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>38.64</v>
+        <v>41.17</v>
       </c>
       <c r="K66" t="n">
-        <v>54.98</v>
+        <v>58.58</v>
       </c>
       <c r="L66" t="n">
-        <v>67.2</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>108.07</v>
+        <v>107.27</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.81</v>
+        <v>-9.74</v>
       </c>
       <c r="L67" t="n">
-        <v>108.51</v>
+        <v>107.71</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.96</v>
+        <v>-2.89</v>
       </c>
       <c r="K68" t="n">
-        <v>49.74</v>
+        <v>48.63</v>
       </c>
       <c r="L68" t="n">
-        <v>49.83</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>46.64</v>
+        <v>46.4</v>
       </c>
       <c r="K69" t="n">
-        <v>113.62</v>
+        <v>113.03</v>
       </c>
       <c r="L69" t="n">
-        <v>122.82</v>
+        <v>122.19</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>100.4</v>
+        <v>102.91</v>
       </c>
       <c r="K70" t="n">
-        <v>-47.02</v>
+        <v>-48.2</v>
       </c>
       <c r="L70" t="n">
-        <v>110.86</v>
+        <v>113.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>181.17</v>
+        <v>181.25</v>
       </c>
       <c r="K71" t="n">
         <v>3.82</v>
       </c>
       <c r="L71" t="n">
-        <v>181.21</v>
+        <v>181.29</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-122.68</v>
+        <v>-129.99</v>
       </c>
       <c r="K72" t="n">
-        <v>37.29</v>
+        <v>39.51</v>
       </c>
       <c r="L72" t="n">
-        <v>128.22</v>
+        <v>135.86</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-107.64</v>
+        <v>-115.6</v>
       </c>
       <c r="K73" t="n">
-        <v>45.59</v>
+        <v>48.96</v>
       </c>
       <c r="L73" t="n">
-        <v>116.9</v>
+        <v>125.54</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>47.81</v>
+        <v>47.11</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.82</v>
+        <v>-47.12</v>
       </c>
       <c r="L74" t="n">
-        <v>67.62</v>
+        <v>66.63</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-43.33</v>
+        <v>-45.17</v>
       </c>
       <c r="K75" t="n">
-        <v>26.52</v>
+        <v>27.65</v>
       </c>
       <c r="L75" t="n">
-        <v>50.8</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>40.02</v>
+        <v>42.02</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="L76" t="n">
-        <v>40.02</v>
+        <v>42.02</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-78.59</v>
+        <v>-76.73</v>
       </c>
       <c r="K77" t="n">
-        <v>-19.48</v>
+        <v>-19.01</v>
       </c>
       <c r="L77" t="n">
-        <v>80.97</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>16.38</v>
+        <v>17.71</v>
       </c>
       <c r="K78" t="n">
-        <v>-38.52</v>
+        <v>-41.65</v>
       </c>
       <c r="L78" t="n">
-        <v>41.86</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.91</v>
+        <v>-42.21</v>
       </c>
       <c r="K79" t="n">
-        <v>51.54</v>
+        <v>51.92</v>
       </c>
       <c r="L79" t="n">
-        <v>66.43000000000001</v>
+        <v>66.92</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-30.4</v>
+        <v>-28.96</v>
       </c>
       <c r="K80" t="n">
-        <v>-147.45</v>
+        <v>-140.49</v>
       </c>
       <c r="L80" t="n">
-        <v>150.55</v>
+        <v>143.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-107.04</v>
+        <v>-105.38</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.96</v>
+        <v>-17.68</v>
       </c>
       <c r="L81" t="n">
-        <v>108.54</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-38.33</v>
+        <v>-38.73</v>
       </c>
       <c r="K82" t="n">
-        <v>-80.91</v>
+        <v>-81.75</v>
       </c>
       <c r="L82" t="n">
-        <v>89.53</v>
+        <v>90.45999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>151.78</v>
+        <v>145.61</v>
       </c>
       <c r="K83" t="n">
-        <v>99.94</v>
+        <v>95.87</v>
       </c>
       <c r="L83" t="n">
-        <v>181.73</v>
+        <v>174.34</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>124.99</v>
+        <v>127.31</v>
       </c>
       <c r="K84" t="n">
-        <v>12.1</v>
+        <v>12.33</v>
       </c>
       <c r="L84" t="n">
-        <v>125.58</v>
+        <v>127.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.7</v>
+        <v>-31.06</v>
       </c>
       <c r="K85" t="n">
-        <v>161.33</v>
+        <v>158.1</v>
       </c>
       <c r="L85" t="n">
-        <v>164.41</v>
+        <v>161.12</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-107.45</v>
+        <v>-105.6</v>
       </c>
       <c r="K86" t="n">
-        <v>-185.75</v>
+        <v>-182.54</v>
       </c>
       <c r="L86" t="n">
-        <v>214.59</v>
+        <v>210.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-140.47</v>
+        <v>-141.66</v>
       </c>
       <c r="K87" t="n">
-        <v>-90.61</v>
+        <v>-91.38</v>
       </c>
       <c r="L87" t="n">
-        <v>167.16</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>120.62</v>
+        <v>121.52</v>
       </c>
       <c r="K88" t="n">
-        <v>119.96</v>
+        <v>120.85</v>
       </c>
       <c r="L88" t="n">
-        <v>170.12</v>
+        <v>171.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>16.24</v>
+        <v>17.82</v>
       </c>
       <c r="K14" t="n">
-        <v>-22.76</v>
+        <v>-24.98</v>
       </c>
       <c r="L14" t="n">
-        <v>27.96</v>
+        <v>30.68</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-30.57</v>
+        <v>-32.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-14.8</v>
+        <v>-15.57</v>
       </c>
       <c r="L15" t="n">
-        <v>33.96</v>
+        <v>35.73</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>29.85</v>
+        <v>31.16</v>
       </c>
       <c r="K16" t="n">
-        <v>-26.59</v>
+        <v>-27.76</v>
       </c>
       <c r="L16" t="n">
-        <v>39.97</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>51.68</v>
+        <v>50.46</v>
       </c>
       <c r="K17" t="n">
-        <v>60.02</v>
+        <v>58.61</v>
       </c>
       <c r="L17" t="n">
-        <v>79.20999999999999</v>
+        <v>77.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>5.67</v>
+        <v>6.13</v>
       </c>
       <c r="K18" t="n">
-        <v>-13.3</v>
+        <v>-14.38</v>
       </c>
       <c r="L18" t="n">
-        <v>14.46</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-32.25</v>
+        <v>-29.98</v>
       </c>
       <c r="K19" t="n">
-        <v>-112.48</v>
+        <v>-104.58</v>
       </c>
       <c r="L19" t="n">
-        <v>117.02</v>
+        <v>108.79</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>70.70999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>81.77</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>108.1</v>
+        <v>106.47</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-88.13</v>
+        <v>-87.89</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.83</v>
+        <v>-49.69</v>
       </c>
       <c r="L21" t="n">
-        <v>101.25</v>
+        <v>100.97</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-72.59999999999999</v>
+        <v>-73.78</v>
       </c>
       <c r="K22" t="n">
-        <v>-48.91</v>
+        <v>-49.7</v>
       </c>
       <c r="L22" t="n">
-        <v>87.54000000000001</v>
+        <v>88.95999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-85.22</v>
+        <v>-84.94</v>
       </c>
       <c r="K23" t="n">
-        <v>-82.12</v>
+        <v>-81.86</v>
       </c>
       <c r="L23" t="n">
-        <v>118.35</v>
+        <v>117.97</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-132.68</v>
+        <v>-131.92</v>
       </c>
       <c r="K24" t="n">
-        <v>13.44</v>
+        <v>13.36</v>
       </c>
       <c r="L24" t="n">
-        <v>133.36</v>
+        <v>132.59</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>19.48</v>
+        <v>20.86</v>
       </c>
       <c r="K25" t="n">
-        <v>-81.34999999999999</v>
+        <v>-87.08</v>
       </c>
       <c r="L25" t="n">
-        <v>83.65000000000001</v>
+        <v>89.54000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-129.12</v>
+        <v>-130.15</v>
       </c>
       <c r="K26" t="n">
-        <v>122.69</v>
+        <v>123.67</v>
       </c>
       <c r="L26" t="n">
-        <v>178.11</v>
+        <v>179.54</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>82.97</v>
+        <v>79.95</v>
       </c>
       <c r="K27" t="n">
-        <v>231.05</v>
+        <v>222.63</v>
       </c>
       <c r="L27" t="n">
-        <v>245.5</v>
+        <v>236.55</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.86</v>
+        <v>-5.89</v>
       </c>
       <c r="K28" t="n">
-        <v>-194.04</v>
+        <v>-194.93</v>
       </c>
       <c r="L28" t="n">
-        <v>194.13</v>
+        <v>195.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.26</v>
+        <v>24.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-45.98</v>
+        <v>-45.76</v>
       </c>
       <c r="L29" t="n">
-        <v>51.99</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>56.75</v>
+        <v>56.55</v>
       </c>
       <c r="K30" t="n">
-        <v>-21.41</v>
+        <v>-21.33</v>
       </c>
       <c r="L30" t="n">
-        <v>60.66</v>
+        <v>60.44</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-32.28</v>
+        <v>-33.08</v>
       </c>
       <c r="K31" t="n">
-        <v>33.09</v>
+        <v>33.91</v>
       </c>
       <c r="L31" t="n">
-        <v>46.23</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-3.98</v>
+        <v>-4.36</v>
       </c>
       <c r="K32" t="n">
-        <v>29.71</v>
+        <v>32.55</v>
       </c>
       <c r="L32" t="n">
-        <v>29.97</v>
+        <v>32.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>86.12</v>
+        <v>82.44</v>
       </c>
       <c r="K33" t="n">
-        <v>-41.28</v>
+        <v>-39.52</v>
       </c>
       <c r="L33" t="n">
-        <v>95.5</v>
+        <v>91.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.19</v>
+        <v>-11.69</v>
       </c>
       <c r="K34" t="n">
-        <v>-53.49</v>
+        <v>-55.91</v>
       </c>
       <c r="L34" t="n">
-        <v>54.64</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>89.12</v>
+        <v>88.14</v>
       </c>
       <c r="K35" t="n">
-        <v>52.57</v>
+        <v>51.99</v>
       </c>
       <c r="L35" t="n">
-        <v>103.47</v>
+        <v>102.33</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>73.88</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-8.960000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>74.42</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>41.33</v>
+        <v>44.28</v>
       </c>
       <c r="K37" t="n">
-        <v>-55.63</v>
+        <v>-59.6</v>
       </c>
       <c r="L37" t="n">
-        <v>69.3</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-23.94</v>
+        <v>-23.78</v>
       </c>
       <c r="K38" t="n">
-        <v>134.44</v>
+        <v>133.53</v>
       </c>
       <c r="L38" t="n">
-        <v>136.55</v>
+        <v>135.63</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-85.12</v>
+        <v>-92.98999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>15.71</v>
+        <v>17.16</v>
       </c>
       <c r="L39" t="n">
-        <v>86.56</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-49.59</v>
+        <v>-51.38</v>
       </c>
       <c r="K40" t="n">
-        <v>-77.23999999999999</v>
+        <v>-80.03</v>
       </c>
       <c r="L40" t="n">
-        <v>91.79000000000001</v>
+        <v>95.09999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-269.95</v>
+        <v>-257.2</v>
       </c>
       <c r="K41" t="n">
-        <v>54.68</v>
+        <v>52.1</v>
       </c>
       <c r="L41" t="n">
-        <v>275.43</v>
+        <v>262.42</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>40.05</v>
+        <v>40.63</v>
       </c>
       <c r="K42" t="n">
-        <v>-171.13</v>
+        <v>-173.63</v>
       </c>
       <c r="L42" t="n">
-        <v>175.75</v>
+        <v>178.32</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-57.7</v>
+        <v>-61.68</v>
       </c>
       <c r="K43" t="n">
-        <v>120.81</v>
+        <v>129.16</v>
       </c>
       <c r="L43" t="n">
-        <v>133.88</v>
+        <v>143.13</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-48.49</v>
+        <v>-46.37</v>
       </c>
       <c r="K44" t="n">
-        <v>-55.79</v>
+        <v>-53.35</v>
       </c>
       <c r="L44" t="n">
-        <v>73.92</v>
+        <v>70.68000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>63.62</v>
+        <v>62.34</v>
       </c>
       <c r="K45" t="n">
-        <v>32.22</v>
+        <v>31.57</v>
       </c>
       <c r="L45" t="n">
-        <v>71.31999999999999</v>
+        <v>69.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-63.85</v>
+        <v>-61.75</v>
       </c>
       <c r="K46" t="n">
-        <v>10.11</v>
+        <v>9.77</v>
       </c>
       <c r="L46" t="n">
-        <v>64.65000000000001</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>40.66</v>
+        <v>42.32</v>
       </c>
       <c r="K47" t="n">
-        <v>26.88</v>
+        <v>27.98</v>
       </c>
       <c r="L47" t="n">
-        <v>48.74</v>
+        <v>50.74</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>23.36</v>
+        <v>24.68</v>
       </c>
       <c r="K48" t="n">
-        <v>-46.68</v>
+        <v>-49.31</v>
       </c>
       <c r="L48" t="n">
-        <v>52.2</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.21</v>
+        <v>-28.26</v>
       </c>
       <c r="K49" t="n">
-        <v>55.95</v>
+        <v>56.05</v>
       </c>
       <c r="L49" t="n">
-        <v>62.65</v>
+        <v>62.77</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>73.95</v>
+        <v>75.34</v>
       </c>
       <c r="K50" t="n">
-        <v>-45.96</v>
+        <v>-46.82</v>
       </c>
       <c r="L50" t="n">
-        <v>87.06</v>
+        <v>88.7</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-42.73</v>
+        <v>-43.81</v>
       </c>
       <c r="K51" t="n">
-        <v>-79.15000000000001</v>
+        <v>-81.16</v>
       </c>
       <c r="L51" t="n">
-        <v>89.95</v>
+        <v>92.23</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-44.37</v>
+        <v>-47.83</v>
       </c>
       <c r="K52" t="n">
-        <v>48.77</v>
+        <v>52.58</v>
       </c>
       <c r="L52" t="n">
-        <v>65.93000000000001</v>
+        <v>71.08</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>9.69</v>
+        <v>10.17</v>
       </c>
       <c r="K53" t="n">
-        <v>-84.41</v>
+        <v>-88.56999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>84.97</v>
+        <v>89.15000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>97.45</v>
+        <v>95.16</v>
       </c>
       <c r="K54" t="n">
-        <v>117.48</v>
+        <v>114.71</v>
       </c>
       <c r="L54" t="n">
-        <v>152.64</v>
+        <v>149.05</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.6</v>
+        <v>-19.35</v>
       </c>
       <c r="K55" t="n">
-        <v>141.57</v>
+        <v>139.75</v>
       </c>
       <c r="L55" t="n">
-        <v>142.92</v>
+        <v>141.08</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>177.49</v>
+        <v>178.09</v>
       </c>
       <c r="K56" t="n">
-        <v>-64.14</v>
+        <v>-64.36</v>
       </c>
       <c r="L56" t="n">
-        <v>188.73</v>
+        <v>189.36</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>183.8</v>
+        <v>183.29</v>
       </c>
       <c r="K57" t="n">
-        <v>-49.55</v>
+        <v>-49.41</v>
       </c>
       <c r="L57" t="n">
-        <v>190.36</v>
+        <v>189.84</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>187.6</v>
+        <v>183.82</v>
       </c>
       <c r="K58" t="n">
-        <v>73.28</v>
+        <v>71.81</v>
       </c>
       <c r="L58" t="n">
-        <v>201.4</v>
+        <v>197.35</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-74.73999999999999</v>
+        <v>-71.38</v>
       </c>
       <c r="K59" t="n">
-        <v>13.87</v>
+        <v>13.25</v>
       </c>
       <c r="L59" t="n">
-        <v>76.02</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>14.62</v>
+        <v>13.86</v>
       </c>
       <c r="K60" t="n">
-        <v>-78.81999999999999</v>
+        <v>-74.76000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>80.17</v>
+        <v>76.03</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.22</v>
+        <v>-18.01</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.54</v>
+        <v>-53.9</v>
       </c>
       <c r="L61" t="n">
-        <v>57.5</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-25.02</v>
+        <v>-26.16</v>
       </c>
       <c r="K62" t="n">
-        <v>54.27</v>
+        <v>56.76</v>
       </c>
       <c r="L62" t="n">
-        <v>59.76</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-69.20999999999999</v>
+        <v>-67.23999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-49.18</v>
+        <v>-47.78</v>
       </c>
       <c r="L63" t="n">
-        <v>84.91</v>
+        <v>82.48999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-68.55</v>
+        <v>-66.15000000000001</v>
       </c>
       <c r="K64" t="n">
-        <v>61.92</v>
+        <v>59.75</v>
       </c>
       <c r="L64" t="n">
-        <v>92.38</v>
+        <v>89.14</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-92.53</v>
+        <v>-91.73</v>
       </c>
       <c r="K65" t="n">
-        <v>44.86</v>
+        <v>44.47</v>
       </c>
       <c r="L65" t="n">
-        <v>102.83</v>
+        <v>101.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>41.17</v>
+        <v>44.06</v>
       </c>
       <c r="K66" t="n">
-        <v>58.58</v>
+        <v>62.69</v>
       </c>
       <c r="L66" t="n">
-        <v>71.59999999999999</v>
+        <v>76.62</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>107.27</v>
+        <v>106.35</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.74</v>
+        <v>-9.66</v>
       </c>
       <c r="L67" t="n">
-        <v>107.71</v>
+        <v>106.79</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.89</v>
+        <v>-3.15</v>
       </c>
       <c r="K68" t="n">
-        <v>48.63</v>
+        <v>53.02</v>
       </c>
       <c r="L68" t="n">
-        <v>48.72</v>
+        <v>53.11</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>46.4</v>
+        <v>46.12</v>
       </c>
       <c r="K69" t="n">
-        <v>113.03</v>
+        <v>112.36</v>
       </c>
       <c r="L69" t="n">
-        <v>122.19</v>
+        <v>121.46</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>102.91</v>
+        <v>105.79</v>
       </c>
       <c r="K70" t="n">
-        <v>-48.2</v>
+        <v>-49.55</v>
       </c>
       <c r="L70" t="n">
-        <v>113.64</v>
+        <v>116.82</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>181.25</v>
+        <v>181.33</v>
       </c>
       <c r="K71" t="n">
         <v>3.82</v>
       </c>
       <c r="L71" t="n">
-        <v>181.29</v>
+        <v>181.37</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-129.99</v>
+        <v>-138.33</v>
       </c>
       <c r="K72" t="n">
-        <v>39.51</v>
+        <v>42.04</v>
       </c>
       <c r="L72" t="n">
-        <v>135.86</v>
+        <v>144.58</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-115.6</v>
+        <v>-124.69</v>
       </c>
       <c r="K73" t="n">
-        <v>48.96</v>
+        <v>52.81</v>
       </c>
       <c r="L73" t="n">
-        <v>125.54</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>47.11</v>
+        <v>46.32</v>
       </c>
       <c r="K74" t="n">
-        <v>-47.12</v>
+        <v>-46.33</v>
       </c>
       <c r="L74" t="n">
-        <v>66.63</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-45.17</v>
+        <v>-47.27</v>
       </c>
       <c r="K75" t="n">
-        <v>27.65</v>
+        <v>28.93</v>
       </c>
       <c r="L75" t="n">
-        <v>52.96</v>
+        <v>55.42</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>42.02</v>
+        <v>44.31</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="L76" t="n">
-        <v>42.02</v>
+        <v>44.31</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-76.73</v>
+        <v>-74.59999999999999</v>
       </c>
       <c r="K77" t="n">
-        <v>-19.01</v>
+        <v>-18.49</v>
       </c>
       <c r="L77" t="n">
-        <v>79.05</v>
+        <v>76.86</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>17.71</v>
+        <v>19.24</v>
       </c>
       <c r="K78" t="n">
-        <v>-41.65</v>
+        <v>-45.24</v>
       </c>
       <c r="L78" t="n">
-        <v>45.26</v>
+        <v>49.16</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.21</v>
+        <v>-42.57</v>
       </c>
       <c r="K79" t="n">
-        <v>51.92</v>
+        <v>52.35</v>
       </c>
       <c r="L79" t="n">
-        <v>66.92</v>
+        <v>67.47</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-28.96</v>
+        <v>-27.32</v>
       </c>
       <c r="K80" t="n">
-        <v>-140.49</v>
+        <v>-132.54</v>
       </c>
       <c r="L80" t="n">
-        <v>143.45</v>
+        <v>135.33</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-105.38</v>
+        <v>-103.48</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.68</v>
+        <v>-17.36</v>
       </c>
       <c r="L81" t="n">
-        <v>106.85</v>
+        <v>104.93</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-38.73</v>
+        <v>-39.18</v>
       </c>
       <c r="K82" t="n">
-        <v>-81.75</v>
+        <v>-82.70999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>90.45999999999999</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>145.61</v>
+        <v>138.55</v>
       </c>
       <c r="K83" t="n">
-        <v>95.87</v>
+        <v>91.23</v>
       </c>
       <c r="L83" t="n">
-        <v>174.34</v>
+        <v>165.89</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>127.31</v>
+        <v>129.95</v>
       </c>
       <c r="K84" t="n">
-        <v>12.33</v>
+        <v>12.58</v>
       </c>
       <c r="L84" t="n">
-        <v>127.9</v>
+        <v>130.56</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.06</v>
+        <v>-30.34</v>
       </c>
       <c r="K85" t="n">
-        <v>158.1</v>
+        <v>154.4</v>
       </c>
       <c r="L85" t="n">
-        <v>161.12</v>
+        <v>157.36</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-105.6</v>
+        <v>-103.48</v>
       </c>
       <c r="K86" t="n">
-        <v>-182.54</v>
+        <v>-178.88</v>
       </c>
       <c r="L86" t="n">
-        <v>210.88</v>
+        <v>206.65</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-141.66</v>
+        <v>-143.02</v>
       </c>
       <c r="K87" t="n">
-        <v>-91.38</v>
+        <v>-92.25</v>
       </c>
       <c r="L87" t="n">
-        <v>168.58</v>
+        <v>170.19</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>121.52</v>
+        <v>122.54</v>
       </c>
       <c r="K88" t="n">
-        <v>120.85</v>
+        <v>121.86</v>
       </c>
       <c r="L88" t="n">
-        <v>171.38</v>
+        <v>172.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.95</v>
+        <v>2.41</v>
       </c>
       <c r="F14" t="n">
-        <v>7.74</v>
+        <v>8.85</v>
       </c>
       <c r="G14" t="n">
-        <v>308.7</v>
+        <v>326.5</v>
       </c>
       <c r="H14" t="n">
-        <v>49.4</v>
+        <v>55.9</v>
       </c>
       <c r="I14" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>17.82</v>
+        <v>45.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.98</v>
+        <v>-40.25</v>
       </c>
       <c r="L14" t="n">
-        <v>30.68</v>
+        <v>61.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:02:03</t>
+          <t>05:01:25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="F15" t="n">
-        <v>7.41</v>
+        <v>4.22</v>
       </c>
       <c r="G15" t="n">
-        <v>309.3</v>
+        <v>314.3</v>
       </c>
       <c r="H15" t="n">
-        <v>49.4</v>
+        <v>46.1</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-32.16</v>
+        <v>42.63</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.57</v>
+        <v>49.61</v>
       </c>
       <c r="L15" t="n">
-        <v>35.73</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:03:15</t>
+          <t>05:03:41</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="F16" t="n">
-        <v>8.48</v>
+        <v>6.73</v>
       </c>
       <c r="G16" t="n">
-        <v>320.5</v>
+        <v>316.8</v>
       </c>
       <c r="H16" t="n">
-        <v>57.3</v>
+        <v>60</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>31.16</v>
+        <v>5.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-27.76</v>
+        <v>-15.21</v>
       </c>
       <c r="L16" t="n">
-        <v>41.73</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:06:35</t>
+          <t>05:07:46</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="F17" t="n">
-        <v>7.88</v>
+        <v>6.93</v>
       </c>
       <c r="G17" t="n">
-        <v>300.8</v>
+        <v>308</v>
       </c>
       <c r="H17" t="n">
-        <v>57.2</v>
+        <v>41</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>50.46</v>
+        <v>-38.81</v>
       </c>
       <c r="K17" t="n">
-        <v>58.61</v>
+        <v>-131.64</v>
       </c>
       <c r="L17" t="n">
-        <v>77.34</v>
+        <v>137.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:08:17</t>
+          <t>05:09:39</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="F18" t="n">
-        <v>8</v>
+        <v>4.68</v>
       </c>
       <c r="G18" t="n">
-        <v>328.7</v>
+        <v>321.9</v>
       </c>
       <c r="H18" t="n">
-        <v>51.1</v>
+        <v>52.6</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>6.13</v>
+        <v>56.71</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.38</v>
+        <v>65.55</v>
       </c>
       <c r="L18" t="n">
-        <v>15.63</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:09:13</t>
+          <t>05:11:34</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.21</v>
+        <v>2.02</v>
       </c>
       <c r="F19" t="n">
-        <v>7.56</v>
+        <v>7.55</v>
       </c>
       <c r="G19" t="n">
-        <v>290.6</v>
+        <v>315</v>
       </c>
       <c r="H19" t="n">
-        <v>45.6</v>
+        <v>47.9</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-29.98</v>
+        <v>-79.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-104.58</v>
+        <v>-44.62</v>
       </c>
       <c r="L19" t="n">
-        <v>108.79</v>
+        <v>91.13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:13:46</t>
+          <t>05:15:10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.07</v>
+        <v>2.39</v>
       </c>
       <c r="F20" t="n">
-        <v>8.26</v>
+        <v>8.68</v>
       </c>
       <c r="G20" t="n">
-        <v>313.9</v>
+        <v>303</v>
       </c>
       <c r="H20" t="n">
-        <v>48.6</v>
+        <v>47.4</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>69.65000000000001</v>
+        <v>-109.09</v>
       </c>
       <c r="K20" t="n">
-        <v>80.54000000000001</v>
+        <v>-61.93</v>
       </c>
       <c r="L20" t="n">
-        <v>106.47</v>
+        <v>125.44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:14:45</t>
+          <t>05:16:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.03</v>
+        <v>1.83</v>
       </c>
       <c r="F21" t="n">
-        <v>7.91</v>
+        <v>8.02</v>
       </c>
       <c r="G21" t="n">
-        <v>304.5</v>
+        <v>310.3</v>
       </c>
       <c r="H21" t="n">
-        <v>49.4</v>
+        <v>55.2</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-87.89</v>
+        <v>-94.69</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.69</v>
+        <v>-85.33</v>
       </c>
       <c r="L21" t="n">
-        <v>100.97</v>
+        <v>127.46</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:15:38</t>
+          <t>05:19:12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="F22" t="n">
-        <v>7.31</v>
+        <v>8.85</v>
       </c>
       <c r="G22" t="n">
-        <v>303.4</v>
+        <v>306.9</v>
       </c>
       <c r="H22" t="n">
-        <v>55.2</v>
+        <v>45.4</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.78</v>
+        <v>-131.15</v>
       </c>
       <c r="K22" t="n">
-        <v>-49.7</v>
+        <v>16.87</v>
       </c>
       <c r="L22" t="n">
-        <v>88.95999999999999</v>
+        <v>132.23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:20:33</t>
+          <t>05:24:26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.84</v>
+        <v>2.3</v>
       </c>
       <c r="F23" t="n">
-        <v>7.68</v>
+        <v>6.61</v>
       </c>
       <c r="G23" t="n">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H23" t="n">
-        <v>47</v>
+        <v>51.1</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-84.94</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-81.86</v>
+        <v>-116.43</v>
       </c>
       <c r="L23" t="n">
-        <v>117.97</v>
+        <v>116.78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:21:41</t>
+          <t>05:25:33</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="F24" t="n">
-        <v>7.51</v>
+        <v>7.49</v>
       </c>
       <c r="G24" t="n">
-        <v>299.4</v>
+        <v>312.5</v>
       </c>
       <c r="H24" t="n">
-        <v>58.5</v>
+        <v>50.7</v>
       </c>
       <c r="I24" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.92</v>
+        <v>-124.02</v>
       </c>
       <c r="K24" t="n">
-        <v>13.36</v>
+        <v>118.35</v>
       </c>
       <c r="L24" t="n">
-        <v>132.59</v>
+        <v>171.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:22:49</t>
+          <t>05:26:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="F25" t="n">
-        <v>8.210000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G25" t="n">
-        <v>310.9</v>
+        <v>301</v>
       </c>
       <c r="H25" t="n">
-        <v>46.3</v>
+        <v>50.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>20.86</v>
+        <v>59.07</v>
       </c>
       <c r="K25" t="n">
-        <v>-87.08</v>
+        <v>209.52</v>
       </c>
       <c r="L25" t="n">
-        <v>89.54000000000001</v>
+        <v>217.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:28:41</t>
+          <t>05:31:45</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.33</v>
+        <v>2.85</v>
       </c>
       <c r="F26" t="n">
-        <v>7.79</v>
+        <v>5.85</v>
       </c>
       <c r="G26" t="n">
-        <v>310</v>
+        <v>318.1</v>
       </c>
       <c r="H26" t="n">
-        <v>53</v>
+        <v>39.6</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-130.15</v>
+        <v>-33.7</v>
       </c>
       <c r="K26" t="n">
-        <v>123.67</v>
+        <v>-184.75</v>
       </c>
       <c r="L26" t="n">
-        <v>179.54</v>
+        <v>187.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:29:43</t>
+          <t>05:33:35</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="F27" t="n">
-        <v>7.21</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>308.9</v>
+        <v>309.8</v>
       </c>
       <c r="H27" t="n">
-        <v>53.1</v>
+        <v>53.8</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>79.95</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>222.63</v>
+        <v>-216.89</v>
       </c>
       <c r="L27" t="n">
-        <v>236.55</v>
+        <v>231.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:32:02</t>
+          <t>05:35:41</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.85</v>
+        <v>2.67</v>
       </c>
       <c r="F28" t="n">
-        <v>8.07</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>287.9</v>
+        <v>324.1</v>
       </c>
       <c r="H28" t="n">
-        <v>46</v>
+        <v>52.2</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.89</v>
+        <v>224.01</v>
       </c>
       <c r="K28" t="n">
-        <v>-194.93</v>
+        <v>-33.87</v>
       </c>
       <c r="L28" t="n">
-        <v>195.02</v>
+        <v>226.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:42:56</t>
+          <t>05:44:50</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.32</v>
+        <v>2.62</v>
       </c>
       <c r="F29" t="n">
-        <v>7.65</v>
+        <v>5.33</v>
       </c>
       <c r="G29" t="n">
-        <v>316.1</v>
+        <v>309.1</v>
       </c>
       <c r="H29" t="n">
-        <v>52.2</v>
+        <v>55.2</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>24.15</v>
+        <v>-42.66</v>
       </c>
       <c r="K29" t="n">
-        <v>-45.76</v>
+        <v>43.26</v>
       </c>
       <c r="L29" t="n">
-        <v>51.75</v>
+        <v>60.76</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:44:25</t>
+          <t>05:45:36</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.69</v>
+        <v>2.78</v>
       </c>
       <c r="F30" t="n">
-        <v>8.359999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G30" t="n">
-        <v>313</v>
+        <v>315.4</v>
       </c>
       <c r="H30" t="n">
-        <v>53</v>
+        <v>51.9</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>56.55</v>
+        <v>-5.08</v>
       </c>
       <c r="K30" t="n">
-        <v>-21.33</v>
+        <v>38.7</v>
       </c>
       <c r="L30" t="n">
-        <v>60.44</v>
+        <v>39.03</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:45:31</t>
+          <t>05:46:55</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="F31" t="n">
-        <v>7.62</v>
+        <v>8.26</v>
       </c>
       <c r="G31" t="n">
-        <v>319</v>
+        <v>307.8</v>
       </c>
       <c r="H31" t="n">
-        <v>49.1</v>
+        <v>52.9</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.08</v>
+        <v>76.77</v>
       </c>
       <c r="K31" t="n">
-        <v>33.91</v>
+        <v>-36.92</v>
       </c>
       <c r="L31" t="n">
-        <v>47.37</v>
+        <v>85.18000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:50:17</t>
+          <t>05:50:43</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.79</v>
+        <v>2.09</v>
       </c>
       <c r="F32" t="n">
-        <v>7.93</v>
+        <v>4.68</v>
       </c>
       <c r="G32" t="n">
-        <v>312.4</v>
+        <v>312</v>
       </c>
       <c r="H32" t="n">
-        <v>62.3</v>
+        <v>51.1</v>
       </c>
       <c r="I32" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.36</v>
+        <v>-14.31</v>
       </c>
       <c r="K32" t="n">
-        <v>32.55</v>
+        <v>-58.69</v>
       </c>
       <c r="L32" t="n">
-        <v>32.84</v>
+        <v>60.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:51:48</t>
+          <t>05:52:09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.11</v>
+        <v>2.53</v>
       </c>
       <c r="F33" t="n">
-        <v>7.55</v>
+        <v>6.46</v>
       </c>
       <c r="G33" t="n">
-        <v>314.3</v>
+        <v>319.5</v>
       </c>
       <c r="H33" t="n">
-        <v>44.9</v>
+        <v>50.6</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>82.44</v>
+        <v>78.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.52</v>
+        <v>46.74</v>
       </c>
       <c r="L33" t="n">
-        <v>91.42</v>
+        <v>91.63</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:53:38</t>
+          <t>05:52:58</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.09</v>
+        <v>2.37</v>
       </c>
       <c r="F34" t="n">
-        <v>7.76</v>
+        <v>6.46</v>
       </c>
       <c r="G34" t="n">
-        <v>310.9</v>
+        <v>316.6</v>
       </c>
       <c r="H34" t="n">
-        <v>48</v>
+        <v>42.4</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.69</v>
+        <v>73.13</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.91</v>
+        <v>-6.89</v>
       </c>
       <c r="L34" t="n">
-        <v>57.12</v>
+        <v>73.45999999999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:58:21</t>
+          <t>05:57:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1510,31 +1510,31 @@
         <v>2.54</v>
       </c>
       <c r="F35" t="n">
-        <v>8.140000000000001</v>
+        <v>5.29</v>
       </c>
       <c r="G35" t="n">
-        <v>309.8</v>
+        <v>304.6</v>
       </c>
       <c r="H35" t="n">
-        <v>57</v>
+        <v>50.6</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>88.14</v>
+        <v>44.05</v>
       </c>
       <c r="K35" t="n">
-        <v>51.99</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>102.33</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:58:51</t>
+          <t>05:59:15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.38</v>
+        <v>2.03</v>
       </c>
       <c r="F36" t="n">
-        <v>7.99</v>
+        <v>5.87</v>
       </c>
       <c r="G36" t="n">
-        <v>293.5</v>
+        <v>305.4</v>
       </c>
       <c r="H36" t="n">
-        <v>50.1</v>
+        <v>46.8</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>76.65000000000001</v>
+        <v>-22.38</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.300000000000001</v>
+        <v>111</v>
       </c>
       <c r="L36" t="n">
-        <v>77.20999999999999</v>
+        <v>113.24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:00:48</t>
+          <t>06:00:47</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="F37" t="n">
-        <v>7.39</v>
+        <v>6.15</v>
       </c>
       <c r="G37" t="n">
-        <v>309.7</v>
+        <v>320.4</v>
       </c>
       <c r="H37" t="n">
-        <v>41.2</v>
+        <v>55.2</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>44.28</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>-59.6</v>
+        <v>23.57</v>
       </c>
       <c r="L37" t="n">
-        <v>74.25</v>
+        <v>83.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:04:42</t>
+          <t>06:04:23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="F38" t="n">
-        <v>7.43</v>
+        <v>7.22</v>
       </c>
       <c r="G38" t="n">
-        <v>302.1</v>
+        <v>310.1</v>
       </c>
       <c r="H38" t="n">
-        <v>51</v>
+        <v>54.7</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-23.78</v>
+        <v>-88.86</v>
       </c>
       <c r="K38" t="n">
-        <v>133.53</v>
+        <v>-100.8</v>
       </c>
       <c r="L38" t="n">
-        <v>135.63</v>
+        <v>134.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:06:10</t>
+          <t>06:05:50</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="F39" t="n">
-        <v>8.18</v>
+        <v>7.83</v>
       </c>
       <c r="G39" t="n">
-        <v>319</v>
+        <v>307.5</v>
       </c>
       <c r="H39" t="n">
-        <v>52.8</v>
+        <v>53.5</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.98999999999999</v>
+        <v>-225.46</v>
       </c>
       <c r="K39" t="n">
-        <v>17.16</v>
+        <v>49.62</v>
       </c>
       <c r="L39" t="n">
-        <v>94.56</v>
+        <v>230.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:07:50</t>
+          <t>06:07:37</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.79</v>
+        <v>2.43</v>
       </c>
       <c r="F40" t="n">
-        <v>7.67</v>
+        <v>6.96</v>
       </c>
       <c r="G40" t="n">
-        <v>318</v>
+        <v>324.9</v>
       </c>
       <c r="H40" t="n">
-        <v>55.5</v>
+        <v>50.1</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-51.38</v>
+        <v>30.78</v>
       </c>
       <c r="K40" t="n">
-        <v>-80.03</v>
+        <v>-146.4</v>
       </c>
       <c r="L40" t="n">
-        <v>95.09999999999999</v>
+        <v>149.6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:12:42</t>
+          <t>06:12:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.3</v>
+        <v>2.96</v>
       </c>
       <c r="F41" t="n">
-        <v>7.53</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>315.7</v>
+        <v>317.9</v>
       </c>
       <c r="H41" t="n">
-        <v>52.3</v>
+        <v>49.1</v>
       </c>
       <c r="I41" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-257.2</v>
+        <v>-99.04000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>52.1</v>
+        <v>178.21</v>
       </c>
       <c r="L41" t="n">
-        <v>262.42</v>
+        <v>203.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:14:19</t>
+          <t>06:14:34</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="F42" t="n">
-        <v>8.41</v>
+        <v>7.87</v>
       </c>
       <c r="G42" t="n">
-        <v>308.7</v>
+        <v>308.2</v>
       </c>
       <c r="H42" t="n">
-        <v>50.7</v>
+        <v>53</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>40.63</v>
+        <v>-239.61</v>
       </c>
       <c r="K42" t="n">
-        <v>-173.63</v>
+        <v>-200.29</v>
       </c>
       <c r="L42" t="n">
-        <v>178.32</v>
+        <v>312.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:16:38</t>
+          <t>06:15:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.97</v>
+        <v>2.85</v>
       </c>
       <c r="F43" t="n">
-        <v>8.050000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G43" t="n">
-        <v>306.9</v>
+        <v>293.2</v>
       </c>
       <c r="H43" t="n">
-        <v>52.4</v>
+        <v>55.8</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>-61.68</v>
+        <v>193.85</v>
       </c>
       <c r="K43" t="n">
-        <v>129.16</v>
+        <v>155.38</v>
       </c>
       <c r="L43" t="n">
-        <v>143.13</v>
+        <v>248.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:28:02</t>
+          <t>06:25:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="F44" t="n">
-        <v>7.57</v>
+        <v>4.6</v>
       </c>
       <c r="G44" t="n">
-        <v>314.6</v>
+        <v>308</v>
       </c>
       <c r="H44" t="n">
-        <v>52.4</v>
+        <v>56.7</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-46.37</v>
+        <v>-72.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.35</v>
+        <v>11.58</v>
       </c>
       <c r="L44" t="n">
-        <v>70.68000000000001</v>
+        <v>73.40000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:29:06</t>
+          <t>06:27:45</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.88</v>
+        <v>2.13</v>
       </c>
       <c r="F45" t="n">
-        <v>6.82</v>
+        <v>5.57</v>
       </c>
       <c r="G45" t="n">
-        <v>320.3</v>
+        <v>298.2</v>
       </c>
       <c r="H45" t="n">
-        <v>47.8</v>
+        <v>48.8</v>
       </c>
       <c r="I45" t="n">
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>62.34</v>
+        <v>39.79</v>
       </c>
       <c r="K45" t="n">
-        <v>31.57</v>
+        <v>26.26</v>
       </c>
       <c r="L45" t="n">
-        <v>69.88</v>
+        <v>47.67</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:30:33</t>
+          <t>06:30:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="F46" t="n">
-        <v>7.56</v>
+        <v>6.96</v>
       </c>
       <c r="G46" t="n">
-        <v>321.9</v>
+        <v>307</v>
       </c>
       <c r="H46" t="n">
-        <v>45.8</v>
+        <v>51.3</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>-61.75</v>
+        <v>23.04</v>
       </c>
       <c r="K46" t="n">
-        <v>9.77</v>
+        <v>-46.54</v>
       </c>
       <c r="L46" t="n">
-        <v>62.52</v>
+        <v>51.93</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:34:58</t>
+          <t>06:36:03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="F47" t="n">
-        <v>7.07</v>
+        <v>4.92</v>
       </c>
       <c r="G47" t="n">
-        <v>306.2</v>
+        <v>317.2</v>
       </c>
       <c r="H47" t="n">
-        <v>52.3</v>
+        <v>60.5</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>42.32</v>
+        <v>-35.52</v>
       </c>
       <c r="K47" t="n">
-        <v>27.98</v>
+        <v>68.69</v>
       </c>
       <c r="L47" t="n">
-        <v>50.74</v>
+        <v>77.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:36:54</t>
+          <t>06:38:13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="F48" t="n">
-        <v>7.51</v>
+        <v>8.85</v>
       </c>
       <c r="G48" t="n">
-        <v>311.3</v>
+        <v>311</v>
       </c>
       <c r="H48" t="n">
-        <v>50.3</v>
+        <v>50</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>24.68</v>
+        <v>73.94</v>
       </c>
       <c r="K48" t="n">
-        <v>-49.31</v>
+        <v>-45.68</v>
       </c>
       <c r="L48" t="n">
-        <v>55.15</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:38:39</t>
+          <t>06:39:51</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.1</v>
+        <v>2.73</v>
       </c>
       <c r="F49" t="n">
-        <v>8.02</v>
+        <v>8.85</v>
       </c>
       <c r="G49" t="n">
-        <v>329.6</v>
+        <v>310.7</v>
       </c>
       <c r="H49" t="n">
-        <v>51.4</v>
+        <v>54</v>
       </c>
       <c r="I49" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.26</v>
+        <v>-40.28</v>
       </c>
       <c r="K49" t="n">
-        <v>56.05</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>62.77</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:42:40</t>
+          <t>06:45:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.49</v>
+        <v>2.69</v>
       </c>
       <c r="F50" t="n">
-        <v>7.71</v>
+        <v>7.6</v>
       </c>
       <c r="G50" t="n">
-        <v>308.6</v>
+        <v>323.7</v>
       </c>
       <c r="H50" t="n">
-        <v>59.2</v>
+        <v>52.5</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>75.34</v>
+        <v>-59.11</v>
       </c>
       <c r="K50" t="n">
-        <v>-46.82</v>
+        <v>70.66</v>
       </c>
       <c r="L50" t="n">
-        <v>88.7</v>
+        <v>92.13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:43:45</t>
+          <t>06:47:06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.73</v>
+        <v>1.98</v>
       </c>
       <c r="F51" t="n">
-        <v>7.69</v>
+        <v>5.27</v>
       </c>
       <c r="G51" t="n">
-        <v>316.6</v>
+        <v>317.7</v>
       </c>
       <c r="H51" t="n">
-        <v>48.5</v>
+        <v>44.7</v>
       </c>
       <c r="I51" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-43.81</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.16</v>
+        <v>-86.83</v>
       </c>
       <c r="L51" t="n">
-        <v>92.23</v>
+        <v>87.23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:45:55</t>
+          <t>06:49:20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="F52" t="n">
-        <v>8.35</v>
+        <v>7.08</v>
       </c>
       <c r="G52" t="n">
-        <v>313.6</v>
+        <v>304.4</v>
       </c>
       <c r="H52" t="n">
-        <v>50</v>
+        <v>52.9</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-47.83</v>
+        <v>86.03</v>
       </c>
       <c r="K52" t="n">
-        <v>52.58</v>
+        <v>111.81</v>
       </c>
       <c r="L52" t="n">
-        <v>71.08</v>
+        <v>141.07</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:50:30</t>
+          <t>06:53:38</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.98</v>
+        <v>2.83</v>
       </c>
       <c r="F53" t="n">
-        <v>8.039999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H53" t="n">
-        <v>48.2</v>
+        <v>43.9</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>10.17</v>
+        <v>-41.27</v>
       </c>
       <c r="K53" t="n">
-        <v>-88.56999999999999</v>
+        <v>176.95</v>
       </c>
       <c r="L53" t="n">
-        <v>89.15000000000001</v>
+        <v>181.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:52:25</t>
+          <t>06:56:17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="F54" t="n">
-        <v>7.38</v>
+        <v>8.85</v>
       </c>
       <c r="G54" t="n">
-        <v>314.4</v>
+        <v>316.3</v>
       </c>
       <c r="H54" t="n">
-        <v>50</v>
+        <v>49.2</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>95.16</v>
+        <v>155.86</v>
       </c>
       <c r="K54" t="n">
-        <v>114.71</v>
+        <v>-41.94</v>
       </c>
       <c r="L54" t="n">
-        <v>149.05</v>
+        <v>161.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:54:49</t>
+          <t>06:57:19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="F55" t="n">
-        <v>7.16</v>
+        <v>8.85</v>
       </c>
       <c r="G55" t="n">
-        <v>296.3</v>
+        <v>294.5</v>
       </c>
       <c r="H55" t="n">
-        <v>49.3</v>
+        <v>51.1</v>
       </c>
       <c r="I55" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.35</v>
+        <v>163.88</v>
       </c>
       <c r="K55" t="n">
-        <v>139.75</v>
+        <v>-46.06</v>
       </c>
       <c r="L55" t="n">
-        <v>141.08</v>
+        <v>170.23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:00:25</t>
+          <t>07:02:51</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="F56" t="n">
-        <v>7.97</v>
+        <v>8.85</v>
       </c>
       <c r="G56" t="n">
-        <v>307</v>
+        <v>303.3</v>
       </c>
       <c r="H56" t="n">
-        <v>54.4</v>
+        <v>51.9</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>178.09</v>
+        <v>224.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-64.36</v>
+        <v>127.26</v>
       </c>
       <c r="L56" t="n">
-        <v>189.36</v>
+        <v>258.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:02:57</t>
+          <t>07:04:27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="F57" t="n">
-        <v>6.89</v>
+        <v>8.85</v>
       </c>
       <c r="G57" t="n">
-        <v>310.8</v>
+        <v>316.6</v>
       </c>
       <c r="H57" t="n">
-        <v>51</v>
+        <v>52.4</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>183.29</v>
+        <v>-309.23</v>
       </c>
       <c r="K57" t="n">
-        <v>-49.41</v>
+        <v>84.83</v>
       </c>
       <c r="L57" t="n">
-        <v>189.84</v>
+        <v>320.66</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:03:42</t>
+          <t>07:06:29</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="F58" t="n">
-        <v>7.33</v>
+        <v>7.22</v>
       </c>
       <c r="G58" t="n">
-        <v>312.3</v>
+        <v>296.4</v>
       </c>
       <c r="H58" t="n">
-        <v>55.4</v>
+        <v>44.9</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>183.82</v>
+        <v>15.87</v>
       </c>
       <c r="K58" t="n">
-        <v>71.81</v>
+        <v>-286.8</v>
       </c>
       <c r="L58" t="n">
-        <v>197.35</v>
+        <v>287.23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:13:06</t>
+          <t>07:18:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="F59" t="n">
-        <v>7.99</v>
+        <v>6.87</v>
       </c>
       <c r="G59" t="n">
-        <v>313.3</v>
+        <v>299.9</v>
       </c>
       <c r="H59" t="n">
-        <v>54.4</v>
+        <v>55.3</v>
       </c>
       <c r="I59" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-71.38</v>
+        <v>-23.75</v>
       </c>
       <c r="K59" t="n">
-        <v>13.25</v>
+        <v>-68.7</v>
       </c>
       <c r="L59" t="n">
-        <v>72.59999999999999</v>
+        <v>72.69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:14:41</t>
+          <t>07:21:11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.51</v>
+        <v>3.03</v>
       </c>
       <c r="F60" t="n">
-        <v>6.98</v>
+        <v>8.85</v>
       </c>
       <c r="G60" t="n">
-        <v>298.4</v>
+        <v>314.9</v>
       </c>
       <c r="H60" t="n">
-        <v>50.3</v>
+        <v>55.3</v>
       </c>
       <c r="I60" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>13.86</v>
+        <v>-26.58</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.76000000000001</v>
+        <v>56.96</v>
       </c>
       <c r="L60" t="n">
-        <v>76.03</v>
+        <v>62.86</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:17:20</t>
+          <t>07:23:12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="F61" t="n">
-        <v>7.16</v>
+        <v>8.85</v>
       </c>
       <c r="G61" t="n">
-        <v>319.2</v>
+        <v>313.9</v>
       </c>
       <c r="H61" t="n">
-        <v>56.1</v>
+        <v>43.6</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.01</v>
+        <v>-64.91</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.9</v>
+        <v>-45.87</v>
       </c>
       <c r="L61" t="n">
-        <v>56.83</v>
+        <v>79.48</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:21:11</t>
+          <t>07:27:28</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.03</v>
+        <v>2.34</v>
       </c>
       <c r="F62" t="n">
-        <v>7.91</v>
+        <v>8.85</v>
       </c>
       <c r="G62" t="n">
-        <v>319.2</v>
+        <v>298.1</v>
       </c>
       <c r="H62" t="n">
-        <v>52.2</v>
+        <v>57.7</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-26.16</v>
+        <v>-79.17</v>
       </c>
       <c r="K62" t="n">
-        <v>56.76</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>62.5</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:22:54</t>
+          <t>07:29:22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="F63" t="n">
-        <v>7.85</v>
+        <v>8.67</v>
       </c>
       <c r="G63" t="n">
-        <v>295.8</v>
+        <v>314.9</v>
       </c>
       <c r="H63" t="n">
-        <v>41.8</v>
+        <v>46.6</v>
       </c>
       <c r="I63" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-67.23999999999999</v>
+        <v>-87.22</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.78</v>
+        <v>43.45</v>
       </c>
       <c r="L63" t="n">
-        <v>82.48999999999999</v>
+        <v>97.44</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:24:30</t>
+          <t>07:31:05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="F64" t="n">
-        <v>7.06</v>
+        <v>7.39</v>
       </c>
       <c r="G64" t="n">
-        <v>323.9</v>
+        <v>312.6</v>
       </c>
       <c r="H64" t="n">
-        <v>55.9</v>
+        <v>54.7</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-66.15000000000001</v>
+        <v>37.11</v>
       </c>
       <c r="K64" t="n">
-        <v>59.75</v>
+        <v>53.2</v>
       </c>
       <c r="L64" t="n">
-        <v>89.14</v>
+        <v>64.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:29:50</t>
+          <t>07:35:31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="F65" t="n">
-        <v>7.91</v>
+        <v>7.25</v>
       </c>
       <c r="G65" t="n">
-        <v>301.8</v>
+        <v>309.8</v>
       </c>
       <c r="H65" t="n">
-        <v>50.9</v>
+        <v>44.2</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>-91.73</v>
+        <v>116.58</v>
       </c>
       <c r="K65" t="n">
-        <v>44.47</v>
+        <v>-4.38</v>
       </c>
       <c r="L65" t="n">
-        <v>101.94</v>
+        <v>116.66</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:32:26</t>
+          <t>07:36:16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="F66" t="n">
-        <v>7.79</v>
+        <v>7.83</v>
       </c>
       <c r="G66" t="n">
-        <v>317.9</v>
+        <v>330.6</v>
       </c>
       <c r="H66" t="n">
-        <v>50.6</v>
+        <v>47.7</v>
       </c>
       <c r="I66" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>44.06</v>
+        <v>-3.13</v>
       </c>
       <c r="K66" t="n">
-        <v>62.69</v>
+        <v>90.14</v>
       </c>
       <c r="L66" t="n">
-        <v>76.62</v>
+        <v>90.2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:34:06</t>
+          <t>07:38:02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="F67" t="n">
-        <v>7.65</v>
+        <v>7.54</v>
       </c>
       <c r="G67" t="n">
-        <v>297</v>
+        <v>306.3</v>
       </c>
       <c r="H67" t="n">
-        <v>53.8</v>
+        <v>41.9</v>
       </c>
       <c r="I67" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>106.35</v>
+        <v>44.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.66</v>
+        <v>120.82</v>
       </c>
       <c r="L67" t="n">
-        <v>106.79</v>
+        <v>128.79</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:39:49</t>
+          <t>07:42:45</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="F68" t="n">
-        <v>8.69</v>
+        <v>7.24</v>
       </c>
       <c r="G68" t="n">
-        <v>304</v>
+        <v>310.8</v>
       </c>
       <c r="H68" t="n">
-        <v>49.7</v>
+        <v>57.5</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.15</v>
+        <v>127.36</v>
       </c>
       <c r="K68" t="n">
-        <v>53.02</v>
+        <v>-54.32</v>
       </c>
       <c r="L68" t="n">
-        <v>53.11</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:41:13</t>
+          <t>07:43:38</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="F69" t="n">
-        <v>7.47</v>
+        <v>8.85</v>
       </c>
       <c r="G69" t="n">
-        <v>292.4</v>
+        <v>307.4</v>
       </c>
       <c r="H69" t="n">
-        <v>51.4</v>
+        <v>57.4</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>46.12</v>
+        <v>173.52</v>
       </c>
       <c r="K69" t="n">
-        <v>112.36</v>
+        <v>13.36</v>
       </c>
       <c r="L69" t="n">
-        <v>121.46</v>
+        <v>174.03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:42:25</t>
+          <t>07:44:30</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="F70" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="G70" t="n">
-        <v>323.5</v>
+        <v>300.4</v>
       </c>
       <c r="H70" t="n">
-        <v>50.9</v>
+        <v>52.8</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>105.79</v>
+        <v>-133.82</v>
       </c>
       <c r="K70" t="n">
-        <v>-49.55</v>
+        <v>41.6</v>
       </c>
       <c r="L70" t="n">
-        <v>116.82</v>
+        <v>140.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:46:44</t>
+          <t>07:49:24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="F71" t="n">
-        <v>7.53</v>
+        <v>8.01</v>
       </c>
       <c r="G71" t="n">
-        <v>323.4</v>
+        <v>309.3</v>
       </c>
       <c r="H71" t="n">
-        <v>49</v>
+        <v>49.4</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>181.33</v>
+        <v>-175.69</v>
       </c>
       <c r="K71" t="n">
-        <v>3.82</v>
+        <v>99.22</v>
       </c>
       <c r="L71" t="n">
-        <v>181.37</v>
+        <v>201.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:47:47</t>
+          <t>07:51:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="F72" t="n">
-        <v>7.18</v>
+        <v>8.85</v>
       </c>
       <c r="G72" t="n">
-        <v>314.2</v>
+        <v>312.5</v>
       </c>
       <c r="H72" t="n">
-        <v>49.3</v>
+        <v>55.3</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>-138.33</v>
+        <v>171.19</v>
       </c>
       <c r="K72" t="n">
-        <v>42.04</v>
+        <v>-176.9</v>
       </c>
       <c r="L72" t="n">
-        <v>144.58</v>
+        <v>246.17</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:48:41</t>
+          <t>07:53:12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="F73" t="n">
-        <v>7.62</v>
+        <v>8.85</v>
       </c>
       <c r="G73" t="n">
-        <v>307.3</v>
+        <v>318.6</v>
       </c>
       <c r="H73" t="n">
-        <v>62.1</v>
+        <v>46.4</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-124.69</v>
+        <v>-180.83</v>
       </c>
       <c r="K73" t="n">
-        <v>52.81</v>
+        <v>140.74</v>
       </c>
       <c r="L73" t="n">
-        <v>135.41</v>
+        <v>229.14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>07:58:03</t>
+          <t>08:01:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="F74" t="n">
-        <v>7.78</v>
+        <v>8.85</v>
       </c>
       <c r="G74" t="n">
-        <v>319.2</v>
+        <v>308.9</v>
       </c>
       <c r="H74" t="n">
-        <v>55.4</v>
+        <v>57.2</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>46.32</v>
+        <v>61.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.33</v>
+        <v>0.17</v>
       </c>
       <c r="L74" t="n">
-        <v>65.51000000000001</v>
+        <v>61.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:00:05</t>
+          <t>08:04:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>3.25</v>
+        <v>2.37</v>
       </c>
       <c r="F75" t="n">
-        <v>8.09</v>
+        <v>8.85</v>
       </c>
       <c r="G75" t="n">
-        <v>301.3</v>
+        <v>312.9</v>
       </c>
       <c r="H75" t="n">
-        <v>46.3</v>
+        <v>50.3</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.27</v>
+        <v>-81.93000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>28.93</v>
+        <v>-20.19</v>
       </c>
       <c r="L75" t="n">
-        <v>55.42</v>
+        <v>84.38</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:00:58</t>
+          <t>08:05:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.69</v>
+        <v>3.14</v>
       </c>
       <c r="F76" t="n">
-        <v>7.6</v>
+        <v>7.78</v>
       </c>
       <c r="G76" t="n">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="H76" t="n">
-        <v>60</v>
+        <v>51.6</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>44.31</v>
+        <v>23.68</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.3</v>
+        <v>-54.05</v>
       </c>
       <c r="L76" t="n">
-        <v>44.31</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:04:02</t>
+          <t>08:09:23</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="F77" t="n">
-        <v>7.8</v>
+        <v>6.82</v>
       </c>
       <c r="G77" t="n">
-        <v>309.1</v>
+        <v>302.6</v>
       </c>
       <c r="H77" t="n">
-        <v>56.1</v>
+        <v>49.7</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-74.59999999999999</v>
+        <v>-49.72</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.49</v>
+        <v>59.93</v>
       </c>
       <c r="L77" t="n">
-        <v>76.86</v>
+        <v>77.87</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:06:16</t>
+          <t>08:11:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>3.14</v>
+        <v>2.71</v>
       </c>
       <c r="F78" t="n">
-        <v>8.109999999999999</v>
+        <v>6.62</v>
       </c>
       <c r="G78" t="n">
-        <v>311.7</v>
+        <v>316.7</v>
       </c>
       <c r="H78" t="n">
-        <v>46.6</v>
+        <v>49.6</v>
       </c>
       <c r="I78" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>19.24</v>
+        <v>-24.4</v>
       </c>
       <c r="K78" t="n">
-        <v>-45.24</v>
+        <v>-119.38</v>
       </c>
       <c r="L78" t="n">
-        <v>49.16</v>
+        <v>121.84</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:08:34</t>
+          <t>08:13:04</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.24</v>
+        <v>2.49</v>
       </c>
       <c r="F79" t="n">
-        <v>7.29</v>
+        <v>6.18</v>
       </c>
       <c r="G79" t="n">
-        <v>308</v>
+        <v>310.5</v>
       </c>
       <c r="H79" t="n">
-        <v>51</v>
+        <v>54.4</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.57</v>
+        <v>-87.34999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>52.35</v>
+        <v>-14.86</v>
       </c>
       <c r="L79" t="n">
-        <v>67.47</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:12:33</t>
+          <t>08:17:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.71</v>
+        <v>2.19</v>
       </c>
       <c r="F80" t="n">
-        <v>7.99</v>
+        <v>4.99</v>
       </c>
       <c r="G80" t="n">
-        <v>307.8</v>
+        <v>314.1</v>
       </c>
       <c r="H80" t="n">
-        <v>46.9</v>
+        <v>56.2</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-27.32</v>
+        <v>-50.76</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.54</v>
+        <v>-89.33</v>
       </c>
       <c r="L80" t="n">
-        <v>135.33</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:14:36</t>
+          <t>08:18:15</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="F81" t="n">
-        <v>7.69</v>
+        <v>8.85</v>
       </c>
       <c r="G81" t="n">
-        <v>317.3</v>
+        <v>309.3</v>
       </c>
       <c r="H81" t="n">
-        <v>49.4</v>
+        <v>49.6</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-103.48</v>
+        <v>139.86</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.36</v>
+        <v>97.11</v>
       </c>
       <c r="L81" t="n">
-        <v>104.93</v>
+        <v>170.27</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:16:11</t>
+          <t>08:20:36</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.19</v>
+        <v>2.73</v>
       </c>
       <c r="F82" t="n">
-        <v>7.86</v>
+        <v>8.85</v>
       </c>
       <c r="G82" t="n">
-        <v>321.1</v>
+        <v>307.5</v>
       </c>
       <c r="H82" t="n">
-        <v>46.9</v>
+        <v>53.1</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>-39.18</v>
+        <v>119.35</v>
       </c>
       <c r="K82" t="n">
-        <v>-82.70999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="L82" t="n">
-        <v>91.53</v>
+        <v>120.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:19:22</t>
+          <t>08:26:27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.41</v>
+        <v>2.91</v>
       </c>
       <c r="F83" t="n">
-        <v>7.62</v>
+        <v>8.85</v>
       </c>
       <c r="G83" t="n">
-        <v>307.8</v>
+        <v>312.5</v>
       </c>
       <c r="H83" t="n">
-        <v>52.7</v>
+        <v>63.9</v>
       </c>
       <c r="I83" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>138.55</v>
+        <v>-60.96</v>
       </c>
       <c r="K83" t="n">
-        <v>91.23</v>
+        <v>212.11</v>
       </c>
       <c r="L83" t="n">
-        <v>165.89</v>
+        <v>220.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:20:26</t>
+          <t>08:28:48</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.73</v>
+        <v>2.37</v>
       </c>
       <c r="F84" t="n">
-        <v>7.53</v>
+        <v>8.85</v>
       </c>
       <c r="G84" t="n">
-        <v>314.8</v>
+        <v>309.9</v>
       </c>
       <c r="H84" t="n">
-        <v>52.3</v>
+        <v>50</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>129.95</v>
+        <v>-106.49</v>
       </c>
       <c r="K84" t="n">
-        <v>12.58</v>
+        <v>-153.93</v>
       </c>
       <c r="L84" t="n">
-        <v>130.56</v>
+        <v>187.18</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:21:24</t>
+          <t>08:29:25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.91</v>
+        <v>2.34</v>
       </c>
       <c r="F85" t="n">
-        <v>7.78</v>
+        <v>7.89</v>
       </c>
       <c r="G85" t="n">
-        <v>336.4</v>
+        <v>308.6</v>
       </c>
       <c r="H85" t="n">
-        <v>52.5</v>
+        <v>46.5</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-30.34</v>
+        <v>-146.86</v>
       </c>
       <c r="K85" t="n">
-        <v>154.4</v>
+        <v>-73.04000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>157.36</v>
+        <v>164.02</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:27:17</t>
+          <t>08:34:50</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="F86" t="n">
-        <v>7.66</v>
+        <v>8.24</v>
       </c>
       <c r="G86" t="n">
-        <v>308.6</v>
+        <v>312.5</v>
       </c>
       <c r="H86" t="n">
-        <v>55.5</v>
+        <v>59.6</v>
       </c>
       <c r="I86" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>-103.48</v>
+        <v>125.77</v>
       </c>
       <c r="K86" t="n">
-        <v>-178.88</v>
+        <v>199.15</v>
       </c>
       <c r="L86" t="n">
-        <v>206.65</v>
+        <v>235.54</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:28:34</t>
+          <t>08:36:41</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="F87" t="n">
-        <v>7.59</v>
+        <v>8.09</v>
       </c>
       <c r="G87" t="n">
-        <v>301.5</v>
+        <v>313.6</v>
       </c>
       <c r="H87" t="n">
-        <v>48.3</v>
+        <v>53.3</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-143.02</v>
+        <v>-152.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-92.25</v>
+        <v>184.53</v>
       </c>
       <c r="L87" t="n">
-        <v>170.19</v>
+        <v>239.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:38:59</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.39</v>
+        <v>2.74</v>
       </c>
       <c r="F88" t="n">
-        <v>7.79</v>
+        <v>8.32</v>
       </c>
       <c r="G88" t="n">
-        <v>327.7</v>
+        <v>316.7</v>
       </c>
       <c r="H88" t="n">
-        <v>52.5</v>
+        <v>49.7</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>122.54</v>
+        <v>-158.63</v>
       </c>
       <c r="K88" t="n">
-        <v>121.86</v>
+        <v>237.18</v>
       </c>
       <c r="L88" t="n">
-        <v>172.82</v>
+        <v>285.34</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>45.87</v>
+        <v>51.5</v>
       </c>
       <c r="K14" t="n">
-        <v>-40.25</v>
+        <v>-45.19</v>
       </c>
       <c r="L14" t="n">
-        <v>61.02</v>
+        <v>68.51000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>42.63</v>
+        <v>45.78</v>
       </c>
       <c r="K15" t="n">
-        <v>49.61</v>
+        <v>53.28</v>
       </c>
       <c r="L15" t="n">
-        <v>65.41</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>5.68</v>
+        <v>6.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-15.21</v>
+        <v>-16.34</v>
       </c>
       <c r="L16" t="n">
-        <v>16.24</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.81</v>
+        <v>-44.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-131.64</v>
+        <v>-149.8</v>
       </c>
       <c r="L17" t="n">
-        <v>137.24</v>
+        <v>156.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>56.71</v>
+        <v>64.53</v>
       </c>
       <c r="K18" t="n">
-        <v>65.55</v>
+        <v>74.59</v>
       </c>
       <c r="L18" t="n">
-        <v>86.68000000000001</v>
+        <v>98.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-79.45</v>
+        <v>-90.41</v>
       </c>
       <c r="K19" t="n">
-        <v>-44.62</v>
+        <v>-50.78</v>
       </c>
       <c r="L19" t="n">
-        <v>91.13</v>
+        <v>103.7</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>16</v>
       </c>
       <c r="J20" t="n">
-        <v>-109.09</v>
+        <v>-124.13</v>
       </c>
       <c r="K20" t="n">
-        <v>-61.93</v>
+        <v>-70.47</v>
       </c>
       <c r="L20" t="n">
-        <v>125.44</v>
+        <v>142.74</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-94.69</v>
+        <v>-101.7</v>
       </c>
       <c r="K21" t="n">
-        <v>-85.33</v>
+        <v>-91.65000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>127.46</v>
+        <v>136.9</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-131.15</v>
+        <v>-143.07</v>
       </c>
       <c r="K22" t="n">
-        <v>16.87</v>
+        <v>18.41</v>
       </c>
       <c r="L22" t="n">
-        <v>132.23</v>
+        <v>144.25</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>9.050000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="K23" t="n">
-        <v>-116.43</v>
+        <v>-128.9</v>
       </c>
       <c r="L23" t="n">
-        <v>116.78</v>
+        <v>129.29</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-124.02</v>
+        <v>-141.13</v>
       </c>
       <c r="K24" t="n">
-        <v>118.35</v>
+        <v>134.68</v>
       </c>
       <c r="L24" t="n">
-        <v>171.43</v>
+        <v>195.08</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>59.07</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>209.52</v>
+        <v>235.25</v>
       </c>
       <c r="L25" t="n">
-        <v>217.69</v>
+        <v>244.43</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-33.7</v>
+        <v>-35.61</v>
       </c>
       <c r="K26" t="n">
-        <v>-184.75</v>
+        <v>-195.21</v>
       </c>
       <c r="L26" t="n">
-        <v>187.8</v>
+        <v>198.43</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>17</v>
       </c>
       <c r="J27" t="n">
-        <v>81.90000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>-216.89</v>
+        <v>-243.52</v>
       </c>
       <c r="L27" t="n">
-        <v>231.84</v>
+        <v>260.31</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>224.01</v>
+        <v>248.01</v>
       </c>
       <c r="K28" t="n">
-        <v>-33.87</v>
+        <v>-37.49</v>
       </c>
       <c r="L28" t="n">
-        <v>226.55</v>
+        <v>250.83</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-42.66</v>
+        <v>-48.54</v>
       </c>
       <c r="K29" t="n">
-        <v>43.26</v>
+        <v>49.23</v>
       </c>
       <c r="L29" t="n">
-        <v>60.76</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>16</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.08</v>
+        <v>-5.78</v>
       </c>
       <c r="K30" t="n">
-        <v>38.7</v>
+        <v>44.04</v>
       </c>
       <c r="L30" t="n">
-        <v>39.03</v>
+        <v>44.42</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>17</v>
       </c>
       <c r="J31" t="n">
-        <v>76.77</v>
+        <v>86.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-36.92</v>
+        <v>-41.45</v>
       </c>
       <c r="L31" t="n">
-        <v>85.18000000000001</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>21</v>
       </c>
       <c r="J32" t="n">
-        <v>-14.31</v>
+        <v>-15.12</v>
       </c>
       <c r="K32" t="n">
-        <v>-58.69</v>
+        <v>-62.01</v>
       </c>
       <c r="L32" t="n">
-        <v>60.41</v>
+        <v>63.83</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>16</v>
       </c>
       <c r="J33" t="n">
-        <v>78.81</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>46.74</v>
+        <v>53.18</v>
       </c>
       <c r="L33" t="n">
-        <v>91.63</v>
+        <v>104.26</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>73.13</v>
+        <v>83.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-6.89</v>
+        <v>-7.84</v>
       </c>
       <c r="L34" t="n">
-        <v>73.45999999999999</v>
+        <v>83.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>44.05</v>
+        <v>48.77</v>
       </c>
       <c r="K35" t="n">
-        <v>-72.01000000000001</v>
+        <v>-79.72</v>
       </c>
       <c r="L35" t="n">
-        <v>84.41</v>
+        <v>93.45999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.38</v>
+        <v>-23.64</v>
       </c>
       <c r="K36" t="n">
-        <v>111</v>
+        <v>117.29</v>
       </c>
       <c r="L36" t="n">
-        <v>113.24</v>
+        <v>119.65</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-80.48999999999999</v>
+        <v>-86.45999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>23.57</v>
+        <v>25.32</v>
       </c>
       <c r="L37" t="n">
-        <v>83.88</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-88.86</v>
+        <v>-95.44</v>
       </c>
       <c r="K38" t="n">
-        <v>-100.8</v>
+        <v>-108.27</v>
       </c>
       <c r="L38" t="n">
-        <v>134.37</v>
+        <v>144.33</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>16</v>
       </c>
       <c r="J39" t="n">
-        <v>-225.46</v>
+        <v>-256.56</v>
       </c>
       <c r="K39" t="n">
-        <v>49.62</v>
+        <v>56.46</v>
       </c>
       <c r="L39" t="n">
-        <v>230.86</v>
+        <v>262.7</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>30.78</v>
+        <v>35.03</v>
       </c>
       <c r="K40" t="n">
-        <v>-146.4</v>
+        <v>-166.59</v>
       </c>
       <c r="L40" t="n">
-        <v>149.6</v>
+        <v>170.24</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>-99.04000000000001</v>
+        <v>-109.65</v>
       </c>
       <c r="K41" t="n">
-        <v>178.21</v>
+        <v>197.31</v>
       </c>
       <c r="L41" t="n">
-        <v>203.88</v>
+        <v>225.73</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>17</v>
       </c>
       <c r="J42" t="n">
-        <v>-239.61</v>
+        <v>-269.03</v>
       </c>
       <c r="K42" t="n">
-        <v>-200.29</v>
+        <v>-224.89</v>
       </c>
       <c r="L42" t="n">
-        <v>312.3</v>
+        <v>350.65</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>193.85</v>
+        <v>211.47</v>
       </c>
       <c r="K43" t="n">
-        <v>155.38</v>
+        <v>169.5</v>
       </c>
       <c r="L43" t="n">
-        <v>248.43</v>
+        <v>271.02</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="J44" t="n">
-        <v>-72.48</v>
+        <v>-81.38</v>
       </c>
       <c r="K44" t="n">
-        <v>11.58</v>
+        <v>13</v>
       </c>
       <c r="L44" t="n">
-        <v>73.40000000000001</v>
+        <v>82.41</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>39.79</v>
+        <v>42.04</v>
       </c>
       <c r="K45" t="n">
-        <v>26.26</v>
+        <v>27.75</v>
       </c>
       <c r="L45" t="n">
-        <v>47.67</v>
+        <v>50.37</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>23.04</v>
+        <v>24.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-46.54</v>
+        <v>-49.99</v>
       </c>
       <c r="L46" t="n">
-        <v>51.93</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>-35.52</v>
+        <v>-38.75</v>
       </c>
       <c r="K47" t="n">
-        <v>68.69</v>
+        <v>74.93000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>77.33</v>
+        <v>84.36</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>16</v>
       </c>
       <c r="J48" t="n">
-        <v>73.94</v>
+        <v>84.14</v>
       </c>
       <c r="K48" t="n">
-        <v>-45.68</v>
+        <v>-51.98</v>
       </c>
       <c r="L48" t="n">
-        <v>86.92</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-40.28</v>
+        <v>-45.23</v>
       </c>
       <c r="K49" t="n">
-        <v>-74.06999999999999</v>
+        <v>-83.17</v>
       </c>
       <c r="L49" t="n">
-        <v>84.31999999999999</v>
+        <v>94.67</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>-59.11</v>
+        <v>-62.46</v>
       </c>
       <c r="K50" t="n">
-        <v>70.66</v>
+        <v>74.66</v>
       </c>
       <c r="L50" t="n">
-        <v>92.13</v>
+        <v>97.34</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>8.380000000000001</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-86.83</v>
+        <v>-93.26000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>87.23</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>86.03</v>
+        <v>97.89</v>
       </c>
       <c r="K52" t="n">
-        <v>111.81</v>
+        <v>127.23</v>
       </c>
       <c r="L52" t="n">
-        <v>141.07</v>
+        <v>160.53</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-41.27</v>
+        <v>-43.61</v>
       </c>
       <c r="K53" t="n">
-        <v>176.95</v>
+        <v>186.97</v>
       </c>
       <c r="L53" t="n">
-        <v>181.7</v>
+        <v>191.99</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>155.86</v>
+        <v>167.41</v>
       </c>
       <c r="K54" t="n">
-        <v>-41.94</v>
+        <v>-45.04</v>
       </c>
       <c r="L54" t="n">
-        <v>161.41</v>
+        <v>173.36</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>163.88</v>
+        <v>181.43</v>
       </c>
       <c r="K55" t="n">
-        <v>-46.06</v>
+        <v>-50.99</v>
       </c>
       <c r="L55" t="n">
-        <v>170.23</v>
+        <v>188.46</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>224.78</v>
+        <v>248.87</v>
       </c>
       <c r="K56" t="n">
-        <v>127.26</v>
+        <v>140.9</v>
       </c>
       <c r="L56" t="n">
-        <v>258.31</v>
+        <v>285.98</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-309.23</v>
+        <v>-326.74</v>
       </c>
       <c r="K57" t="n">
-        <v>84.83</v>
+        <v>89.63</v>
       </c>
       <c r="L57" t="n">
-        <v>320.66</v>
+        <v>338.81</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>15.87</v>
+        <v>17.04</v>
       </c>
       <c r="K58" t="n">
-        <v>-286.8</v>
+        <v>-308.04</v>
       </c>
       <c r="L58" t="n">
-        <v>287.23</v>
+        <v>308.51</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>-23.75</v>
+        <v>-27.03</v>
       </c>
       <c r="K59" t="n">
-        <v>-68.7</v>
+        <v>-78.17</v>
       </c>
       <c r="L59" t="n">
-        <v>72.69</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-26.58</v>
+        <v>-28.55</v>
       </c>
       <c r="K60" t="n">
-        <v>56.96</v>
+        <v>61.18</v>
       </c>
       <c r="L60" t="n">
-        <v>62.86</v>
+        <v>67.51000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>20</v>
       </c>
       <c r="J61" t="n">
-        <v>-64.91</v>
+        <v>-69.70999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>-45.87</v>
+        <v>-49.26</v>
       </c>
       <c r="L61" t="n">
-        <v>79.48</v>
+        <v>85.36</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>21</v>
       </c>
       <c r="J62" t="n">
-        <v>-79.17</v>
+        <v>-83.65000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>70.06999999999999</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>105.72</v>
+        <v>111.71</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-87.22</v>
+        <v>-99.25</v>
       </c>
       <c r="K63" t="n">
-        <v>43.45</v>
+        <v>49.44</v>
       </c>
       <c r="L63" t="n">
-        <v>97.44</v>
+        <v>110.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>37.11</v>
+        <v>39.86</v>
       </c>
       <c r="K64" t="n">
-        <v>53.2</v>
+        <v>57.15</v>
       </c>
       <c r="L64" t="n">
-        <v>64.87</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>116.58</v>
+        <v>123.18</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.38</v>
+        <v>-4.63</v>
       </c>
       <c r="L65" t="n">
-        <v>116.66</v>
+        <v>123.26</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.13</v>
+        <v>-3.56</v>
       </c>
       <c r="K66" t="n">
-        <v>90.14</v>
+        <v>102.58</v>
       </c>
       <c r="L66" t="n">
-        <v>90.2</v>
+        <v>102.64</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>17</v>
       </c>
       <c r="J67" t="n">
-        <v>44.59</v>
+        <v>50.07</v>
       </c>
       <c r="K67" t="n">
-        <v>120.82</v>
+        <v>135.66</v>
       </c>
       <c r="L67" t="n">
-        <v>128.79</v>
+        <v>144.6</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>127.36</v>
+        <v>141.01</v>
       </c>
       <c r="K68" t="n">
-        <v>-54.32</v>
+        <v>-60.13</v>
       </c>
       <c r="L68" t="n">
-        <v>138.46</v>
+        <v>153.29</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>173.52</v>
+        <v>197.45</v>
       </c>
       <c r="K69" t="n">
-        <v>13.36</v>
+        <v>15.2</v>
       </c>
       <c r="L69" t="n">
-        <v>174.03</v>
+        <v>198.04</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>17</v>
       </c>
       <c r="J70" t="n">
-        <v>-133.82</v>
+        <v>-150.26</v>
       </c>
       <c r="K70" t="n">
-        <v>41.6</v>
+        <v>46.7</v>
       </c>
       <c r="L70" t="n">
-        <v>140.14</v>
+        <v>157.35</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>16</v>
       </c>
       <c r="J71" t="n">
-        <v>-175.69</v>
+        <v>-199.93</v>
       </c>
       <c r="K71" t="n">
-        <v>99.22</v>
+        <v>112.91</v>
       </c>
       <c r="L71" t="n">
-        <v>201.77</v>
+        <v>229.61</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>171.19</v>
+        <v>194.8</v>
       </c>
       <c r="K72" t="n">
-        <v>-176.9</v>
+        <v>-201.3</v>
       </c>
       <c r="L72" t="n">
-        <v>246.17</v>
+        <v>280.13</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>17</v>
       </c>
       <c r="J73" t="n">
-        <v>-180.83</v>
+        <v>-203.03</v>
       </c>
       <c r="K73" t="n">
-        <v>140.74</v>
+        <v>158.02</v>
       </c>
       <c r="L73" t="n">
-        <v>229.14</v>
+        <v>257.28</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>61.42</v>
+        <v>68.95999999999999</v>
       </c>
       <c r="K74" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="L74" t="n">
-        <v>61.42</v>
+        <v>68.95999999999999</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-81.93000000000001</v>
+        <v>-93.23</v>
       </c>
       <c r="K75" t="n">
-        <v>-20.19</v>
+        <v>-22.98</v>
       </c>
       <c r="L75" t="n">
-        <v>84.38</v>
+        <v>96.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>23.68</v>
+        <v>26.94</v>
       </c>
       <c r="K76" t="n">
-        <v>-54.05</v>
+        <v>-61.51</v>
       </c>
       <c r="L76" t="n">
-        <v>59.01</v>
+        <v>67.15000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>-49.72</v>
+        <v>-52.54</v>
       </c>
       <c r="K77" t="n">
-        <v>59.93</v>
+        <v>63.32</v>
       </c>
       <c r="L77" t="n">
-        <v>77.87</v>
+        <v>82.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>17</v>
       </c>
       <c r="J78" t="n">
-        <v>-24.4</v>
+        <v>-27.39</v>
       </c>
       <c r="K78" t="n">
-        <v>-119.38</v>
+        <v>-134.04</v>
       </c>
       <c r="L78" t="n">
-        <v>121.84</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-87.34999999999999</v>
+        <v>-93.81999999999999</v>
       </c>
       <c r="K79" t="n">
-        <v>-14.86</v>
+        <v>-15.96</v>
       </c>
       <c r="L79" t="n">
-        <v>88.59999999999999</v>
+        <v>95.17</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>-50.76</v>
+        <v>-54.52</v>
       </c>
       <c r="K80" t="n">
-        <v>-89.33</v>
+        <v>-95.95</v>
       </c>
       <c r="L80" t="n">
-        <v>102.75</v>
+        <v>110.36</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>139.86</v>
+        <v>154.84</v>
       </c>
       <c r="K81" t="n">
-        <v>97.11</v>
+        <v>107.52</v>
       </c>
       <c r="L81" t="n">
-        <v>170.27</v>
+        <v>188.51</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>119.35</v>
+        <v>135.82</v>
       </c>
       <c r="K82" t="n">
-        <v>16.5</v>
+        <v>18.77</v>
       </c>
       <c r="L82" t="n">
-        <v>120.49</v>
+        <v>137.11</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>16</v>
       </c>
       <c r="J83" t="n">
-        <v>-60.96</v>
+        <v>-69.37</v>
       </c>
       <c r="K83" t="n">
-        <v>212.11</v>
+        <v>241.36</v>
       </c>
       <c r="L83" t="n">
-        <v>220.69</v>
+        <v>251.13</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>-106.49</v>
+        <v>-116.17</v>
       </c>
       <c r="K84" t="n">
-        <v>-153.93</v>
+        <v>-167.93</v>
       </c>
       <c r="L84" t="n">
-        <v>187.18</v>
+        <v>204.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>-146.86</v>
+        <v>-164.9</v>
       </c>
       <c r="K85" t="n">
-        <v>-73.04000000000001</v>
+        <v>-82.01000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>164.02</v>
+        <v>184.16</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>18</v>
       </c>
       <c r="J86" t="n">
-        <v>125.77</v>
+        <v>139.24</v>
       </c>
       <c r="K86" t="n">
-        <v>199.15</v>
+        <v>220.49</v>
       </c>
       <c r="L86" t="n">
-        <v>235.54</v>
+        <v>260.78</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-152.91</v>
+        <v>-164.24</v>
       </c>
       <c r="K87" t="n">
-        <v>184.53</v>
+        <v>198.2</v>
       </c>
       <c r="L87" t="n">
-        <v>239.66</v>
+        <v>257.41</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-158.63</v>
+        <v>-173.05</v>
       </c>
       <c r="K88" t="n">
-        <v>237.18</v>
+        <v>258.74</v>
       </c>
       <c r="L88" t="n">
-        <v>285.34</v>
+        <v>311.28</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="F14" t="n">
-        <v>8.85</v>
+        <v>5.83</v>
       </c>
       <c r="G14" t="n">
-        <v>326.5</v>
+        <v>319.1</v>
       </c>
       <c r="H14" t="n">
-        <v>55.9</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>51.5</v>
+        <v>-4.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-45.19</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>68.51000000000001</v>
+        <v>32.31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:01:25</t>
+          <t>05:02:02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="F15" t="n">
-        <v>4.22</v>
+        <v>8.85</v>
       </c>
       <c r="G15" t="n">
-        <v>314.3</v>
+        <v>315</v>
       </c>
       <c r="H15" t="n">
-        <v>46.1</v>
+        <v>38.9</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>45.78</v>
+        <v>-25.64</v>
       </c>
       <c r="K15" t="n">
-        <v>53.28</v>
+        <v>27.87</v>
       </c>
       <c r="L15" t="n">
-        <v>70.25</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:03:41</t>
+          <t>05:03:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="F16" t="n">
-        <v>6.73</v>
+        <v>3.53</v>
       </c>
       <c r="G16" t="n">
-        <v>316.8</v>
+        <v>307.4</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>33.5</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>6.11</v>
+        <v>-36.72</v>
       </c>
       <c r="K16" t="n">
-        <v>-16.34</v>
+        <v>13.76</v>
       </c>
       <c r="L16" t="n">
-        <v>17.44</v>
+        <v>39.22</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:07:46</t>
+          <t>05:07:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="F17" t="n">
-        <v>6.93</v>
+        <v>5.71</v>
       </c>
       <c r="G17" t="n">
-        <v>308</v>
+        <v>319.2</v>
       </c>
       <c r="H17" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="I17" t="n">
         <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>-44.16</v>
+        <v>55.93</v>
       </c>
       <c r="K17" t="n">
-        <v>-149.8</v>
+        <v>-13.75</v>
       </c>
       <c r="L17" t="n">
-        <v>156.17</v>
+        <v>57.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:09:39</t>
+          <t>05:08:54</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.06</v>
+        <v>3.14</v>
       </c>
       <c r="F18" t="n">
-        <v>4.68</v>
+        <v>8.85</v>
       </c>
       <c r="G18" t="n">
-        <v>321.9</v>
+        <v>314.2</v>
       </c>
       <c r="H18" t="n">
-        <v>52.6</v>
+        <v>40.1</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>64.53</v>
+        <v>65.63</v>
       </c>
       <c r="K18" t="n">
-        <v>74.59</v>
+        <v>-61.82</v>
       </c>
       <c r="L18" t="n">
-        <v>98.63</v>
+        <v>90.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:11:34</t>
+          <t>05:11:02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.02</v>
+        <v>2.72</v>
       </c>
       <c r="F19" t="n">
-        <v>7.55</v>
+        <v>7.38</v>
       </c>
       <c r="G19" t="n">
-        <v>315</v>
+        <v>317.6</v>
       </c>
       <c r="H19" t="n">
-        <v>47.9</v>
+        <v>61.5</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>-90.41</v>
+        <v>-61.12</v>
       </c>
       <c r="K19" t="n">
-        <v>-50.78</v>
+        <v>-4.33</v>
       </c>
       <c r="L19" t="n">
-        <v>103.7</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:15:10</t>
+          <t>05:15:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.39</v>
+        <v>2.07</v>
       </c>
       <c r="F20" t="n">
-        <v>8.68</v>
+        <v>7.3</v>
       </c>
       <c r="G20" t="n">
-        <v>303</v>
+        <v>315.6</v>
       </c>
       <c r="H20" t="n">
-        <v>47.4</v>
+        <v>61.6</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-124.13</v>
+        <v>-91.72</v>
       </c>
       <c r="K20" t="n">
-        <v>-70.47</v>
+        <v>-50.66</v>
       </c>
       <c r="L20" t="n">
-        <v>142.74</v>
+        <v>104.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:16:53</t>
+          <t>05:16:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.83</v>
+        <v>2.13</v>
       </c>
       <c r="F21" t="n">
-        <v>8.02</v>
+        <v>4.74</v>
       </c>
       <c r="G21" t="n">
-        <v>310.3</v>
+        <v>309.9</v>
       </c>
       <c r="H21" t="n">
-        <v>55.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-101.7</v>
+        <v>83.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-91.65000000000001</v>
+        <v>-19.53</v>
       </c>
       <c r="L21" t="n">
-        <v>136.9</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:19:12</t>
+          <t>05:19:11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.21</v>
+        <v>1.92</v>
       </c>
       <c r="F22" t="n">
-        <v>8.85</v>
+        <v>5.4</v>
       </c>
       <c r="G22" t="n">
-        <v>306.9</v>
+        <v>310.2</v>
       </c>
       <c r="H22" t="n">
-        <v>45.4</v>
+        <v>56.5</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J22" t="n">
-        <v>-143.07</v>
+        <v>-84.55</v>
       </c>
       <c r="K22" t="n">
-        <v>18.41</v>
+        <v>17.98</v>
       </c>
       <c r="L22" t="n">
-        <v>144.25</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:24:26</t>
+          <t>05:23:45</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="F23" t="n">
-        <v>6.61</v>
+        <v>8.85</v>
       </c>
       <c r="G23" t="n">
-        <v>321</v>
+        <v>303.8</v>
       </c>
       <c r="H23" t="n">
-        <v>51.1</v>
+        <v>94</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" t="n">
-        <v>10.02</v>
+        <v>137.16</v>
       </c>
       <c r="K23" t="n">
-        <v>-128.9</v>
+        <v>-27.54</v>
       </c>
       <c r="L23" t="n">
-        <v>129.29</v>
+        <v>139.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:25:33</t>
+          <t>05:26:10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="F24" t="n">
-        <v>7.49</v>
+        <v>3.22</v>
       </c>
       <c r="G24" t="n">
-        <v>312.5</v>
+        <v>307.8</v>
       </c>
       <c r="H24" t="n">
-        <v>50.7</v>
+        <v>22.7</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>-141.13</v>
+        <v>-137.24</v>
       </c>
       <c r="K24" t="n">
-        <v>134.68</v>
+        <v>16.64</v>
       </c>
       <c r="L24" t="n">
-        <v>195.08</v>
+        <v>138.24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:26:55</t>
+          <t>05:28:09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.52</v>
+        <v>2.93</v>
       </c>
       <c r="F25" t="n">
-        <v>8.85</v>
+        <v>7.65</v>
       </c>
       <c r="G25" t="n">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="H25" t="n">
-        <v>50.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J25" t="n">
-        <v>66.31999999999999</v>
+        <v>-168.2</v>
       </c>
       <c r="K25" t="n">
-        <v>235.25</v>
+        <v>-23.48</v>
       </c>
       <c r="L25" t="n">
-        <v>244.43</v>
+        <v>169.83</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:31:45</t>
+          <t>05:32:44</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="F26" t="n">
-        <v>5.85</v>
+        <v>5.29</v>
       </c>
       <c r="G26" t="n">
-        <v>318.1</v>
+        <v>304.3</v>
       </c>
       <c r="H26" t="n">
-        <v>39.6</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-35.61</v>
+        <v>-201.94</v>
       </c>
       <c r="K26" t="n">
-        <v>-195.21</v>
+        <v>-51.78</v>
       </c>
       <c r="L26" t="n">
-        <v>198.43</v>
+        <v>208.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:33:35</t>
+          <t>05:35:06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="F27" t="n">
-        <v>8.050000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="G27" t="n">
-        <v>309.8</v>
+        <v>301.7</v>
       </c>
       <c r="H27" t="n">
-        <v>53.8</v>
+        <v>47.7</v>
       </c>
       <c r="I27" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>91.95999999999999</v>
+        <v>12.23</v>
       </c>
       <c r="K27" t="n">
-        <v>-243.52</v>
+        <v>-136.48</v>
       </c>
       <c r="L27" t="n">
-        <v>260.31</v>
+        <v>137.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:35:41</t>
+          <t>05:36:06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.67</v>
+        <v>2.51</v>
       </c>
       <c r="F28" t="n">
-        <v>8.550000000000001</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>324.1</v>
+        <v>308.5</v>
       </c>
       <c r="H28" t="n">
-        <v>52.2</v>
+        <v>66.2</v>
       </c>
       <c r="I28" t="n">
         <v>18</v>
       </c>
       <c r="J28" t="n">
-        <v>248.01</v>
+        <v>-68.73</v>
       </c>
       <c r="K28" t="n">
-        <v>-37.49</v>
+        <v>265.66</v>
       </c>
       <c r="L28" t="n">
-        <v>250.83</v>
+        <v>274.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:44:50</t>
+          <t>05:46:25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="F29" t="n">
-        <v>5.33</v>
+        <v>6.06</v>
       </c>
       <c r="G29" t="n">
-        <v>309.1</v>
+        <v>321.6</v>
       </c>
       <c r="H29" t="n">
-        <v>55.2</v>
+        <v>79.7</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
-        <v>-48.54</v>
+        <v>-32.92</v>
       </c>
       <c r="K29" t="n">
-        <v>49.23</v>
+        <v>42.31</v>
       </c>
       <c r="L29" t="n">
-        <v>69.14</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:45:36</t>
+          <t>05:47:55</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.78</v>
+        <v>2.05</v>
       </c>
       <c r="F30" t="n">
-        <v>8.85</v>
+        <v>5.55</v>
       </c>
       <c r="G30" t="n">
-        <v>315.4</v>
+        <v>319.8</v>
       </c>
       <c r="H30" t="n">
-        <v>51.9</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.78</v>
+        <v>-37.36</v>
       </c>
       <c r="K30" t="n">
-        <v>44.04</v>
+        <v>-18.38</v>
       </c>
       <c r="L30" t="n">
-        <v>44.42</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:46:55</t>
+          <t>05:49:48</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="F31" t="n">
-        <v>8.26</v>
+        <v>7.66</v>
       </c>
       <c r="G31" t="n">
-        <v>307.8</v>
+        <v>307.3</v>
       </c>
       <c r="H31" t="n">
-        <v>52.9</v>
+        <v>79.7</v>
       </c>
       <c r="I31" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>86.2</v>
+        <v>-22.77</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.45</v>
+        <v>26.29</v>
       </c>
       <c r="L31" t="n">
-        <v>95.65000000000001</v>
+        <v>34.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:50:43</t>
+          <t>05:54:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="F32" t="n">
-        <v>4.68</v>
+        <v>6.64</v>
       </c>
       <c r="G32" t="n">
-        <v>312</v>
+        <v>327.1</v>
       </c>
       <c r="H32" t="n">
-        <v>51.1</v>
+        <v>40.7</v>
       </c>
       <c r="I32" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J32" t="n">
-        <v>-15.12</v>
+        <v>42.41</v>
       </c>
       <c r="K32" t="n">
-        <v>-62.01</v>
+        <v>-12.23</v>
       </c>
       <c r="L32" t="n">
-        <v>63.83</v>
+        <v>44.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:52:09</t>
+          <t>05:55:51</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="F33" t="n">
-        <v>6.46</v>
+        <v>3.96</v>
       </c>
       <c r="G33" t="n">
-        <v>319.5</v>
+        <v>306.9</v>
       </c>
       <c r="H33" t="n">
-        <v>50.6</v>
+        <v>54.1</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>89.68000000000001</v>
+        <v>-97.45</v>
       </c>
       <c r="K33" t="n">
-        <v>53.18</v>
+        <v>30.55</v>
       </c>
       <c r="L33" t="n">
-        <v>104.26</v>
+        <v>102.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:52:58</t>
+          <t>05:57:46</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.37</v>
+        <v>3.11</v>
       </c>
       <c r="F34" t="n">
-        <v>6.46</v>
+        <v>8.85</v>
       </c>
       <c r="G34" t="n">
-        <v>316.6</v>
+        <v>310.9</v>
       </c>
       <c r="H34" t="n">
-        <v>42.4</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>83.22</v>
+        <v>-69.77</v>
       </c>
       <c r="K34" t="n">
-        <v>-7.84</v>
+        <v>37.1</v>
       </c>
       <c r="L34" t="n">
-        <v>83.59</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>05:57:57</t>
+          <t>06:02:57</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="F35" t="n">
-        <v>5.29</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>304.6</v>
+        <v>334.6</v>
       </c>
       <c r="H35" t="n">
-        <v>50.6</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>48.77</v>
+        <v>-95.59</v>
       </c>
       <c r="K35" t="n">
-        <v>-79.72</v>
+        <v>-32.54</v>
       </c>
       <c r="L35" t="n">
-        <v>93.45999999999999</v>
+        <v>100.98</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>05:59:15</t>
+          <t>06:04:46</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="F36" t="n">
-        <v>5.87</v>
+        <v>7.03</v>
       </c>
       <c r="G36" t="n">
-        <v>305.4</v>
+        <v>310.7</v>
       </c>
       <c r="H36" t="n">
-        <v>46.8</v>
+        <v>58.9</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-23.64</v>
+        <v>-72.92</v>
       </c>
       <c r="K36" t="n">
-        <v>117.29</v>
+        <v>-28.07</v>
       </c>
       <c r="L36" t="n">
-        <v>119.65</v>
+        <v>78.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:00:47</t>
+          <t>06:07:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="F37" t="n">
-        <v>6.15</v>
+        <v>3.53</v>
       </c>
       <c r="G37" t="n">
-        <v>320.4</v>
+        <v>300</v>
       </c>
       <c r="H37" t="n">
-        <v>55.2</v>
+        <v>47.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-86.45999999999999</v>
+        <v>48.86</v>
       </c>
       <c r="K37" t="n">
-        <v>25.32</v>
+        <v>-91.91</v>
       </c>
       <c r="L37" t="n">
-        <v>90.09</v>
+        <v>104.09</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:04:23</t>
+          <t>06:11:48</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.78</v>
+        <v>2.85</v>
       </c>
       <c r="F38" t="n">
-        <v>7.22</v>
+        <v>6.18</v>
       </c>
       <c r="G38" t="n">
-        <v>310.1</v>
+        <v>314.1</v>
       </c>
       <c r="H38" t="n">
-        <v>54.7</v>
+        <v>62.6</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-95.44</v>
+        <v>140.79</v>
       </c>
       <c r="K38" t="n">
-        <v>-108.27</v>
+        <v>-82.26000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>144.33</v>
+        <v>163.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:05:50</t>
+          <t>06:13:20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.28</v>
+        <v>2.54</v>
       </c>
       <c r="F39" t="n">
-        <v>7.83</v>
+        <v>6.96</v>
       </c>
       <c r="G39" t="n">
-        <v>307.5</v>
+        <v>308.9</v>
       </c>
       <c r="H39" t="n">
-        <v>53.5</v>
+        <v>35.1</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J39" t="n">
-        <v>-256.56</v>
+        <v>70.97</v>
       </c>
       <c r="K39" t="n">
-        <v>56.46</v>
+        <v>81.70999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>262.7</v>
+        <v>108.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:07:37</t>
+          <t>06:16:04</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.43</v>
+        <v>1.99</v>
       </c>
       <c r="F40" t="n">
-        <v>6.96</v>
+        <v>6.19</v>
       </c>
       <c r="G40" t="n">
-        <v>324.9</v>
+        <v>307.3</v>
       </c>
       <c r="H40" t="n">
-        <v>50.1</v>
+        <v>41.4</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J40" t="n">
-        <v>35.03</v>
+        <v>-50.23</v>
       </c>
       <c r="K40" t="n">
-        <v>-166.59</v>
+        <v>-93.75</v>
       </c>
       <c r="L40" t="n">
-        <v>170.24</v>
+        <v>106.36</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:12:49</t>
+          <t>06:21:32</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.96</v>
+        <v>2.35</v>
       </c>
       <c r="F41" t="n">
-        <v>8.720000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G41" t="n">
-        <v>317.9</v>
+        <v>300.5</v>
       </c>
       <c r="H41" t="n">
-        <v>49.1</v>
+        <v>36.8</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-109.65</v>
+        <v>145.31</v>
       </c>
       <c r="K41" t="n">
-        <v>197.31</v>
+        <v>-119.44</v>
       </c>
       <c r="L41" t="n">
-        <v>225.73</v>
+        <v>188.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:14:34</t>
+          <t>06:23:51</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.47</v>
+        <v>3.99</v>
       </c>
       <c r="F42" t="n">
-        <v>7.87</v>
+        <v>8.85</v>
       </c>
       <c r="G42" t="n">
-        <v>308.2</v>
+        <v>308</v>
       </c>
       <c r="H42" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="I42" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>-269.03</v>
+        <v>-65.79000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-224.89</v>
+        <v>200.71</v>
       </c>
       <c r="L42" t="n">
-        <v>350.65</v>
+        <v>211.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:15:41</t>
+          <t>06:24:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="F43" t="n">
-        <v>8.85</v>
+        <v>5.68</v>
       </c>
       <c r="G43" t="n">
-        <v>293.2</v>
+        <v>315.3</v>
       </c>
       <c r="H43" t="n">
-        <v>55.8</v>
+        <v>70.7</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>211.47</v>
+        <v>-56.13</v>
       </c>
       <c r="K43" t="n">
-        <v>169.5</v>
+        <v>128.1</v>
       </c>
       <c r="L43" t="n">
-        <v>271.02</v>
+        <v>139.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:25:31</t>
+          <t>06:37:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="F44" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>308</v>
+        <v>317.8</v>
       </c>
       <c r="H44" t="n">
-        <v>56.7</v>
+        <v>45.6</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-81.38</v>
+        <v>25.37</v>
       </c>
       <c r="K44" t="n">
-        <v>13</v>
+        <v>35.51</v>
       </c>
       <c r="L44" t="n">
-        <v>82.41</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:27:45</t>
+          <t>06:39:27</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="F45" t="n">
-        <v>5.57</v>
+        <v>3.64</v>
       </c>
       <c r="G45" t="n">
-        <v>298.2</v>
+        <v>320.4</v>
       </c>
       <c r="H45" t="n">
-        <v>48.8</v>
+        <v>41.6</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>42.04</v>
+        <v>-9.06</v>
       </c>
       <c r="K45" t="n">
-        <v>27.75</v>
+        <v>-37.71</v>
       </c>
       <c r="L45" t="n">
-        <v>50.37</v>
+        <v>38.78</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:30:12</t>
+          <t>06:40:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="F46" t="n">
-        <v>6.96</v>
+        <v>7.15</v>
       </c>
       <c r="G46" t="n">
-        <v>307</v>
+        <v>297.5</v>
       </c>
       <c r="H46" t="n">
-        <v>51.3</v>
+        <v>54</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>24.74</v>
+        <v>-21.79</v>
       </c>
       <c r="K46" t="n">
-        <v>-49.99</v>
+        <v>25.63</v>
       </c>
       <c r="L46" t="n">
-        <v>55.78</v>
+        <v>33.64</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:36:03</t>
+          <t>06:45:24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="F47" t="n">
-        <v>4.92</v>
+        <v>8.85</v>
       </c>
       <c r="G47" t="n">
-        <v>317.2</v>
+        <v>312.6</v>
       </c>
       <c r="H47" t="n">
-        <v>60.5</v>
+        <v>35</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>-38.75</v>
+        <v>-38.55</v>
       </c>
       <c r="K47" t="n">
-        <v>74.93000000000001</v>
+        <v>-56.5</v>
       </c>
       <c r="L47" t="n">
-        <v>84.36</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:38:13</t>
+          <t>06:47:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.48</v>
+        <v>2.39</v>
       </c>
       <c r="F48" t="n">
         <v>8.85</v>
       </c>
       <c r="G48" t="n">
-        <v>311</v>
+        <v>314.8</v>
       </c>
       <c r="H48" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>84.14</v>
+        <v>-20.4</v>
       </c>
       <c r="K48" t="n">
-        <v>-51.98</v>
+        <v>44.74</v>
       </c>
       <c r="L48" t="n">
-        <v>98.90000000000001</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:39:51</t>
+          <t>06:49:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.73</v>
+        <v>2.47</v>
       </c>
       <c r="F49" t="n">
-        <v>8.85</v>
+        <v>4.79</v>
       </c>
       <c r="G49" t="n">
-        <v>310.7</v>
+        <v>318.8</v>
       </c>
       <c r="H49" t="n">
-        <v>54</v>
+        <v>90.2</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>-45.23</v>
+        <v>-58.37</v>
       </c>
       <c r="K49" t="n">
-        <v>-83.17</v>
+        <v>17.59</v>
       </c>
       <c r="L49" t="n">
-        <v>94.67</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:45:41</t>
+          <t>06:55:16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.69</v>
+        <v>2.43</v>
       </c>
       <c r="F50" t="n">
-        <v>7.6</v>
+        <v>6.53</v>
       </c>
       <c r="G50" t="n">
-        <v>323.7</v>
+        <v>325.4</v>
       </c>
       <c r="H50" t="n">
-        <v>52.5</v>
+        <v>93.7</v>
       </c>
       <c r="I50" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J50" t="n">
-        <v>-62.46</v>
+        <v>-29.01</v>
       </c>
       <c r="K50" t="n">
-        <v>74.66</v>
+        <v>-117.06</v>
       </c>
       <c r="L50" t="n">
-        <v>97.34</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:47:06</t>
+          <t>06:57:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.98</v>
+        <v>2.75</v>
       </c>
       <c r="F51" t="n">
-        <v>5.27</v>
+        <v>8.58</v>
       </c>
       <c r="G51" t="n">
-        <v>317.7</v>
+        <v>308.6</v>
       </c>
       <c r="H51" t="n">
-        <v>44.7</v>
+        <v>28.3</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
-        <v>9</v>
+        <v>-63.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-93.26000000000001</v>
+        <v>-59.45</v>
       </c>
       <c r="L51" t="n">
-        <v>93.69</v>
+        <v>87.14</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:49:20</t>
+          <t>06:58:30</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.51</v>
+        <v>2.22</v>
       </c>
       <c r="F52" t="n">
-        <v>7.08</v>
+        <v>7.06</v>
       </c>
       <c r="G52" t="n">
-        <v>304.4</v>
+        <v>296.6</v>
       </c>
       <c r="H52" t="n">
-        <v>52.9</v>
+        <v>57.6</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>97.89</v>
+        <v>56.67</v>
       </c>
       <c r="K52" t="n">
-        <v>127.23</v>
+        <v>-77.04000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>160.53</v>
+        <v>95.64</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>06:53:38</t>
+          <t>07:02:26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="F53" t="n">
-        <v>8.609999999999999</v>
+        <v>8.23</v>
       </c>
       <c r="G53" t="n">
-        <v>300</v>
+        <v>304.7</v>
       </c>
       <c r="H53" t="n">
-        <v>43.9</v>
+        <v>45.2</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>-43.61</v>
+        <v>-73.62</v>
       </c>
       <c r="K53" t="n">
-        <v>186.97</v>
+        <v>-109.97</v>
       </c>
       <c r="L53" t="n">
-        <v>191.99</v>
+        <v>132.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>06:56:17</t>
+          <t>07:04:06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.83</v>
+        <v>2.28</v>
       </c>
       <c r="F54" t="n">
-        <v>8.85</v>
+        <v>5.78</v>
       </c>
       <c r="G54" t="n">
-        <v>316.3</v>
+        <v>308</v>
       </c>
       <c r="H54" t="n">
-        <v>49.2</v>
+        <v>40.3</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>167.41</v>
+        <v>102.48</v>
       </c>
       <c r="K54" t="n">
-        <v>-45.04</v>
+        <v>-35.3</v>
       </c>
       <c r="L54" t="n">
-        <v>173.36</v>
+        <v>108.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>06:57:19</t>
+          <t>07:05:51</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.76</v>
+        <v>2.56</v>
       </c>
       <c r="F55" t="n">
         <v>8.85</v>
       </c>
       <c r="G55" t="n">
-        <v>294.5</v>
+        <v>312</v>
       </c>
       <c r="H55" t="n">
-        <v>51.1</v>
+        <v>72.8</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J55" t="n">
-        <v>181.43</v>
+        <v>89.64</v>
       </c>
       <c r="K55" t="n">
-        <v>-50.99</v>
+        <v>-158.96</v>
       </c>
       <c r="L55" t="n">
-        <v>188.46</v>
+        <v>182.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:02:51</t>
+          <t>07:10:41</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="F56" t="n">
-        <v>8.85</v>
+        <v>7.03</v>
       </c>
       <c r="G56" t="n">
-        <v>303.3</v>
+        <v>305.8</v>
       </c>
       <c r="H56" t="n">
-        <v>51.9</v>
+        <v>65</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>248.87</v>
+        <v>-135.37</v>
       </c>
       <c r="K56" t="n">
-        <v>140.9</v>
+        <v>-63.51</v>
       </c>
       <c r="L56" t="n">
-        <v>285.98</v>
+        <v>149.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:04:27</t>
+          <t>07:11:31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="F57" t="n">
         <v>8.85</v>
       </c>
       <c r="G57" t="n">
-        <v>316.6</v>
+        <v>315</v>
       </c>
       <c r="H57" t="n">
-        <v>52.4</v>
+        <v>79.2</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-326.74</v>
+        <v>146.94</v>
       </c>
       <c r="K57" t="n">
-        <v>89.63</v>
+        <v>85.58</v>
       </c>
       <c r="L57" t="n">
-        <v>338.81</v>
+        <v>170.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:06:29</t>
+          <t>07:13:46</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="F58" t="n">
-        <v>7.22</v>
+        <v>8.85</v>
       </c>
       <c r="G58" t="n">
-        <v>296.4</v>
+        <v>319.6</v>
       </c>
       <c r="H58" t="n">
-        <v>44.9</v>
+        <v>18.7</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>17.04</v>
+        <v>-139.41</v>
       </c>
       <c r="K58" t="n">
-        <v>-308.04</v>
+        <v>96.69</v>
       </c>
       <c r="L58" t="n">
-        <v>308.51</v>
+        <v>169.66</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:18:31</t>
+          <t>07:25:38</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
       <c r="F59" t="n">
-        <v>6.87</v>
+        <v>5.77</v>
       </c>
       <c r="G59" t="n">
-        <v>299.9</v>
+        <v>300.8</v>
       </c>
       <c r="H59" t="n">
-        <v>55.3</v>
+        <v>35.3</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>-27.03</v>
+        <v>-6.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-78.17</v>
+        <v>-38.99</v>
       </c>
       <c r="L59" t="n">
-        <v>82.70999999999999</v>
+        <v>39.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:21:11</t>
+          <t>07:27:17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="F60" t="n">
-        <v>8.85</v>
+        <v>8.77</v>
       </c>
       <c r="G60" t="n">
-        <v>314.9</v>
+        <v>321.2</v>
       </c>
       <c r="H60" t="n">
-        <v>55.3</v>
+        <v>44.4</v>
       </c>
       <c r="I60" t="n">
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-28.55</v>
+        <v>-19.99</v>
       </c>
       <c r="K60" t="n">
-        <v>61.18</v>
+        <v>-23.39</v>
       </c>
       <c r="L60" t="n">
-        <v>67.51000000000001</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:23:12</t>
+          <t>07:29:19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.53</v>
+        <v>2.76</v>
       </c>
       <c r="F61" t="n">
         <v>8.85</v>
       </c>
       <c r="G61" t="n">
-        <v>313.9</v>
+        <v>300.5</v>
       </c>
       <c r="H61" t="n">
-        <v>43.6</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>-69.70999999999999</v>
+        <v>-16.13</v>
       </c>
       <c r="K61" t="n">
-        <v>-49.26</v>
+        <v>6.14</v>
       </c>
       <c r="L61" t="n">
-        <v>85.36</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:27:28</t>
+          <t>07:33:24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.34</v>
+        <v>2.97</v>
       </c>
       <c r="F62" t="n">
         <v>8.85</v>
       </c>
       <c r="G62" t="n">
-        <v>298.1</v>
+        <v>303.9</v>
       </c>
       <c r="H62" t="n">
-        <v>57.7</v>
+        <v>56.6</v>
       </c>
       <c r="I62" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>-83.65000000000001</v>
+        <v>-64.72</v>
       </c>
       <c r="K62" t="n">
-        <v>74.04000000000001</v>
+        <v>42.53</v>
       </c>
       <c r="L62" t="n">
-        <v>111.71</v>
+        <v>77.44</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:29:22</t>
+          <t>07:35:08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="F63" t="n">
-        <v>8.67</v>
+        <v>7.01</v>
       </c>
       <c r="G63" t="n">
-        <v>314.9</v>
+        <v>314.6</v>
       </c>
       <c r="H63" t="n">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-99.25</v>
+        <v>39.27</v>
       </c>
       <c r="K63" t="n">
-        <v>49.44</v>
+        <v>52.74</v>
       </c>
       <c r="L63" t="n">
-        <v>110.88</v>
+        <v>65.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:31:05</t>
+          <t>07:36:46</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="F64" t="n">
-        <v>7.39</v>
+        <v>6.07</v>
       </c>
       <c r="G64" t="n">
-        <v>312.6</v>
+        <v>320.2</v>
       </c>
       <c r="H64" t="n">
-        <v>54.7</v>
+        <v>17</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>39.86</v>
+        <v>52.42</v>
       </c>
       <c r="K64" t="n">
-        <v>57.15</v>
+        <v>-39.18</v>
       </c>
       <c r="L64" t="n">
-        <v>69.68000000000001</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:35:31</t>
+          <t>07:41:34</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.71</v>
+        <v>2.48</v>
       </c>
       <c r="F65" t="n">
-        <v>7.25</v>
+        <v>8.85</v>
       </c>
       <c r="G65" t="n">
-        <v>309.8</v>
+        <v>320.7</v>
       </c>
       <c r="H65" t="n">
-        <v>44.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J65" t="n">
-        <v>123.18</v>
+        <v>57.22</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.63</v>
+        <v>70.53</v>
       </c>
       <c r="L65" t="n">
-        <v>123.26</v>
+        <v>90.81999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:36:16</t>
+          <t>07:42:58</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.74</v>
+        <v>2.49</v>
       </c>
       <c r="F66" t="n">
-        <v>7.83</v>
+        <v>5.09</v>
       </c>
       <c r="G66" t="n">
-        <v>330.6</v>
+        <v>296.1</v>
       </c>
       <c r="H66" t="n">
-        <v>47.7</v>
+        <v>41.7</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.56</v>
+        <v>-92.72</v>
       </c>
       <c r="K66" t="n">
-        <v>102.58</v>
+        <v>24.41</v>
       </c>
       <c r="L66" t="n">
-        <v>102.64</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:38:02</t>
+          <t>07:44:19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="F67" t="n">
-        <v>7.54</v>
+        <v>7.21</v>
       </c>
       <c r="G67" t="n">
-        <v>306.3</v>
+        <v>325.2</v>
       </c>
       <c r="H67" t="n">
-        <v>41.9</v>
+        <v>26.4</v>
       </c>
       <c r="I67" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J67" t="n">
-        <v>50.07</v>
+        <v>4.82</v>
       </c>
       <c r="K67" t="n">
-        <v>135.66</v>
+        <v>82.3</v>
       </c>
       <c r="L67" t="n">
-        <v>144.6</v>
+        <v>82.44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:42:45</t>
+          <t>07:48:15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="F68" t="n">
-        <v>7.24</v>
+        <v>7.85</v>
       </c>
       <c r="G68" t="n">
-        <v>310.8</v>
+        <v>315.6</v>
       </c>
       <c r="H68" t="n">
-        <v>57.5</v>
+        <v>98.7</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J68" t="n">
-        <v>141.01</v>
+        <v>146</v>
       </c>
       <c r="K68" t="n">
-        <v>-60.13</v>
+        <v>44.34</v>
       </c>
       <c r="L68" t="n">
-        <v>153.29</v>
+        <v>152.58</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:43:38</t>
+          <t>07:49:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="F69" t="n">
         <v>8.85</v>
       </c>
       <c r="G69" t="n">
-        <v>307.4</v>
+        <v>320.3</v>
       </c>
       <c r="H69" t="n">
-        <v>57.4</v>
+        <v>50.7</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>197.45</v>
+        <v>143.63</v>
       </c>
       <c r="K69" t="n">
-        <v>15.2</v>
+        <v>-2.52</v>
       </c>
       <c r="L69" t="n">
-        <v>198.04</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:44:30</t>
+          <t>07:50:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="F70" t="n">
-        <v>7.2</v>
+        <v>8.85</v>
       </c>
       <c r="G70" t="n">
-        <v>300.4</v>
+        <v>294.8</v>
       </c>
       <c r="H70" t="n">
-        <v>52.8</v>
+        <v>49.4</v>
       </c>
       <c r="I70" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J70" t="n">
-        <v>-150.26</v>
+        <v>0.26</v>
       </c>
       <c r="K70" t="n">
-        <v>46.7</v>
+        <v>-128.59</v>
       </c>
       <c r="L70" t="n">
-        <v>157.35</v>
+        <v>128.59</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:49:24</t>
+          <t>07:56:10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="F71" t="n">
-        <v>8.01</v>
+        <v>8.65</v>
       </c>
       <c r="G71" t="n">
-        <v>309.3</v>
+        <v>302.8</v>
       </c>
       <c r="H71" t="n">
-        <v>49.4</v>
+        <v>36.7</v>
       </c>
       <c r="I71" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-199.93</v>
+        <v>-184.67</v>
       </c>
       <c r="K71" t="n">
-        <v>112.91</v>
+        <v>-89.06</v>
       </c>
       <c r="L71" t="n">
-        <v>229.61</v>
+        <v>205.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:51:42</t>
+          <t>07:58:29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.85</v>
+        <v>2.36</v>
       </c>
       <c r="F72" t="n">
-        <v>8.85</v>
+        <v>3.39</v>
       </c>
       <c r="G72" t="n">
-        <v>312.5</v>
+        <v>313.6</v>
       </c>
       <c r="H72" t="n">
-        <v>55.3</v>
+        <v>70.7</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>194.8</v>
+        <v>200.52</v>
       </c>
       <c r="K72" t="n">
-        <v>-201.3</v>
+        <v>20.54</v>
       </c>
       <c r="L72" t="n">
-        <v>280.13</v>
+        <v>201.57</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:53:12</t>
+          <t>07:59:41</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.24</v>
+        <v>2.52</v>
       </c>
       <c r="F73" t="n">
-        <v>8.85</v>
+        <v>7.38</v>
       </c>
       <c r="G73" t="n">
-        <v>318.6</v>
+        <v>299</v>
       </c>
       <c r="H73" t="n">
-        <v>46.4</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J73" t="n">
-        <v>-203.03</v>
+        <v>42.35</v>
       </c>
       <c r="K73" t="n">
-        <v>158.02</v>
+        <v>144.45</v>
       </c>
       <c r="L73" t="n">
-        <v>257.28</v>
+        <v>150.53</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:01:59</t>
+          <t>08:08:17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.69</v>
+        <v>2.82</v>
       </c>
       <c r="F74" t="n">
-        <v>8.85</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>308.9</v>
+        <v>312.8</v>
       </c>
       <c r="H74" t="n">
-        <v>57.2</v>
+        <v>26.8</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>68.95999999999999</v>
+        <v>-15.98</v>
       </c>
       <c r="K74" t="n">
-        <v>0.19</v>
+        <v>45.76</v>
       </c>
       <c r="L74" t="n">
-        <v>68.95999999999999</v>
+        <v>48.47</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:04:25</t>
+          <t>08:10:23</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="F75" t="n">
         <v>8.85</v>
       </c>
       <c r="G75" t="n">
-        <v>312.9</v>
+        <v>301.8</v>
       </c>
       <c r="H75" t="n">
-        <v>50.3</v>
+        <v>33.1</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-93.23</v>
+        <v>19.19</v>
       </c>
       <c r="K75" t="n">
-        <v>-22.98</v>
+        <v>42.16</v>
       </c>
       <c r="L75" t="n">
-        <v>96.02</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:05:41</t>
+          <t>08:13:04</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.14</v>
+        <v>2.63</v>
       </c>
       <c r="F76" t="n">
-        <v>7.78</v>
+        <v>8.85</v>
       </c>
       <c r="G76" t="n">
-        <v>319</v>
+        <v>310.4</v>
       </c>
       <c r="H76" t="n">
-        <v>51.6</v>
+        <v>53</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>26.94</v>
+        <v>-31.2</v>
       </c>
       <c r="K76" t="n">
-        <v>-61.51</v>
+        <v>18.64</v>
       </c>
       <c r="L76" t="n">
-        <v>67.15000000000001</v>
+        <v>36.34</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:09:23</t>
+          <t>08:18:39</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="F77" t="n">
-        <v>6.82</v>
+        <v>8</v>
       </c>
       <c r="G77" t="n">
-        <v>302.6</v>
+        <v>305.5</v>
       </c>
       <c r="H77" t="n">
-        <v>49.7</v>
+        <v>43.7</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-52.54</v>
+        <v>28.98</v>
       </c>
       <c r="K77" t="n">
-        <v>63.32</v>
+        <v>71.34</v>
       </c>
       <c r="L77" t="n">
-        <v>82.28</v>
+        <v>77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:11:20</t>
+          <t>08:20:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="F78" t="n">
-        <v>6.62</v>
+        <v>7.56</v>
       </c>
       <c r="G78" t="n">
-        <v>316.7</v>
+        <v>323</v>
       </c>
       <c r="H78" t="n">
-        <v>49.6</v>
+        <v>52.2</v>
       </c>
       <c r="I78" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J78" t="n">
-        <v>-27.39</v>
+        <v>22.06</v>
       </c>
       <c r="K78" t="n">
-        <v>-134.04</v>
+        <v>47.14</v>
       </c>
       <c r="L78" t="n">
-        <v>136.81</v>
+        <v>52.04</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:13:04</t>
+          <t>08:21:49</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="F79" t="n">
-        <v>6.18</v>
+        <v>8.85</v>
       </c>
       <c r="G79" t="n">
-        <v>310.5</v>
+        <v>307.3</v>
       </c>
       <c r="H79" t="n">
-        <v>54.4</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-93.81999999999999</v>
+        <v>-54.24</v>
       </c>
       <c r="K79" t="n">
-        <v>-15.96</v>
+        <v>27.05</v>
       </c>
       <c r="L79" t="n">
-        <v>95.17</v>
+        <v>60.61</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:17:13</t>
+          <t>08:24:45</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.19</v>
+        <v>2.89</v>
       </c>
       <c r="F80" t="n">
-        <v>4.99</v>
+        <v>8.85</v>
       </c>
       <c r="G80" t="n">
-        <v>314.1</v>
+        <v>309.1</v>
       </c>
       <c r="H80" t="n">
-        <v>56.2</v>
+        <v>36.1</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J80" t="n">
-        <v>-54.52</v>
+        <v>21.16</v>
       </c>
       <c r="K80" t="n">
-        <v>-95.95</v>
+        <v>92.91</v>
       </c>
       <c r="L80" t="n">
-        <v>110.36</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:18:15</t>
+          <t>08:26:26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.41</v>
+        <v>2.69</v>
       </c>
       <c r="F81" t="n">
-        <v>8.85</v>
+        <v>7.33</v>
       </c>
       <c r="G81" t="n">
-        <v>309.3</v>
+        <v>316.9</v>
       </c>
       <c r="H81" t="n">
-        <v>49.6</v>
+        <v>37.5</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>154.84</v>
+        <v>47.7</v>
       </c>
       <c r="K81" t="n">
-        <v>107.52</v>
+        <v>83.59</v>
       </c>
       <c r="L81" t="n">
-        <v>188.51</v>
+        <v>96.23999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:20:36</t>
+          <t>08:28:51</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.73</v>
+        <v>2.01</v>
       </c>
       <c r="F82" t="n">
-        <v>8.85</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>307.5</v>
+        <v>307.2</v>
       </c>
       <c r="H82" t="n">
-        <v>53.1</v>
+        <v>37.7</v>
       </c>
       <c r="I82" t="n">
         <v>16</v>
       </c>
       <c r="J82" t="n">
-        <v>135.82</v>
+        <v>-48.1</v>
       </c>
       <c r="K82" t="n">
-        <v>18.77</v>
+        <v>54.07</v>
       </c>
       <c r="L82" t="n">
-        <v>137.11</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:26:27</t>
+          <t>08:34:25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F83" t="n">
         <v>8.85</v>
       </c>
       <c r="G83" t="n">
-        <v>312.5</v>
+        <v>308</v>
       </c>
       <c r="H83" t="n">
-        <v>63.9</v>
+        <v>8.5</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J83" t="n">
-        <v>-69.37</v>
+        <v>121.16</v>
       </c>
       <c r="K83" t="n">
-        <v>241.36</v>
+        <v>-96.67</v>
       </c>
       <c r="L83" t="n">
-        <v>251.13</v>
+        <v>155</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:28:48</t>
+          <t>08:35:23</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.37</v>
+        <v>2.73</v>
       </c>
       <c r="F84" t="n">
         <v>8.85</v>
       </c>
       <c r="G84" t="n">
-        <v>309.9</v>
+        <v>317.4</v>
       </c>
       <c r="H84" t="n">
-        <v>50</v>
+        <v>44.5</v>
       </c>
       <c r="I84" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-116.17</v>
+        <v>73.89</v>
       </c>
       <c r="K84" t="n">
-        <v>-167.93</v>
+        <v>117.07</v>
       </c>
       <c r="L84" t="n">
-        <v>204.2</v>
+        <v>138.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:29:25</t>
+          <t>08:37:55</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="F85" t="n">
-        <v>7.89</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>308.6</v>
+        <v>303.5</v>
       </c>
       <c r="H85" t="n">
-        <v>46.5</v>
+        <v>46.3</v>
       </c>
       <c r="I85" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J85" t="n">
-        <v>-164.9</v>
+        <v>-102.44</v>
       </c>
       <c r="K85" t="n">
-        <v>-82.01000000000001</v>
+        <v>61.98</v>
       </c>
       <c r="L85" t="n">
-        <v>184.16</v>
+        <v>119.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:34:50</t>
+          <t>08:43:20</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="F86" t="n">
-        <v>8.24</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>312.5</v>
+        <v>319.4</v>
       </c>
       <c r="H86" t="n">
-        <v>59.6</v>
+        <v>23</v>
       </c>
       <c r="I86" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J86" t="n">
-        <v>139.24</v>
+        <v>-208.32</v>
       </c>
       <c r="K86" t="n">
-        <v>220.49</v>
+        <v>27.7</v>
       </c>
       <c r="L86" t="n">
-        <v>260.78</v>
+        <v>210.16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:36:41</t>
+          <t>08:44:15</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.56</v>
+        <v>3.03</v>
       </c>
       <c r="F87" t="n">
-        <v>8.09</v>
+        <v>6.6</v>
       </c>
       <c r="G87" t="n">
-        <v>313.6</v>
+        <v>306.7</v>
       </c>
       <c r="H87" t="n">
-        <v>53.3</v>
+        <v>51.7</v>
       </c>
       <c r="I87" t="n">
         <v>20</v>
       </c>
       <c r="J87" t="n">
-        <v>-164.24</v>
+        <v>165.18</v>
       </c>
       <c r="K87" t="n">
-        <v>198.2</v>
+        <v>-238.46</v>
       </c>
       <c r="L87" t="n">
-        <v>257.41</v>
+        <v>290.09</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:38:59</t>
+          <t>08:46:31</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.74</v>
+        <v>2.61</v>
       </c>
       <c r="F88" t="n">
-        <v>8.32</v>
+        <v>7.59</v>
       </c>
       <c r="G88" t="n">
-        <v>316.7</v>
+        <v>318.3</v>
       </c>
       <c r="H88" t="n">
-        <v>49.7</v>
+        <v>38.8</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J88" t="n">
-        <v>-173.05</v>
+        <v>-41.07</v>
       </c>
       <c r="K88" t="n">
-        <v>258.74</v>
+        <v>-259.43</v>
       </c>
       <c r="L88" t="n">
-        <v>311.28</v>
+        <v>262.66</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.22</v>
+        <v>2.59</v>
       </c>
       <c r="F14" t="n">
-        <v>5.83</v>
+        <v>8.85</v>
       </c>
       <c r="G14" t="n">
-        <v>319.1</v>
+        <v>313.3</v>
       </c>
       <c r="H14" t="n">
-        <v>89.09999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.46</v>
+        <v>-10.75</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>-43.89</v>
       </c>
       <c r="L14" t="n">
-        <v>32.31</v>
+        <v>45.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05:02:02</t>
+          <t>05:02:08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="F15" t="n">
-        <v>8.85</v>
+        <v>7.44</v>
       </c>
       <c r="G15" t="n">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H15" t="n">
-        <v>38.9</v>
+        <v>42.2</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-25.64</v>
+        <v>34.12</v>
       </c>
       <c r="K15" t="n">
-        <v>27.87</v>
+        <v>22.87</v>
       </c>
       <c r="L15" t="n">
-        <v>37.87</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05:03:02</t>
+          <t>05:03:39</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="F16" t="n">
-        <v>3.53</v>
+        <v>6.69</v>
       </c>
       <c r="G16" t="n">
-        <v>307.4</v>
+        <v>310.5</v>
       </c>
       <c r="H16" t="n">
-        <v>33.5</v>
+        <v>40.7</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-36.72</v>
+        <v>7.52</v>
       </c>
       <c r="K16" t="n">
-        <v>13.76</v>
+        <v>-31.77</v>
       </c>
       <c r="L16" t="n">
-        <v>39.22</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05:07:57</t>
+          <t>05:08:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.09</v>
+        <v>2.22</v>
       </c>
       <c r="F17" t="n">
-        <v>5.71</v>
+        <v>8.85</v>
       </c>
       <c r="G17" t="n">
-        <v>319.2</v>
+        <v>308.6</v>
       </c>
       <c r="H17" t="n">
-        <v>38.2</v>
+        <v>43.1</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>55.93</v>
+        <v>-30.07</v>
       </c>
       <c r="K17" t="n">
-        <v>-13.75</v>
+        <v>45.85</v>
       </c>
       <c r="L17" t="n">
-        <v>57.6</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05:08:54</t>
+          <t>05:10:20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.14</v>
+        <v>2.51</v>
       </c>
       <c r="F18" t="n">
         <v>8.85</v>
       </c>
       <c r="G18" t="n">
-        <v>314.2</v>
+        <v>328.7</v>
       </c>
       <c r="H18" t="n">
-        <v>40.1</v>
+        <v>76.2</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J18" t="n">
-        <v>65.63</v>
+        <v>-7.75</v>
       </c>
       <c r="K18" t="n">
-        <v>-61.82</v>
+        <v>77.41</v>
       </c>
       <c r="L18" t="n">
-        <v>90.16</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05:11:02</t>
+          <t>05:12:18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
       <c r="F19" t="n">
-        <v>7.38</v>
+        <v>5.65</v>
       </c>
       <c r="G19" t="n">
-        <v>317.6</v>
+        <v>305.2</v>
       </c>
       <c r="H19" t="n">
-        <v>61.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.12</v>
+        <v>-78.93000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-4.33</v>
+        <v>12.66</v>
       </c>
       <c r="L19" t="n">
-        <v>61.27</v>
+        <v>79.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05:15:03</t>
+          <t>05:16:20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.07</v>
+        <v>2.29</v>
       </c>
       <c r="F20" t="n">
-        <v>7.3</v>
+        <v>8.85</v>
       </c>
       <c r="G20" t="n">
-        <v>315.6</v>
+        <v>302.8</v>
       </c>
       <c r="H20" t="n">
-        <v>61.6</v>
+        <v>67</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>-91.72</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.66</v>
+        <v>-99.18000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>104.78</v>
+        <v>99.56</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05:16:56</t>
+          <t>05:17:45</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="F21" t="n">
-        <v>4.74</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>309.9</v>
+        <v>311</v>
       </c>
       <c r="H21" t="n">
-        <v>96.40000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J21" t="n">
-        <v>83.28</v>
+        <v>-85.79000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.53</v>
+        <v>-17.3</v>
       </c>
       <c r="L21" t="n">
-        <v>85.54000000000001</v>
+        <v>87.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05:19:11</t>
+          <t>05:19:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.92</v>
+        <v>2.11</v>
       </c>
       <c r="F22" t="n">
-        <v>5.4</v>
+        <v>5.14</v>
       </c>
       <c r="G22" t="n">
-        <v>310.2</v>
+        <v>315.5</v>
       </c>
       <c r="H22" t="n">
-        <v>56.5</v>
+        <v>32.4</v>
       </c>
       <c r="I22" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-84.55</v>
+        <v>6.64</v>
       </c>
       <c r="K22" t="n">
-        <v>17.98</v>
+        <v>-109.11</v>
       </c>
       <c r="L22" t="n">
-        <v>86.44</v>
+        <v>109.31</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05:23:45</t>
+          <t>05:25:04</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="F23" t="n">
-        <v>8.85</v>
+        <v>6.87</v>
       </c>
       <c r="G23" t="n">
-        <v>303.8</v>
+        <v>310.5</v>
       </c>
       <c r="H23" t="n">
-        <v>94</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>137.16</v>
+        <v>121.87</v>
       </c>
       <c r="K23" t="n">
-        <v>-27.54</v>
+        <v>42.71</v>
       </c>
       <c r="L23" t="n">
-        <v>139.9</v>
+        <v>129.14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05:26:10</t>
+          <t>05:25:53</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="F24" t="n">
-        <v>3.22</v>
+        <v>6.45</v>
       </c>
       <c r="G24" t="n">
-        <v>307.8</v>
+        <v>308.2</v>
       </c>
       <c r="H24" t="n">
-        <v>22.7</v>
+        <v>72.7</v>
       </c>
       <c r="I24" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J24" t="n">
-        <v>-137.24</v>
+        <v>-32.3</v>
       </c>
       <c r="K24" t="n">
-        <v>16.64</v>
+        <v>-202.43</v>
       </c>
       <c r="L24" t="n">
-        <v>138.24</v>
+        <v>204.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>05:28:09</t>
+          <t>05:28:18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.93</v>
+        <v>2.32</v>
       </c>
       <c r="F25" t="n">
-        <v>7.65</v>
+        <v>7.84</v>
       </c>
       <c r="G25" t="n">
-        <v>303</v>
+        <v>308.8</v>
       </c>
       <c r="H25" t="n">
-        <v>68.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="I25" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>-168.2</v>
+        <v>104.99</v>
       </c>
       <c r="K25" t="n">
-        <v>-23.48</v>
+        <v>11.47</v>
       </c>
       <c r="L25" t="n">
-        <v>169.83</v>
+        <v>105.62</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>05:32:44</t>
+          <t>05:32:12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="F26" t="n">
-        <v>5.29</v>
+        <v>7.65</v>
       </c>
       <c r="G26" t="n">
-        <v>304.3</v>
+        <v>317.5</v>
       </c>
       <c r="H26" t="n">
-        <v>85.59999999999999</v>
+        <v>58.7</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>-201.94</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-51.78</v>
+        <v>194.98</v>
       </c>
       <c r="L26" t="n">
-        <v>208.47</v>
+        <v>195.17</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>05:35:06</t>
+          <t>05:33:15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="F27" t="n">
-        <v>8.17</v>
+        <v>5.56</v>
       </c>
       <c r="G27" t="n">
-        <v>301.7</v>
+        <v>303.4</v>
       </c>
       <c r="H27" t="n">
-        <v>47.7</v>
+        <v>48.3</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>12.23</v>
+        <v>207.39</v>
       </c>
       <c r="K27" t="n">
-        <v>-136.48</v>
+        <v>-40.5</v>
       </c>
       <c r="L27" t="n">
-        <v>137.03</v>
+        <v>211.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>05:36:06</t>
+          <t>05:35:12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.51</v>
+        <v>2.94</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>8.85</v>
       </c>
       <c r="G28" t="n">
-        <v>308.5</v>
+        <v>296.8</v>
       </c>
       <c r="H28" t="n">
-        <v>66.2</v>
+        <v>90.3</v>
       </c>
       <c r="I28" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-68.73</v>
+        <v>-123.42</v>
       </c>
       <c r="K28" t="n">
-        <v>265.66</v>
+        <v>102.57</v>
       </c>
       <c r="L28" t="n">
-        <v>274.41</v>
+        <v>160.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>05:46:25</t>
+          <t>05:45:15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.63</v>
+        <v>2.1</v>
       </c>
       <c r="F29" t="n">
-        <v>6.06</v>
+        <v>4.37</v>
       </c>
       <c r="G29" t="n">
-        <v>321.6</v>
+        <v>313.9</v>
       </c>
       <c r="H29" t="n">
-        <v>79.7</v>
+        <v>77</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.92</v>
+        <v>-12.87</v>
       </c>
       <c r="K29" t="n">
-        <v>42.31</v>
+        <v>25.46</v>
       </c>
       <c r="L29" t="n">
-        <v>53.6</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>05:47:55</t>
+          <t>05:46:33</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="F30" t="n">
-        <v>5.55</v>
+        <v>7.06</v>
       </c>
       <c r="G30" t="n">
-        <v>319.8</v>
+        <v>322.7</v>
       </c>
       <c r="H30" t="n">
-        <v>76.40000000000001</v>
+        <v>34.5</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>-37.36</v>
+        <v>-5.3</v>
       </c>
       <c r="K30" t="n">
-        <v>-18.38</v>
+        <v>-38.61</v>
       </c>
       <c r="L30" t="n">
-        <v>41.63</v>
+        <v>38.98</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>05:49:48</t>
+          <t>05:48:18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="F31" t="n">
-        <v>7.66</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>307.3</v>
+        <v>302.9</v>
       </c>
       <c r="H31" t="n">
-        <v>79.7</v>
+        <v>100</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J31" t="n">
-        <v>-22.77</v>
+        <v>-10.39</v>
       </c>
       <c r="K31" t="n">
-        <v>26.29</v>
+        <v>14.16</v>
       </c>
       <c r="L31" t="n">
-        <v>34.78</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>05:54:50</t>
+          <t>05:52:50</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="F32" t="n">
-        <v>6.64</v>
+        <v>7.11</v>
       </c>
       <c r="G32" t="n">
-        <v>327.1</v>
+        <v>319.4</v>
       </c>
       <c r="H32" t="n">
-        <v>40.7</v>
+        <v>100</v>
       </c>
       <c r="I32" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="J32" t="n">
-        <v>42.41</v>
+        <v>23.28</v>
       </c>
       <c r="K32" t="n">
-        <v>-12.23</v>
+        <v>93.14</v>
       </c>
       <c r="L32" t="n">
-        <v>44.14</v>
+        <v>96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>05:55:51</t>
+          <t>05:54:32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.13</v>
+        <v>2.65</v>
       </c>
       <c r="F33" t="n">
-        <v>3.96</v>
+        <v>8.75</v>
       </c>
       <c r="G33" t="n">
-        <v>306.9</v>
+        <v>322.3</v>
       </c>
       <c r="H33" t="n">
-        <v>54.1</v>
+        <v>30.4</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>-97.45</v>
+        <v>-25.13</v>
       </c>
       <c r="K33" t="n">
-        <v>30.55</v>
+        <v>64.63</v>
       </c>
       <c r="L33" t="n">
-        <v>102.13</v>
+        <v>69.34999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>05:57:46</t>
+          <t>05:56:31</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.11</v>
+        <v>2.57</v>
       </c>
       <c r="F34" t="n">
-        <v>8.85</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>310.9</v>
+        <v>306.4</v>
       </c>
       <c r="H34" t="n">
-        <v>64.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J34" t="n">
-        <v>-69.77</v>
+        <v>-17.95</v>
       </c>
       <c r="K34" t="n">
-        <v>37.1</v>
+        <v>61.14</v>
       </c>
       <c r="L34" t="n">
-        <v>79.02</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:02:57</t>
+          <t>06:00:55</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.52</v>
+        <v>2.21</v>
       </c>
       <c r="F35" t="n">
-        <v>8.720000000000001</v>
+        <v>8.85</v>
       </c>
       <c r="G35" t="n">
-        <v>334.6</v>
+        <v>310.8</v>
       </c>
       <c r="H35" t="n">
-        <v>64.09999999999999</v>
+        <v>60.7</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-95.59</v>
+        <v>31.33</v>
       </c>
       <c r="K35" t="n">
-        <v>-32.54</v>
+        <v>-81.43000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>100.98</v>
+        <v>87.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:04:46</t>
+          <t>06:03:06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.52</v>
+        <v>2.47</v>
       </c>
       <c r="F36" t="n">
-        <v>7.03</v>
+        <v>6.59</v>
       </c>
       <c r="G36" t="n">
-        <v>310.7</v>
+        <v>315.1</v>
       </c>
       <c r="H36" t="n">
-        <v>58.9</v>
+        <v>67.8</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>-72.92</v>
+        <v>-90.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-28.07</v>
+        <v>19.42</v>
       </c>
       <c r="L36" t="n">
-        <v>78.14</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>06:07:07</t>
+          <t>06:04:04</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="F37" t="n">
-        <v>3.53</v>
+        <v>5.63</v>
       </c>
       <c r="G37" t="n">
-        <v>300</v>
+        <v>313.7</v>
       </c>
       <c r="H37" t="n">
-        <v>47.5</v>
+        <v>57.6</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J37" t="n">
-        <v>48.86</v>
+        <v>82.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-91.91</v>
+        <v>-21.97</v>
       </c>
       <c r="L37" t="n">
-        <v>104.09</v>
+        <v>84.92</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>06:11:48</t>
+          <t>06:08:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.85</v>
+        <v>2.07</v>
       </c>
       <c r="F38" t="n">
-        <v>6.18</v>
+        <v>6.88</v>
       </c>
       <c r="G38" t="n">
-        <v>314.1</v>
+        <v>318.6</v>
       </c>
       <c r="H38" t="n">
-        <v>62.6</v>
+        <v>90</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>140.79</v>
+        <v>-27.95</v>
       </c>
       <c r="K38" t="n">
-        <v>-82.26000000000001</v>
+        <v>-135.21</v>
       </c>
       <c r="L38" t="n">
-        <v>163.06</v>
+        <v>138.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>06:13:20</t>
+          <t>06:10:47</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.54</v>
+        <v>2.33</v>
       </c>
       <c r="F39" t="n">
-        <v>6.96</v>
+        <v>5.08</v>
       </c>
       <c r="G39" t="n">
-        <v>308.9</v>
+        <v>317.3</v>
       </c>
       <c r="H39" t="n">
-        <v>35.1</v>
+        <v>61.9</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J39" t="n">
-        <v>70.97</v>
+        <v>137.06</v>
       </c>
       <c r="K39" t="n">
-        <v>81.70999999999999</v>
+        <v>-16.59</v>
       </c>
       <c r="L39" t="n">
-        <v>108.22</v>
+        <v>138.06</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>06:16:04</t>
+          <t>06:12:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="F40" t="n">
-        <v>6.19</v>
+        <v>8.85</v>
       </c>
       <c r="G40" t="n">
-        <v>307.3</v>
+        <v>320.2</v>
       </c>
       <c r="H40" t="n">
-        <v>41.4</v>
+        <v>60.9</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J40" t="n">
-        <v>-50.23</v>
+        <v>154.59</v>
       </c>
       <c r="K40" t="n">
-        <v>-93.75</v>
+        <v>-42.1</v>
       </c>
       <c r="L40" t="n">
-        <v>106.36</v>
+        <v>160.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>06:21:32</t>
+          <t>06:15:36</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="F41" t="n">
-        <v>8.85</v>
+        <v>5.6</v>
       </c>
       <c r="G41" t="n">
-        <v>300.5</v>
+        <v>300.6</v>
       </c>
       <c r="H41" t="n">
-        <v>36.8</v>
+        <v>65.3</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>145.31</v>
+        <v>-138.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-119.44</v>
+        <v>-156.79</v>
       </c>
       <c r="L41" t="n">
-        <v>188.1</v>
+        <v>209.47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>06:23:51</t>
+          <t>06:17:29</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
       <c r="F42" t="n">
         <v>8.85</v>
       </c>
       <c r="G42" t="n">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H42" t="n">
-        <v>57</v>
+        <v>100</v>
       </c>
       <c r="I42" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J42" t="n">
-        <v>-65.79000000000001</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>200.71</v>
+        <v>-281.78</v>
       </c>
       <c r="L42" t="n">
-        <v>211.21</v>
+        <v>290.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>06:24:40</t>
+          <t>06:19:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.4</v>
+        <v>2.79</v>
       </c>
       <c r="F43" t="n">
-        <v>5.68</v>
+        <v>5.86</v>
       </c>
       <c r="G43" t="n">
-        <v>315.3</v>
+        <v>310.3</v>
       </c>
       <c r="H43" t="n">
-        <v>70.7</v>
+        <v>88.7</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J43" t="n">
-        <v>-56.13</v>
+        <v>-164.79</v>
       </c>
       <c r="K43" t="n">
-        <v>128.1</v>
+        <v>-16.37</v>
       </c>
       <c r="L43" t="n">
-        <v>139.86</v>
+        <v>165.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>06:37:20</t>
+          <t>06:30:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="F44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="G44" t="n">
-        <v>317.8</v>
+        <v>310.4</v>
       </c>
       <c r="H44" t="n">
-        <v>45.6</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J44" t="n">
-        <v>25.37</v>
+        <v>61.24</v>
       </c>
       <c r="K44" t="n">
-        <v>35.51</v>
+        <v>5.6</v>
       </c>
       <c r="L44" t="n">
-        <v>43.64</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>06:39:27</t>
+          <t>06:31:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="F45" t="n">
-        <v>3.64</v>
+        <v>8.85</v>
       </c>
       <c r="G45" t="n">
-        <v>320.4</v>
+        <v>321.4</v>
       </c>
       <c r="H45" t="n">
-        <v>41.6</v>
+        <v>30.2</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.06</v>
+        <v>-32.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-37.71</v>
+        <v>-21.01</v>
       </c>
       <c r="L45" t="n">
-        <v>38.78</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>06:40:35</t>
+          <t>06:34:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1972,31 +1972,31 @@
         <v>2.53</v>
       </c>
       <c r="F46" t="n">
-        <v>7.15</v>
+        <v>8.85</v>
       </c>
       <c r="G46" t="n">
-        <v>297.5</v>
+        <v>319.8</v>
       </c>
       <c r="H46" t="n">
-        <v>54</v>
+        <v>58.9</v>
       </c>
       <c r="I46" t="n">
         <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-21.79</v>
+        <v>27.54</v>
       </c>
       <c r="K46" t="n">
-        <v>25.63</v>
+        <v>-34.98</v>
       </c>
       <c r="L46" t="n">
-        <v>33.64</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>06:45:24</t>
+          <t>06:38:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="F47" t="n">
-        <v>8.85</v>
+        <v>6.85</v>
       </c>
       <c r="G47" t="n">
-        <v>312.6</v>
+        <v>300.2</v>
       </c>
       <c r="H47" t="n">
-        <v>35</v>
+        <v>24.2</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-38.55</v>
+        <v>-54</v>
       </c>
       <c r="K47" t="n">
-        <v>-56.5</v>
+        <v>37.08</v>
       </c>
       <c r="L47" t="n">
-        <v>68.40000000000001</v>
+        <v>65.51000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>06:47:03</t>
+          <t>06:40:43</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.39</v>
+        <v>2.65</v>
       </c>
       <c r="F48" t="n">
-        <v>8.85</v>
+        <v>7.66</v>
       </c>
       <c r="G48" t="n">
-        <v>314.8</v>
+        <v>312.3</v>
       </c>
       <c r="H48" t="n">
-        <v>86</v>
+        <v>37.3</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>-20.4</v>
+        <v>-63.87</v>
       </c>
       <c r="K48" t="n">
-        <v>44.74</v>
+        <v>21.29</v>
       </c>
       <c r="L48" t="n">
-        <v>49.17</v>
+        <v>67.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>06:49:01</t>
+          <t>06:42:29</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="F49" t="n">
-        <v>4.79</v>
+        <v>8.85</v>
       </c>
       <c r="G49" t="n">
-        <v>318.8</v>
+        <v>314.7</v>
       </c>
       <c r="H49" t="n">
-        <v>90.2</v>
+        <v>100</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-58.37</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>17.59</v>
+        <v>-0.02</v>
       </c>
       <c r="L49" t="n">
-        <v>60.96</v>
+        <v>85.84999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>06:55:16</t>
+          <t>06:48:27</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.43</v>
+        <v>3.72</v>
       </c>
       <c r="F50" t="n">
-        <v>6.53</v>
+        <v>8.85</v>
       </c>
       <c r="G50" t="n">
-        <v>325.4</v>
+        <v>316</v>
       </c>
       <c r="H50" t="n">
-        <v>93.7</v>
+        <v>27.7</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.01</v>
+        <v>97.72</v>
       </c>
       <c r="K50" t="n">
-        <v>-117.06</v>
+        <v>-138.77</v>
       </c>
       <c r="L50" t="n">
-        <v>120.6</v>
+        <v>169.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>06:57:16</t>
+          <t>06:49:16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="F51" t="n">
-        <v>8.58</v>
+        <v>5.5</v>
       </c>
       <c r="G51" t="n">
-        <v>308.6</v>
+        <v>326.2</v>
       </c>
       <c r="H51" t="n">
-        <v>28.3</v>
+        <v>16.1</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.71</v>
+        <v>43.43</v>
       </c>
       <c r="K51" t="n">
-        <v>-59.45</v>
+        <v>101.3</v>
       </c>
       <c r="L51" t="n">
-        <v>87.14</v>
+        <v>110.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>06:58:30</t>
+          <t>06:50:50</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="F52" t="n">
-        <v>7.06</v>
+        <v>7.39</v>
       </c>
       <c r="G52" t="n">
-        <v>296.6</v>
+        <v>297.8</v>
       </c>
       <c r="H52" t="n">
-        <v>57.6</v>
+        <v>75.3</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>56.67</v>
+        <v>46.15</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.04000000000001</v>
+        <v>92.81</v>
       </c>
       <c r="L52" t="n">
-        <v>95.64</v>
+        <v>103.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:02:26</t>
+          <t>06:55:31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.95</v>
+        <v>2.43</v>
       </c>
       <c r="F53" t="n">
-        <v>8.23</v>
+        <v>5.96</v>
       </c>
       <c r="G53" t="n">
-        <v>304.7</v>
+        <v>306.9</v>
       </c>
       <c r="H53" t="n">
-        <v>45.2</v>
+        <v>38</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>-73.62</v>
+        <v>-120.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-109.97</v>
+        <v>-147.31</v>
       </c>
       <c r="L53" t="n">
-        <v>132.34</v>
+        <v>190.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:04:06</t>
+          <t>06:56:40</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.28</v>
+        <v>2.84</v>
       </c>
       <c r="F54" t="n">
-        <v>5.78</v>
+        <v>7.78</v>
       </c>
       <c r="G54" t="n">
-        <v>308</v>
+        <v>317.8</v>
       </c>
       <c r="H54" t="n">
-        <v>40.3</v>
+        <v>41.6</v>
       </c>
       <c r="I54" t="n">
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>102.48</v>
+        <v>105.32</v>
       </c>
       <c r="K54" t="n">
-        <v>-35.3</v>
+        <v>126.3</v>
       </c>
       <c r="L54" t="n">
-        <v>108.39</v>
+        <v>164.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:05:51</t>
+          <t>06:59:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.56</v>
+        <v>2.76</v>
       </c>
       <c r="F55" t="n">
         <v>8.85</v>
       </c>
       <c r="G55" t="n">
-        <v>312</v>
+        <v>316.8</v>
       </c>
       <c r="H55" t="n">
-        <v>72.8</v>
+        <v>24.6</v>
       </c>
       <c r="I55" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J55" t="n">
-        <v>89.64</v>
+        <v>126.6</v>
       </c>
       <c r="K55" t="n">
-        <v>-158.96</v>
+        <v>-144.08</v>
       </c>
       <c r="L55" t="n">
-        <v>182.49</v>
+        <v>191.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:10:41</t>
+          <t>07:02:40</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="F56" t="n">
-        <v>7.03</v>
+        <v>7.23</v>
       </c>
       <c r="G56" t="n">
-        <v>305.8</v>
+        <v>310.3</v>
       </c>
       <c r="H56" t="n">
-        <v>65</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>-135.37</v>
+        <v>-77.81</v>
       </c>
       <c r="K56" t="n">
-        <v>-63.51</v>
+        <v>-187.89</v>
       </c>
       <c r="L56" t="n">
-        <v>149.53</v>
+        <v>203.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:11:31</t>
+          <t>07:05:15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="F57" t="n">
-        <v>8.85</v>
+        <v>6.46</v>
       </c>
       <c r="G57" t="n">
-        <v>315</v>
+        <v>318.9</v>
       </c>
       <c r="H57" t="n">
-        <v>79.2</v>
+        <v>34.4</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J57" t="n">
-        <v>146.94</v>
+        <v>-119.7</v>
       </c>
       <c r="K57" t="n">
-        <v>85.58</v>
+        <v>-90.04000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>170.04</v>
+        <v>149.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:13:46</t>
+          <t>07:07:49</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.03</v>
+        <v>2.69</v>
       </c>
       <c r="F58" t="n">
         <v>8.85</v>
       </c>
       <c r="G58" t="n">
-        <v>319.6</v>
+        <v>312.9</v>
       </c>
       <c r="H58" t="n">
-        <v>18.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="J58" t="n">
-        <v>-139.41</v>
+        <v>206.35</v>
       </c>
       <c r="K58" t="n">
-        <v>96.69</v>
+        <v>-109.29</v>
       </c>
       <c r="L58" t="n">
-        <v>169.66</v>
+        <v>233.51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>07:25:38</t>
+          <t>07:19:05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.52</v>
+        <v>2.06</v>
       </c>
       <c r="F59" t="n">
-        <v>5.77</v>
+        <v>3.95</v>
       </c>
       <c r="G59" t="n">
-        <v>300.8</v>
+        <v>305</v>
       </c>
       <c r="H59" t="n">
-        <v>35.3</v>
+        <v>19.6</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-6.96</v>
+        <v>13.37</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.99</v>
+        <v>31</v>
       </c>
       <c r="L59" t="n">
-        <v>39.61</v>
+        <v>33.76</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>07:27:17</t>
+          <t>07:20:03</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="F60" t="n">
-        <v>8.77</v>
+        <v>8.81</v>
       </c>
       <c r="G60" t="n">
-        <v>321.2</v>
+        <v>308.9</v>
       </c>
       <c r="H60" t="n">
-        <v>44.4</v>
+        <v>99.7</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J60" t="n">
-        <v>-19.99</v>
+        <v>-29.68</v>
       </c>
       <c r="K60" t="n">
-        <v>-23.39</v>
+        <v>27.69</v>
       </c>
       <c r="L60" t="n">
-        <v>30.77</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>07:29:19</t>
+          <t>07:21:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="F61" t="n">
         <v>8.85</v>
       </c>
       <c r="G61" t="n">
-        <v>300.5</v>
+        <v>312.6</v>
       </c>
       <c r="H61" t="n">
-        <v>67.90000000000001</v>
+        <v>35</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-16.13</v>
+        <v>-17.69</v>
       </c>
       <c r="K61" t="n">
-        <v>6.14</v>
+        <v>-41.75</v>
       </c>
       <c r="L61" t="n">
-        <v>17.26</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>07:33:24</t>
+          <t>07:26:07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.97</v>
+        <v>2.47</v>
       </c>
       <c r="F62" t="n">
         <v>8.85</v>
       </c>
       <c r="G62" t="n">
-        <v>303.9</v>
+        <v>314.8</v>
       </c>
       <c r="H62" t="n">
-        <v>56.6</v>
+        <v>86</v>
       </c>
       <c r="I62" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.72</v>
+        <v>-18.03</v>
       </c>
       <c r="K62" t="n">
-        <v>42.53</v>
+        <v>48.78</v>
       </c>
       <c r="L62" t="n">
-        <v>77.44</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>07:35:08</t>
+          <t>07:27:25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.69</v>
+        <v>2.54</v>
       </c>
       <c r="F63" t="n">
-        <v>7.01</v>
+        <v>5.16</v>
       </c>
       <c r="G63" t="n">
-        <v>314.6</v>
+        <v>318.8</v>
       </c>
       <c r="H63" t="n">
-        <v>45.5</v>
+        <v>90.2</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J63" t="n">
-        <v>39.27</v>
+        <v>-63.26</v>
       </c>
       <c r="K63" t="n">
-        <v>52.74</v>
+        <v>11.48</v>
       </c>
       <c r="L63" t="n">
-        <v>65.75</v>
+        <v>64.29000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>07:36:46</t>
+          <t>07:28:59</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="F64" t="n">
-        <v>6.07</v>
+        <v>6.85</v>
       </c>
       <c r="G64" t="n">
-        <v>320.2</v>
+        <v>325.4</v>
       </c>
       <c r="H64" t="n">
-        <v>17</v>
+        <v>93.7</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>52.42</v>
+        <v>-9.27</v>
       </c>
       <c r="K64" t="n">
-        <v>-39.18</v>
+        <v>-86.67</v>
       </c>
       <c r="L64" t="n">
-        <v>65.44</v>
+        <v>87.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>07:41:34</t>
+          <t>07:34:19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="F65" t="n">
         <v>8.85</v>
       </c>
       <c r="G65" t="n">
-        <v>320.7</v>
+        <v>308.6</v>
       </c>
       <c r="H65" t="n">
-        <v>77.59999999999999</v>
+        <v>28.3</v>
       </c>
       <c r="I65" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>57.22</v>
+        <v>-51.93</v>
       </c>
       <c r="K65" t="n">
-        <v>70.53</v>
+        <v>-74.81999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>90.81999999999999</v>
+        <v>91.08</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>07:42:58</t>
+          <t>07:36:11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="F66" t="n">
-        <v>5.09</v>
+        <v>7.44</v>
       </c>
       <c r="G66" t="n">
-        <v>296.1</v>
+        <v>296.6</v>
       </c>
       <c r="H66" t="n">
-        <v>41.7</v>
+        <v>57.6</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J66" t="n">
-        <v>-92.72</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>24.41</v>
+        <v>-76.20999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>95.88</v>
+        <v>100.46</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>07:44:19</t>
+          <t>07:38:21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.59</v>
+        <v>3.02</v>
       </c>
       <c r="F67" t="n">
-        <v>7.21</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>325.2</v>
+        <v>304.7</v>
       </c>
       <c r="H67" t="n">
-        <v>26.4</v>
+        <v>45.2</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>4.82</v>
+        <v>-39.37</v>
       </c>
       <c r="K67" t="n">
-        <v>82.3</v>
+        <v>85.11</v>
       </c>
       <c r="L67" t="n">
-        <v>82.44</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>07:48:15</t>
+          <t>07:42:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="F68" t="n">
-        <v>7.85</v>
+        <v>5.18</v>
       </c>
       <c r="G68" t="n">
-        <v>315.6</v>
+        <v>305.8</v>
       </c>
       <c r="H68" t="n">
-        <v>98.7</v>
+        <v>39.3</v>
       </c>
       <c r="I68" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>146</v>
+        <v>91.66</v>
       </c>
       <c r="K68" t="n">
-        <v>44.34</v>
+        <v>-65.94</v>
       </c>
       <c r="L68" t="n">
-        <v>152.58</v>
+        <v>112.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>07:49:09</t>
+          <t>07:43:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="F69" t="n">
         <v>8.85</v>
       </c>
       <c r="G69" t="n">
-        <v>320.3</v>
+        <v>305.3</v>
       </c>
       <c r="H69" t="n">
-        <v>50.7</v>
+        <v>69.2</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J69" t="n">
-        <v>143.63</v>
+        <v>153.13</v>
       </c>
       <c r="K69" t="n">
-        <v>-2.52</v>
+        <v>7.19</v>
       </c>
       <c r="L69" t="n">
-        <v>143.65</v>
+        <v>153.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>07:50:38</t>
+          <t>07:45:53</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="F70" t="n">
         <v>8.85</v>
       </c>
       <c r="G70" t="n">
-        <v>294.8</v>
+        <v>307</v>
       </c>
       <c r="H70" t="n">
-        <v>49.4</v>
+        <v>77.3</v>
       </c>
       <c r="I70" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>0.26</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-128.59</v>
+        <v>-133.28</v>
       </c>
       <c r="L70" t="n">
-        <v>128.59</v>
+        <v>154.41</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>07:56:10</t>
+          <t>07:50:17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.82</v>
+        <v>2.54</v>
       </c>
       <c r="F71" t="n">
-        <v>8.65</v>
+        <v>7.07</v>
       </c>
       <c r="G71" t="n">
-        <v>302.8</v>
+        <v>313.1</v>
       </c>
       <c r="H71" t="n">
-        <v>36.7</v>
+        <v>67.3</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-184.67</v>
+        <v>41.52</v>
       </c>
       <c r="K71" t="n">
-        <v>-89.06</v>
+        <v>177.06</v>
       </c>
       <c r="L71" t="n">
-        <v>205.03</v>
+        <v>181.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>07:58:29</t>
+          <t>07:51:30</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="F72" t="n">
-        <v>3.39</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>313.6</v>
+        <v>302.7</v>
       </c>
       <c r="H72" t="n">
-        <v>70.7</v>
+        <v>59.5</v>
       </c>
       <c r="I72" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>200.52</v>
+        <v>156.31</v>
       </c>
       <c r="K72" t="n">
-        <v>20.54</v>
+        <v>99.11</v>
       </c>
       <c r="L72" t="n">
-        <v>201.57</v>
+        <v>185.08</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>07:59:41</t>
+          <t>07:53:00</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.52</v>
+        <v>3.02</v>
       </c>
       <c r="F73" t="n">
-        <v>7.38</v>
+        <v>8.85</v>
       </c>
       <c r="G73" t="n">
-        <v>299</v>
+        <v>307.8</v>
       </c>
       <c r="H73" t="n">
-        <v>70.40000000000001</v>
+        <v>46.6</v>
       </c>
       <c r="I73" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>42.35</v>
+        <v>87.31</v>
       </c>
       <c r="K73" t="n">
-        <v>144.45</v>
+        <v>173.74</v>
       </c>
       <c r="L73" t="n">
-        <v>150.53</v>
+        <v>194.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:08:17</t>
+          <t>08:04:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="F74" t="n">
-        <v>8.279999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G74" t="n">
-        <v>312.8</v>
+        <v>318.4</v>
       </c>
       <c r="H74" t="n">
-        <v>26.8</v>
+        <v>59.2</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>-15.98</v>
+        <v>-13.35</v>
       </c>
       <c r="K74" t="n">
-        <v>45.76</v>
+        <v>47.23</v>
       </c>
       <c r="L74" t="n">
-        <v>48.47</v>
+        <v>49.08</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:10:23</t>
+          <t>08:06:22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.46</v>
+        <v>3.16</v>
       </c>
       <c r="F75" t="n">
-        <v>8.85</v>
+        <v>6.2</v>
       </c>
       <c r="G75" t="n">
-        <v>301.8</v>
+        <v>326.5</v>
       </c>
       <c r="H75" t="n">
-        <v>33.1</v>
+        <v>71.7</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>19.19</v>
+        <v>59.33</v>
       </c>
       <c r="K75" t="n">
-        <v>42.16</v>
+        <v>24.65</v>
       </c>
       <c r="L75" t="n">
-        <v>46.33</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>08:13:04</t>
+          <t>08:07:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.63</v>
+        <v>3.44</v>
       </c>
       <c r="F76" t="n">
         <v>8.85</v>
       </c>
       <c r="G76" t="n">
-        <v>310.4</v>
+        <v>304.7</v>
       </c>
       <c r="H76" t="n">
-        <v>53</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.2</v>
+        <v>-46.97</v>
       </c>
       <c r="K76" t="n">
-        <v>18.64</v>
+        <v>-43.54</v>
       </c>
       <c r="L76" t="n">
-        <v>36.34</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>08:18:39</t>
+          <t>08:13:13</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.56</v>
+        <v>2.24</v>
       </c>
       <c r="F77" t="n">
-        <v>8</v>
+        <v>6.93</v>
       </c>
       <c r="G77" t="n">
-        <v>305.5</v>
+        <v>314.3</v>
       </c>
       <c r="H77" t="n">
-        <v>43.7</v>
+        <v>12.8</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J77" t="n">
-        <v>28.98</v>
+        <v>-38.15</v>
       </c>
       <c r="K77" t="n">
-        <v>71.34</v>
+        <v>30.05</v>
       </c>
       <c r="L77" t="n">
-        <v>77</v>
+        <v>48.56</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>08:20:13</t>
+          <t>08:15:42</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="F78" t="n">
-        <v>7.56</v>
+        <v>8.85</v>
       </c>
       <c r="G78" t="n">
-        <v>323</v>
+        <v>308.2</v>
       </c>
       <c r="H78" t="n">
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
       <c r="I78" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J78" t="n">
-        <v>22.06</v>
+        <v>-32.13</v>
       </c>
       <c r="K78" t="n">
-        <v>47.14</v>
+        <v>47.39</v>
       </c>
       <c r="L78" t="n">
-        <v>52.04</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>08:21:49</t>
+          <t>08:17:45</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.54</v>
+        <v>2.74</v>
       </c>
       <c r="F79" t="n">
-        <v>8.85</v>
+        <v>7.3</v>
       </c>
       <c r="G79" t="n">
-        <v>307.3</v>
+        <v>330.9</v>
       </c>
       <c r="H79" t="n">
-        <v>71.40000000000001</v>
+        <v>40.8</v>
       </c>
       <c r="I79" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>-54.24</v>
+        <v>74</v>
       </c>
       <c r="K79" t="n">
-        <v>27.05</v>
+        <v>31.16</v>
       </c>
       <c r="L79" t="n">
-        <v>60.61</v>
+        <v>80.29000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>08:24:45</t>
+          <t>08:22:03</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="F80" t="n">
-        <v>8.85</v>
+        <v>8.02</v>
       </c>
       <c r="G80" t="n">
-        <v>309.1</v>
+        <v>307.1</v>
       </c>
       <c r="H80" t="n">
-        <v>36.1</v>
+        <v>48.3</v>
       </c>
       <c r="I80" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>21.16</v>
+        <v>60.74</v>
       </c>
       <c r="K80" t="n">
-        <v>92.91</v>
+        <v>-63.95</v>
       </c>
       <c r="L80" t="n">
-        <v>95.29000000000001</v>
+        <v>88.19</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>08:26:26</t>
+          <t>08:24:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="F81" t="n">
-        <v>7.33</v>
+        <v>8.85</v>
       </c>
       <c r="G81" t="n">
-        <v>316.9</v>
+        <v>312.8</v>
       </c>
       <c r="H81" t="n">
-        <v>37.5</v>
+        <v>48.9</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>47.7</v>
+        <v>77.53</v>
       </c>
       <c r="K81" t="n">
-        <v>83.59</v>
+        <v>18.06</v>
       </c>
       <c r="L81" t="n">
-        <v>96.23999999999999</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>08:28:51</t>
+          <t>08:25:18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="F82" t="n">
-        <v>8.289999999999999</v>
+        <v>7.23</v>
       </c>
       <c r="G82" t="n">
-        <v>307.2</v>
+        <v>307.9</v>
       </c>
       <c r="H82" t="n">
-        <v>37.7</v>
+        <v>61.2</v>
       </c>
       <c r="I82" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J82" t="n">
-        <v>-48.1</v>
+        <v>122.77</v>
       </c>
       <c r="K82" t="n">
-        <v>54.07</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>72.37</v>
+        <v>123.11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>08:34:25</t>
+          <t>08:30:34</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.73</v>
+        <v>2.96</v>
       </c>
       <c r="F83" t="n">
         <v>8.85</v>
       </c>
       <c r="G83" t="n">
-        <v>308</v>
+        <v>310.5</v>
       </c>
       <c r="H83" t="n">
-        <v>8.5</v>
+        <v>14.2</v>
       </c>
       <c r="I83" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>121.16</v>
+        <v>-199.97</v>
       </c>
       <c r="K83" t="n">
-        <v>-96.67</v>
+        <v>20.3</v>
       </c>
       <c r="L83" t="n">
-        <v>155</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>08:35:23</t>
+          <t>08:31:10</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.73</v>
+        <v>3.06</v>
       </c>
       <c r="F84" t="n">
         <v>8.85</v>
       </c>
       <c r="G84" t="n">
-        <v>317.4</v>
+        <v>291.5</v>
       </c>
       <c r="H84" t="n">
-        <v>44.5</v>
+        <v>53.1</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>73.89</v>
+        <v>87.31</v>
       </c>
       <c r="K84" t="n">
-        <v>117.07</v>
+        <v>-143.95</v>
       </c>
       <c r="L84" t="n">
-        <v>138.43</v>
+        <v>168.36</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>08:37:55</t>
+          <t>08:33:03</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.79</v>
+        <v>3.1</v>
       </c>
       <c r="F85" t="n">
-        <v>8.109999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>303.5</v>
+        <v>313</v>
       </c>
       <c r="H85" t="n">
-        <v>46.3</v>
+        <v>69.8</v>
       </c>
       <c r="I85" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>-102.44</v>
+        <v>127.31</v>
       </c>
       <c r="K85" t="n">
-        <v>61.98</v>
+        <v>105.13</v>
       </c>
       <c r="L85" t="n">
-        <v>119.73</v>
+        <v>165.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>08:43:20</t>
+          <t>08:39:05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="F86" t="n">
-        <v>8.609999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G86" t="n">
-        <v>319.4</v>
+        <v>290.4</v>
       </c>
       <c r="H86" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J86" t="n">
-        <v>-208.32</v>
+        <v>161.7</v>
       </c>
       <c r="K86" t="n">
-        <v>27.7</v>
+        <v>-59.92</v>
       </c>
       <c r="L86" t="n">
-        <v>210.16</v>
+        <v>172.45</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>08:44:15</t>
+          <t>08:40:33</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.03</v>
+        <v>2.79</v>
       </c>
       <c r="F87" t="n">
-        <v>6.6</v>
+        <v>8.85</v>
       </c>
       <c r="G87" t="n">
-        <v>306.7</v>
+        <v>307.2</v>
       </c>
       <c r="H87" t="n">
-        <v>51.7</v>
+        <v>30.6</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J87" t="n">
-        <v>165.18</v>
+        <v>-126.22</v>
       </c>
       <c r="K87" t="n">
-        <v>-238.46</v>
+        <v>155.21</v>
       </c>
       <c r="L87" t="n">
-        <v>290.09</v>
+        <v>200.05</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>08:46:31</t>
+          <t>08:42:58</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.61</v>
+        <v>2.88</v>
       </c>
       <c r="F88" t="n">
-        <v>7.59</v>
+        <v>8.82</v>
       </c>
       <c r="G88" t="n">
-        <v>318.3</v>
+        <v>310.9</v>
       </c>
       <c r="H88" t="n">
-        <v>38.8</v>
+        <v>59.6</v>
       </c>
       <c r="I88" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>-41.07</v>
+        <v>-162.86</v>
       </c>
       <c r="K88" t="n">
-        <v>-259.43</v>
+        <v>-94.44</v>
       </c>
       <c r="L88" t="n">
-        <v>262.66</v>
+        <v>188.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -640,13 +640,13 @@
         <v>26</v>
       </c>
       <c r="J14" t="n">
-        <v>17.82</v>
+        <v>20.13</v>
       </c>
       <c r="K14" t="n">
-        <v>-24.98</v>
+        <v>-28.21</v>
       </c>
       <c r="L14" t="n">
-        <v>30.68</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>27</v>
       </c>
       <c r="J15" t="n">
-        <v>-32.16</v>
+        <v>-34.26</v>
       </c>
       <c r="K15" t="n">
-        <v>-15.57</v>
+        <v>-16.59</v>
       </c>
       <c r="L15" t="n">
-        <v>35.73</v>
+        <v>38.06</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>31.16</v>
+        <v>33.88</v>
       </c>
       <c r="K16" t="n">
-        <v>-27.76</v>
+        <v>-30.18</v>
       </c>
       <c r="L16" t="n">
-        <v>41.73</v>
+        <v>45.37</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>50.46</v>
+        <v>52.33</v>
       </c>
       <c r="K17" t="n">
-        <v>58.61</v>
+        <v>60.78</v>
       </c>
       <c r="L17" t="n">
-        <v>77.34</v>
+        <v>80.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>6.13</v>
+        <v>7.09</v>
       </c>
       <c r="K18" t="n">
-        <v>-14.38</v>
+        <v>-16.62</v>
       </c>
       <c r="L18" t="n">
-        <v>15.63</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-29.98</v>
+        <v>-28.52</v>
       </c>
       <c r="K19" t="n">
-        <v>-104.58</v>
+        <v>-99.45</v>
       </c>
       <c r="L19" t="n">
-        <v>108.79</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>69.65000000000001</v>
+        <v>75.58</v>
       </c>
       <c r="K20" t="n">
-        <v>80.54000000000001</v>
+        <v>87.39</v>
       </c>
       <c r="L20" t="n">
-        <v>106.47</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-87.89</v>
+        <v>-97.06</v>
       </c>
       <c r="K21" t="n">
-        <v>-49.69</v>
+        <v>-54.88</v>
       </c>
       <c r="L21" t="n">
-        <v>100.97</v>
+        <v>111.51</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-73.78</v>
+        <v>-83.95</v>
       </c>
       <c r="K22" t="n">
-        <v>-49.7</v>
+        <v>-56.55</v>
       </c>
       <c r="L22" t="n">
-        <v>88.95999999999999</v>
+        <v>101.22</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-84.94</v>
+        <v>-96.75</v>
       </c>
       <c r="K23" t="n">
-        <v>-81.86</v>
+        <v>-93.23999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>117.97</v>
+        <v>134.36</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.92</v>
+        <v>-149.58</v>
       </c>
       <c r="K24" t="n">
-        <v>13.36</v>
+        <v>15.15</v>
       </c>
       <c r="L24" t="n">
-        <v>132.59</v>
+        <v>150.34</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>20.86</v>
+        <v>25.32</v>
       </c>
       <c r="K25" t="n">
-        <v>-87.08</v>
+        <v>-105.72</v>
       </c>
       <c r="L25" t="n">
-        <v>89.54000000000001</v>
+        <v>108.71</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-130.15</v>
+        <v>-156.9</v>
       </c>
       <c r="K26" t="n">
-        <v>123.67</v>
+        <v>149.1</v>
       </c>
       <c r="L26" t="n">
-        <v>179.54</v>
+        <v>216.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>79.95</v>
+        <v>91.23</v>
       </c>
       <c r="K27" t="n">
-        <v>222.63</v>
+        <v>254.04</v>
       </c>
       <c r="L27" t="n">
-        <v>236.55</v>
+        <v>269.93</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.89</v>
+        <v>-7.1</v>
       </c>
       <c r="K28" t="n">
-        <v>-194.93</v>
+        <v>-234.99</v>
       </c>
       <c r="L28" t="n">
-        <v>195.02</v>
+        <v>235.09</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>24.15</v>
+        <v>24.57</v>
       </c>
       <c r="K29" t="n">
-        <v>-45.76</v>
+        <v>-46.56</v>
       </c>
       <c r="L29" t="n">
-        <v>51.75</v>
+        <v>52.65</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>56.55</v>
+        <v>59.17</v>
       </c>
       <c r="K30" t="n">
-        <v>-21.33</v>
+        <v>-22.32</v>
       </c>
       <c r="L30" t="n">
-        <v>60.44</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>-33.08</v>
+        <v>-35.24</v>
       </c>
       <c r="K31" t="n">
-        <v>33.91</v>
+        <v>36.12</v>
       </c>
       <c r="L31" t="n">
-        <v>47.37</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-4.36</v>
+        <v>-5.23</v>
       </c>
       <c r="K32" t="n">
-        <v>32.55</v>
+        <v>39.03</v>
       </c>
       <c r="L32" t="n">
-        <v>32.84</v>
+        <v>39.38</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>82.44</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-39.52</v>
+        <v>-39.36</v>
       </c>
       <c r="L33" t="n">
-        <v>91.42</v>
+        <v>91.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>-11.69</v>
+        <v>-13.04</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.91</v>
+        <v>-62.37</v>
       </c>
       <c r="L34" t="n">
-        <v>57.12</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>88.14</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>51.99</v>
+        <v>57.34</v>
       </c>
       <c r="L35" t="n">
-        <v>102.33</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>76.65000000000001</v>
+        <v>88.41</v>
       </c>
       <c r="K36" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10.73</v>
       </c>
       <c r="L36" t="n">
-        <v>77.20999999999999</v>
+        <v>89.06</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>44.28</v>
+        <v>52.97</v>
       </c>
       <c r="K37" t="n">
-        <v>-59.6</v>
+        <v>-71.29000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>74.25</v>
+        <v>88.81999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>-23.78</v>
+        <v>-26.67</v>
       </c>
       <c r="K38" t="n">
-        <v>133.53</v>
+        <v>149.73</v>
       </c>
       <c r="L38" t="n">
-        <v>135.63</v>
+        <v>152.09</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.98999999999999</v>
+        <v>-117.8</v>
       </c>
       <c r="K39" t="n">
-        <v>17.16</v>
+        <v>21.74</v>
       </c>
       <c r="L39" t="n">
-        <v>94.56</v>
+        <v>119.79</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>-51.38</v>
+        <v>-61.63</v>
       </c>
       <c r="K40" t="n">
-        <v>-80.03</v>
+        <v>-96</v>
       </c>
       <c r="L40" t="n">
-        <v>95.09999999999999</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>22</v>
       </c>
       <c r="J41" t="n">
-        <v>-257.2</v>
+        <v>-288.72</v>
       </c>
       <c r="K41" t="n">
-        <v>52.1</v>
+        <v>58.48</v>
       </c>
       <c r="L41" t="n">
-        <v>262.42</v>
+        <v>294.59</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>40.63</v>
+        <v>49.43</v>
       </c>
       <c r="K42" t="n">
-        <v>-173.63</v>
+        <v>-211.24</v>
       </c>
       <c r="L42" t="n">
-        <v>178.32</v>
+        <v>216.95</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>-61.68</v>
+        <v>-80.22</v>
       </c>
       <c r="K43" t="n">
-        <v>129.16</v>
+        <v>167.97</v>
       </c>
       <c r="L43" t="n">
-        <v>143.13</v>
+        <v>186.14</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>-46.37</v>
+        <v>-45.39</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.35</v>
+        <v>-52.23</v>
       </c>
       <c r="L44" t="n">
-        <v>70.68000000000001</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>62.34</v>
+        <v>64.23</v>
       </c>
       <c r="K45" t="n">
-        <v>31.57</v>
+        <v>32.53</v>
       </c>
       <c r="L45" t="n">
-        <v>69.88</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-61.75</v>
+        <v>-60.47</v>
       </c>
       <c r="K46" t="n">
-        <v>9.77</v>
+        <v>9.57</v>
       </c>
       <c r="L46" t="n">
-        <v>62.52</v>
+        <v>61.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>42.32</v>
+        <v>46.73</v>
       </c>
       <c r="K47" t="n">
-        <v>27.98</v>
+        <v>30.9</v>
       </c>
       <c r="L47" t="n">
-        <v>50.74</v>
+        <v>56.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>24.68</v>
+        <v>28.15</v>
       </c>
       <c r="K48" t="n">
-        <v>-49.31</v>
+        <v>-56.25</v>
       </c>
       <c r="L48" t="n">
-        <v>55.15</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>25</v>
       </c>
       <c r="J49" t="n">
-        <v>-28.26</v>
+        <v>-29.88</v>
       </c>
       <c r="K49" t="n">
-        <v>56.05</v>
+        <v>59.26</v>
       </c>
       <c r="L49" t="n">
-        <v>62.77</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>75.34</v>
+        <v>86.72</v>
       </c>
       <c r="K50" t="n">
-        <v>-46.82</v>
+        <v>-53.9</v>
       </c>
       <c r="L50" t="n">
-        <v>88.7</v>
+        <v>102.1</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>21</v>
       </c>
       <c r="J51" t="n">
-        <v>-43.81</v>
+        <v>-50.67</v>
       </c>
       <c r="K51" t="n">
-        <v>-81.16</v>
+        <v>-93.86</v>
       </c>
       <c r="L51" t="n">
-        <v>92.23</v>
+        <v>106.67</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-47.83</v>
+        <v>-58.25</v>
       </c>
       <c r="K52" t="n">
-        <v>52.58</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>71.08</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>10.17</v>
+        <v>12.07</v>
       </c>
       <c r="K53" t="n">
-        <v>-88.56999999999999</v>
+        <v>-105.18</v>
       </c>
       <c r="L53" t="n">
-        <v>89.15000000000001</v>
+        <v>105.87</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>95.16</v>
+        <v>105.5</v>
       </c>
       <c r="K54" t="n">
-        <v>114.71</v>
+        <v>127.18</v>
       </c>
       <c r="L54" t="n">
-        <v>149.05</v>
+        <v>165.25</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>26</v>
       </c>
       <c r="J55" t="n">
-        <v>-19.35</v>
+        <v>-21.88</v>
       </c>
       <c r="K55" t="n">
-        <v>139.75</v>
+        <v>158.02</v>
       </c>
       <c r="L55" t="n">
-        <v>141.08</v>
+        <v>159.53</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>23</v>
       </c>
       <c r="J56" t="n">
-        <v>178.09</v>
+        <v>216.11</v>
       </c>
       <c r="K56" t="n">
-        <v>-64.36</v>
+        <v>-78.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>189.36</v>
+        <v>229.79</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>183.29</v>
+        <v>219.16</v>
       </c>
       <c r="K57" t="n">
-        <v>-49.41</v>
+        <v>-59.08</v>
       </c>
       <c r="L57" t="n">
-        <v>189.84</v>
+        <v>226.99</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>183.82</v>
+        <v>214.4</v>
       </c>
       <c r="K58" t="n">
-        <v>71.81</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>197.35</v>
+        <v>230.18</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>24</v>
       </c>
       <c r="J59" t="n">
-        <v>-71.38</v>
+        <v>-69.95999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>13.25</v>
+        <v>12.98</v>
       </c>
       <c r="L59" t="n">
-        <v>72.59999999999999</v>
+        <v>71.15000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>24</v>
       </c>
       <c r="J60" t="n">
-        <v>13.86</v>
+        <v>13.39</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.76000000000001</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>76.03</v>
+        <v>73.44</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-18.01</v>
+        <v>-18.42</v>
       </c>
       <c r="K61" t="n">
-        <v>-53.9</v>
+        <v>-55.11</v>
       </c>
       <c r="L61" t="n">
-        <v>56.83</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-26.16</v>
+        <v>-29.94</v>
       </c>
       <c r="K62" t="n">
-        <v>56.76</v>
+        <v>64.95</v>
       </c>
       <c r="L62" t="n">
-        <v>62.5</v>
+        <v>71.52</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>23</v>
       </c>
       <c r="J63" t="n">
-        <v>-67.23999999999999</v>
+        <v>-68.51000000000001</v>
       </c>
       <c r="K63" t="n">
-        <v>-47.78</v>
+        <v>-48.68</v>
       </c>
       <c r="L63" t="n">
-        <v>82.48999999999999</v>
+        <v>84.04000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-66.15000000000001</v>
+        <v>-67.88</v>
       </c>
       <c r="K64" t="n">
-        <v>59.75</v>
+        <v>61.32</v>
       </c>
       <c r="L64" t="n">
-        <v>89.14</v>
+        <v>91.48</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>-91.73</v>
+        <v>-101.23</v>
       </c>
       <c r="K65" t="n">
-        <v>44.47</v>
+        <v>49.07</v>
       </c>
       <c r="L65" t="n">
-        <v>101.94</v>
+        <v>112.49</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>21</v>
       </c>
       <c r="J66" t="n">
-        <v>44.06</v>
+        <v>53.38</v>
       </c>
       <c r="K66" t="n">
-        <v>62.69</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>76.62</v>
+        <v>92.84</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>23</v>
       </c>
       <c r="J67" t="n">
-        <v>106.35</v>
+        <v>118.32</v>
       </c>
       <c r="K67" t="n">
-        <v>-9.66</v>
+        <v>-10.74</v>
       </c>
       <c r="L67" t="n">
-        <v>106.79</v>
+        <v>118.81</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-3.15</v>
+        <v>-4.03</v>
       </c>
       <c r="K68" t="n">
-        <v>53.02</v>
+        <v>67.76000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>53.11</v>
+        <v>67.88</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>46.12</v>
+        <v>51.49</v>
       </c>
       <c r="K69" t="n">
-        <v>112.36</v>
+        <v>125.44</v>
       </c>
       <c r="L69" t="n">
-        <v>121.46</v>
+        <v>135.59</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>105.79</v>
+        <v>124.94</v>
       </c>
       <c r="K70" t="n">
-        <v>-49.55</v>
+        <v>-58.51</v>
       </c>
       <c r="L70" t="n">
-        <v>116.82</v>
+        <v>137.96</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>181.33</v>
+        <v>215.82</v>
       </c>
       <c r="K71" t="n">
-        <v>3.82</v>
+        <v>4.55</v>
       </c>
       <c r="L71" t="n">
-        <v>181.37</v>
+        <v>215.86</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-138.33</v>
+        <v>-177.97</v>
       </c>
       <c r="K72" t="n">
-        <v>42.04</v>
+        <v>54.09</v>
       </c>
       <c r="L72" t="n">
-        <v>144.58</v>
+        <v>186.01</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-124.69</v>
+        <v>-165.28</v>
       </c>
       <c r="K73" t="n">
-        <v>52.81</v>
+        <v>70</v>
       </c>
       <c r="L73" t="n">
-        <v>135.41</v>
+        <v>179.49</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>46.32</v>
+        <v>48.06</v>
       </c>
       <c r="K74" t="n">
-        <v>-46.33</v>
+        <v>-48.07</v>
       </c>
       <c r="L74" t="n">
-        <v>65.51000000000001</v>
+        <v>67.97</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-47.27</v>
+        <v>-53.43</v>
       </c>
       <c r="K75" t="n">
-        <v>28.93</v>
+        <v>32.71</v>
       </c>
       <c r="L75" t="n">
-        <v>55.42</v>
+        <v>62.65</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>44.31</v>
+        <v>49.8</v>
       </c>
       <c r="K76" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="L76" t="n">
-        <v>44.31</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-74.59999999999999</v>
+        <v>-76.66</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.49</v>
+        <v>-19</v>
       </c>
       <c r="L77" t="n">
-        <v>76.86</v>
+        <v>78.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>19.24</v>
+        <v>22.6</v>
       </c>
       <c r="K78" t="n">
-        <v>-45.24</v>
+        <v>-53.15</v>
       </c>
       <c r="L78" t="n">
-        <v>49.16</v>
+        <v>57.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>-42.57</v>
+        <v>-45.85</v>
       </c>
       <c r="K79" t="n">
-        <v>52.35</v>
+        <v>56.4</v>
       </c>
       <c r="L79" t="n">
-        <v>67.47</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-27.32</v>
+        <v>-27.95</v>
       </c>
       <c r="K80" t="n">
-        <v>-132.54</v>
+        <v>-135.6</v>
       </c>
       <c r="L80" t="n">
-        <v>135.33</v>
+        <v>138.45</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-103.48</v>
+        <v>-112.21</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.36</v>
+        <v>-18.82</v>
       </c>
       <c r="L81" t="n">
-        <v>104.93</v>
+        <v>113.77</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-39.18</v>
+        <v>-43.99</v>
       </c>
       <c r="K82" t="n">
-        <v>-82.70999999999999</v>
+        <v>-92.86</v>
       </c>
       <c r="L82" t="n">
-        <v>91.53</v>
+        <v>102.75</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>27</v>
       </c>
       <c r="J83" t="n">
-        <v>138.55</v>
+        <v>147.25</v>
       </c>
       <c r="K83" t="n">
-        <v>91.23</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="L83" t="n">
-        <v>165.89</v>
+        <v>176.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>129.95</v>
+        <v>154.74</v>
       </c>
       <c r="K84" t="n">
-        <v>12.58</v>
+        <v>14.98</v>
       </c>
       <c r="L84" t="n">
-        <v>130.56</v>
+        <v>155.46</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>-30.34</v>
+        <v>-34.12</v>
       </c>
       <c r="K85" t="n">
-        <v>154.4</v>
+        <v>173.67</v>
       </c>
       <c r="L85" t="n">
-        <v>157.36</v>
+        <v>176.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>-103.48</v>
+        <v>-120.79</v>
       </c>
       <c r="K86" t="n">
-        <v>-178.88</v>
+        <v>-208.8</v>
       </c>
       <c r="L86" t="n">
-        <v>206.65</v>
+        <v>241.22</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>-143.02</v>
+        <v>-171.46</v>
       </c>
       <c r="K87" t="n">
-        <v>-92.25</v>
+        <v>-110.6</v>
       </c>
       <c r="L87" t="n">
-        <v>170.19</v>
+        <v>204.04</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>25</v>
       </c>
       <c r="J88" t="n">
-        <v>122.54</v>
+        <v>147.56</v>
       </c>
       <c r="K88" t="n">
-        <v>121.86</v>
+        <v>146.75</v>
       </c>
       <c r="L88" t="n">
-        <v>172.82</v>
+        <v>208.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-07-21.xlsx
+++ b/output/2024-07-21.xlsx
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-29.94</v>
+        <v>-30.01</v>
       </c>
       <c r="K62" t="n">
-        <v>64.95</v>
+        <v>65.09</v>
       </c>
       <c r="L62" t="n">
-        <v>71.52</v>
+        <v>71.68000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-53.43</v>
+        <v>-55.51</v>
       </c>
       <c r="K75" t="n">
-        <v>32.71</v>
+        <v>33.98</v>
       </c>
       <c r="L75" t="n">
-        <v>62.65</v>
+        <v>65.09</v>
       </c>
     </row>
     <row r="76">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>22.6</v>
+        <v>22.91</v>
       </c>
       <c r="K78" t="n">
-        <v>-53.15</v>
+        <v>-53.88</v>
       </c>
       <c r="L78" t="n">
-        <v>57.75</v>
+        <v>58.55</v>
       </c>
     </row>
     <row r="79">
